--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -1460,7 +1460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6,000-page yield for Black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+          <t>The printer must integrate advanced AI-driven productivity features, scan workflow enhancements, and manageability solutions to ease business operations for SMBs.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>To meet market demand for higher yield and reduce frequency of replacements, improving customer satisfaction and cost efficiency.</t>
+          <t>Addresses the core value proposition of making business management easier for SMBs and differentiates from competitors.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1556,17 +1556,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Requires bottle redesign and compatibility with new IDS and tank system.</t>
+          <t>Requires integration with SMB portal and AI solution stack.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bottles must be validated to deliver at least 6,000 pages for Black and CMY, with CMY bottle size supporting &gt;8,000 pages in controlled tests.</t>
+          <t>Demonstrated AI productivity features in print and scan workflows; end-user can manage devices through provided solutions; meets user scenario tests.</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1574,10 +1574,14 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1590,17 +1594,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Lowest Business TCO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ensure all ink bottles and refilling processes are spill-free to enhance reliability and user experience.</t>
+          <t>The printer must deliver the lowest total cost of ownership (TCO) for SMB customers compared to HP's other business printers.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spill-free operation is critical for customer satisfaction and reducing warranty/service costs.</t>
+          <t>Cost efficiency is a top priority for SMBs and a key differentiator.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1610,28 +1614,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Marketing, BA, Quality</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bottle design, IDS, NOA-F integration.</t>
+          <t>Supply chain, pricing, and consumable costs.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No ink spillage observed in 99% of refilling scenarios during reliability testing.</t>
+          <t>Independent TCO analysis demonstrates lowest TCO among HP business printers for target use-case (AMPV ~500 pages/month).</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1644,17 +1652,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Integrate a metal foiled labyrinth and lid label into the NOA-F component, with no changes to click-on push-push and TDF mechanisms.</t>
+          <t>The printer must feature a maintenance box that can be replaced by customers without technical assistance, with service center fallback if needed.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enhances part reliability, security, and traceability without redesigning key mechanisms.</t>
+          <t>Reduces downtime and service costs for SMBs with limited IT resources.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1664,28 +1672,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality</t>
+          <t>Quality, R&amp;D Telemetry, Supplies Quality</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Existing NOA-F design, TDF, push-push mechanisms.</t>
+          <t>Design for serviceability, supply chain for replaceable parts.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NOA-F must pass validation with new labyrinth and lid label while maintaining existing functional interfaces.</t>
+          <t>User can replace maintenance box following provided instructions; no tools or minimal tools required; validated in usability testing.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1698,17 +1710,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Inks</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reuse the SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new platform.</t>
+          <t>The printer must use keyed ink bottles to prevent incorrect refilling and ensure user safety and product reliability.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D cost and leverages proven, reliable components.</t>
+          <t>Prevents user error and damage, supports warranty claims, and enhances customer experience.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1718,17 +1730,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>Supplies Quality, Quality, BA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and IDS systems.</t>
+          <t>Ink bottle design, printer hardware design.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks must meet all print quality and reliability standards in Magellan platform.</t>
+          <t>Only correct ink bottle fits and dispenses; passes misfill prevention tests.</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1736,10 +1748,14 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1752,17 +1768,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Enhanced Reliability and Characterization Modeling</t>
+          <t>SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Characterize and model reliability, WVTR, air gain, flow rate, IDS, startup, and NOA-F end-of-life (EOL) parameters.</t>
+          <t>A consolidated web-based portal must be provided for SMBs to manage and monitor their fleet of printers, tailored for non-IT users.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ensures system robustness, longevity, and supports warranty claims.</t>
+          <t>Enables SMBs to self-manage devices without dedicated IT staff, reducing support costs.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1772,28 +1788,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Integration with IDS, tank, and bottle systems.</t>
+          <t>Cloud services, device firmware integration, user authentication.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Models must be validated and predictive within +/-10% of observed reliability outcomes in pilot runs.</t>
+          <t>Portal is accessible, user-friendly, supports core management tasks (status, configuration, alerts) for 6-15 printers.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, 10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1806,48 +1826,52 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling</t>
+          <t>PaaS (Platform as a Service) Support</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Model ink stability in tanks and assess impact on print quality (PQ).</t>
+          <t>The printer and associated software must support integration with HP's PaaS offerings for enhanced solutions and services.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ensures long-term print quality and reduces field failures.</t>
+          <t>Supports HP's goal for PaaS acceleration and coverage; enables future solution monetization.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality</t>
+          <t>Tech Reg, Prod Steward, BA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tank design, ink properties, IDS interface.</t>
+          <t>Cloud infrastructure, HP PaaS APIs.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Ink stability modeling must predict PQ impact over 2-year warranty life with &lt;5% deviation from field data.</t>
+          <t>Printer can be registered and managed via HP's PaaS platform; integration validated in end-to-end tests.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 6, 10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1860,48 +1884,52 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>PDL/PS Support and Improved Print Speed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts for in-warranty support.</t>
+          <t>For PDL SKU, the printer must support PDL/PS and achieve print speeds of at least 25/20 ppm (improved from current 25/19).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reduces downtime and improves customer experience by enabling field replacement.</t>
+          <t>Meets business productivity needs and competitive benchmarks for print speed and compatibility.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>R&amp;D Telemetry, DVAR, Tech Reg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F part inventory, service logistics.</t>
+          <t>Hardware design, firmware, driver support.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NOA-F service parts available and replaceable within warranty support SLAs.</t>
+          <t>PDL/PS compatibility verified; print speed meets or exceeds 25/20 ppm in standard test scenarios.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1914,17 +1942,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology into the ink bottle lid for improved traceability or anti-counterfeiting.</t>
+          <t>The printer must meet Blue Angel environmental certification requirements for the relevant SKU.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Enhances product security and traceability in the supply chain.</t>
+          <t>Supports sustainability goals and competitive positioning, particularly in regulated markets.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1934,17 +1962,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Quality, Supply Chain, Security</t>
+          <t>Prod Steward, Quality, Marketing</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 technology integration.</t>
+          <t>Design, materials selection, manufacturing processes.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Acumen 6 features must be verifiable on all production lids and pass security audits.</t>
+          <t>Certification documentation received; product listed as Blue Angel compliant.</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1952,10 +1980,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1968,17 +2000,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Modify SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Mold 1 to 4 new keyed caps.</t>
+          <t>Printer must utilize at least 60% recycled content plastic in its construction, exceeding key competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ensures manufacturing capability for new components and bottle designs.</t>
+          <t>Differentiates HP on sustainability and supports marketing claims.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1988,17 +2020,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D, Supply Chain</t>
+          <t>Prod Steward, Marketing, BA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Existing line configuration, new component designs.</t>
+          <t>Supply chain, materials engineering.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SA14 and Orcus 5 lines operational with new components and pass production validation.</t>
+          <t>BOM and supplier documentation confirm 60% RCP; validated by internal audit.</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2006,10 +2038,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2022,17 +2058,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Design PHA and NOA-F to be customer replaceable, enhancing serviceability.</t>
+          <t>The printer must feature AI-powered solutions for optimizing print quality and scan accuracy, branded as Perfect Print and Perfect Scan.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces service costs.</t>
+          <t>Addresses top customer needs for quality and efficiency; supports key differentiator claims.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2042,17 +2078,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Marketing, GXD, R&amp;D Telemetry</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PHA and NOA-F design, service documentation.</t>
+          <t>AI model integration, firmware/software development.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F using provided instructions with &lt;5% error rate in usability tests.</t>
+          <t>Demonstrated improvement in print/scan quality in benchmark tests; feature accessible via UI/portal.</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2060,10 +2096,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2076,48 +2116,52 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal of 80,000 Pages</t>
+          <t>Maintenance Free or Less Maintenance Design</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Set new warranty page life goal for the printer at 80,000 pages.</t>
+          <t>Design the printer to be maintenance free or require less maintenance (i.e., fewer parts to replace over product lifetime).</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aligns with market expectations for durability and reduces TCO for customers.</t>
+          <t>Reduces burden on SMBs with limited technical resources and aligns with competitor differentiation.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Component reliability, maintenance schedule.</t>
+          <t>Component design, reliability engineering.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Printer must operate without critical failure for at least 80,000 pages in accelerated life testing.</t>
+          <t>Product requires fewer maintenance interventions than comparable models; validated by field test data.</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2130,48 +2174,52 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Product Reddington ID with Increased Tank Size</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID for product with increased tank size, while keeping Marconi-HI ADF unchanged.</t>
+          <t>The printer must include a warranty covering either 80,000 pages or 2 years, whichever comes first.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Supports higher ink capacity and page yield without redesigning ADF.</t>
+          <t>Provides assurance to SMB customers and supports reliability claims.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>Quality, Marketing, BA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tank redesign, Reddington ID integration.</t>
+          <t>Service policies, reliability engineering.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Product ID and tank design validated in pilot production; ADF remains unchanged.</t>
+          <t>Warranty terms published; support system configured to track both criteria.</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2184,48 +2232,52 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for the product.</t>
+          <t>Printer must support mobile printing via HP App and standard mobile platforms.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Improves product protection during shipping and handling.</t>
+          <t>Addresses evolving work patterns and customer expectations for mobility.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics, Quality</t>
+          <t>Marketing, GXD, BA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Packaging design, supply chain sourcing.</t>
+          <t>App development, firmware integration.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EPS foam packaging passes ISTA transit and drop tests.</t>
+          <t>Printer discoverable and usable from HP App and mobile OS print dialogs; passes connectivity and print tests from mobile devices.</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>Magellan MRD, Page 9</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2238,95 +2290,99 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for environmental standards (PDL SKU).</t>
+          <t>Printer must support telemetry data collection for fleet management, diagnostics, and usage analytics.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Compliance is necessary for market access and corporate sustainability goals.</t>
+          <t>Enables proactive support, device management, and product improvement.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>R&amp;D Telemetry, DVAR, BA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Design, materials, documentation.</t>
+          <t>Firmware, cloud integration, privacy compliance.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Product certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+          <t>Telemetry data is collected, securely transmitted, and accessible via management portal; passes privacy and compliance review.</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REQ-015</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with new tank protrusion and optimize size.</t>
+          <t>Develop NGB keyed ink bottles with 6,000-page yield for Black and CMY, with CMY bottle size supporting over 8,000 pages.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and maintains compact footprint.</t>
+          <t>Higher page yields reduce customer intervention and lower total cost of ownership, supporting competitive differentiation.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tank design, tray redesign.</t>
+          <t>Requires compatibility with existing and new printer platforms.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Trays function correctly with new tank in user tests and fit within defined product envelope.</t>
+          <t>Bottles must deliver at least 6,000 pages for Black and CMY, and CMY bottle size must exceed 8,000 pages as validated by ISO testing.</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2338,49 +2394,49 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REQ-016</t>
+          <t>REQ-002</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Spill-Free Reliability for Bottles</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Integrate a 4.3” CGD (Color Graphic Display) into the product.</t>
+          <t>Design ink bottles and system to ensure spill-free reliability during user handling and refilling.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Enhances user interface and usability.</t>
+          <t>Minimizes mess and waste, improving customer satisfaction and reducing service costs.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>UI design, display sourcing.</t>
+          <t>Depends on bottle design and printer ink tank interface.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Display is functional, clear, and passes user experience tests.</t>
+          <t>No ink spillage occurs during standard refill process in usability and reliability testing.</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2392,25 +2448,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REQ-017</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4-Tube Platform with New Routing and Integration</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes and develop new tube routing and integration for a 4-tube platform.</t>
+          <t>Implement NOA-F (Non-Original Accessory-Filter) with a metal foiled labyrinth and lid label, with no changes to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Supports increased ink flow and reliability with new tank design.</t>
+          <t>Enhances security, anti-counterfeit, and operational reliability.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2420,21 +2476,21 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Security, Service</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tube design, tank integration.</t>
+          <t>Requires integration with current NOA-F and push-push mechanisms.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>New routing and integration validated in reliability and flow tests.</t>
+          <t>NOA-F must pass security validation and function seamlessly with existing mechanisms.</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2446,49 +2502,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REQ-018</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Support for Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Update service station for improved aerosol management and adapt platform for tank changes.</t>
+          <t>Enable customer replacement of Print Head Assembly (PHA) and NOA-F parts to enhance serviceability.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reduces maintenance and improves print environment cleanliness.</t>
+          <t>Reduces downtime and service costs, improves user experience.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Service station design, tank integration.</t>
+          <t>Requires modular hardware design and user instructions.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aerosol levels remain within safety thresholds during operation.</t>
+          <t>Customers can replace PHA and NOA-F without tools, as verified by usability studies.</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2500,49 +2556,49 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REQ-019</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>New Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Design product to support a new warranty page life goal of 80,000 pages per device.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+          <t>Aligns with competitive benchmarks and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Manufacturing</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carriage design, tube routing, weight distribution.</t>
+          <t>Impacts parts durability and consumables yield.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Carriage operates reliably and meets print quality standards in system tests.</t>
+          <t>Device passes accelerated life tests simulating 80,000 printed pages without major failure.</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2554,49 +2610,49 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REQ-020</t>
+          <t>REQ-006</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paperpath Support for Increased Page Life</t>
+          <t>Size Optimization for Larger Tank</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Update paperpath design to support increased 80,000-page life goal.</t>
+          <t>Increase tank size to support higher ink capacity, with associated changes to input and output trays to accommodate tank protrusion.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ensures durability and reliability over extended use.</t>
+          <t>Supports higher page yield and reduces refill frequency.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paperpath materials, wear modeling.</t>
+          <t>Requires redesign of trays and enclosure.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Paperpath passes accelerated life testing for 80,000 pages without critical failure.</t>
+          <t>Printer footprint remains within specified dimensions while supporting larger tank and functional trays.</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2608,25 +2664,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REQ-021</t>
+          <t>REQ-007</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part (Post 80k Life)</t>
+          <t>4.3” CGD Touchscreen Interface</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80,000 pages.</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) touchscreen for improved user interface.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Extends product life and reduces total cost of ownership for customers.</t>
+          <t>Enhances usability and supports advanced features.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2636,21 +2692,21 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>End Users, UX/UI Team, Product Management</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maintenance part design, service documentation.</t>
+          <t>Requires updated firmware and hardware.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance part within standard service time.</t>
+          <t>All key functions accessible via the 4.3” touchscreen, validated by usability testing.</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2662,49 +2718,49 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REQ-022</t>
+          <t>REQ-008</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>140ml K Bottles and New CMY Bottle Sizes</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Introduce 140ml black bottles and new, larger CMY bottles for the ink system.</t>
+          <t>Implement aerosol management in the service station with platform changes due to larger tank.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Supports higher page yields and reduces refill frequency.</t>
+          <t>Prevents ink aerosol contamination and maintains print quality and reliability.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bottle design, tank compatibility.</t>
+          <t>Requires changes to service station design.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bottles validated for compatibility and yield in system tests.</t>
+          <t>Aerosol levels remain within acceptable limits during maintenance cycles.</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2716,25 +2772,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REQ-023</t>
+          <t>REQ-009</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection in IDS</t>
+          <t>Paper Path for Increased Page Life</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Develop new make-break and FI (fluidic interconnect) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Redesign paper path components to support increased page life target of 80,000 pages.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Improves reliability, prevents mis-filling, and supports larger tank sizes.</t>
+          <t>Ensures durability and reliability over the extended warranty period.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2744,21 +2800,21 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality</t>
+          <t>R&amp;D, Quality Assurance, Service</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IDS, LEBI ink-tank, SHAID integration.</t>
+          <t>Impacts material selection and mechanical design.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Connections pass reliability and mis-fill prevention tests.</t>
+          <t>Paper path components pass durability testing for 80,000 pages without failure.</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2770,45 +2826,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REQ-024</t>
+          <t>REQ-010</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Ink Maintenance as Serviceable Part Post-80k Life</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Implement new IDS startup algorithm and air management system.</t>
+          <t>Design ink maintenance components to be serviceable after 80,000-page life, available at service centers.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ensures reliable startup and air handling for new tank and bottle system.</t>
+          <t>Extends device life beyond warranty and reduces e-waste.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality</t>
+          <t>Service, End Users, Sustainability Team</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>IDS, tank, bottle integration.</t>
+          <t>Requires modular design and availability of service parts.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Startup and air management pass reliability and air ingress tests.</t>
+          <t>Service centers can replace ink maintenance parts post-warranty, as validated by service documentation.</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2824,25 +2880,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REQ-025</t>
+          <t>REQ-011</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>New IDS Make-break and FI Connection</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Develop new algorithms for servicing and startup to support new platform requirements.</t>
+          <t>Develop new IDS (Ink Delivery System) make-break and fluidic interconnect (FI) connection with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Improves reliability and user experience with new system components.</t>
+          <t>Supports new tank design and ensures secure, reliable ink delivery.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2852,21 +2908,21 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Firmware, IDS, tank integration.</t>
+          <t>Requires compatibility with new tank and bottle designs.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Algorithms validated in service and startup scenarios with &lt;2% failure rate.</t>
+          <t>IDS connections pass leak and connectivity tests for all supported configurations.</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2878,45 +2934,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>REQ-026</t>
+          <t>REQ-012</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definitions</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and depletion definitions to align with updated page yield targets.</t>
+          <t>Implement a new IDS startup algorithm and air management system for optimized priming and reliability.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ensures consistent output quality and accurate yield metrics.</t>
+          <t>Improves first-time setup experience and reduces startup failures.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Product Management</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PQ testing, depletion modeling.</t>
+          <t>Requires firmware and IDS hardware updates.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PQ and depletion metrics validated in lab and field tests.</t>
+          <t>Startup algorithm completes successfully in 99% of new device installations.</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -2932,49 +2988,49 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>REQ-027</t>
+          <t>REQ-013</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU hardware in the new platform.</t>
+          <t>Define and implement new print quality (PQ) goals and depletion metrics to align with page yield definition.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leverages proven hardware to reduce development cost and risk.</t>
+          <t>Ensures consistent output and aligns with marketing claims.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Marketing, Quality Assurance</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Compatibility with new platform design.</t>
+          <t>Requires test protocol updates.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Hardware passes system integration and functional validation.</t>
+          <t>Print quality and depletion meet or exceed defined metrics in 95% of test runs.</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2986,49 +3042,49 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>REQ-028</t>
+          <t>REQ-014</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for PDL SKU.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Provides modern connectivity options for users.</t>
+          <t>Supports environmental sustainability goals and required certifications for market access.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>End Users, Product Management, IT</t>
+          <t>Sustainability Team, Regulatory, Product Management</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Firmware, hardware interface design.</t>
+          <t>Requires documentation and design alignment to standards.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Wi-Fi module passes connectivity and performance tests.</t>
+          <t>Product passes third-party certification for EPEAT3, LOT4, and Blue Angel.</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3040,25 +3096,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>REQ-029</t>
+          <t>REQ-015</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dune Firmware Platform</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Utilize Dune firmware platform for the printer.</t>
+          <t>Use EPS foam for product packaging to improve protection during shipping.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ensures compatibility and leverages existing firmware capabilities.</t>
+          <t>Reduces damage during transit and supports logistics requirements.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3068,21 +3124,21 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Product Management</t>
+          <t>Logistics, R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Firmware integration, hardware compatibility.</t>
+          <t>Requires packaging design update.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Firmware passes system and feature validation tests.</t>
+          <t>Product passes drop and vibration tests with EPS foam packaging.</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3094,49 +3150,49 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REQ-030</t>
+          <t>REQ-016</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Support for SMB, Consumer, and Enterprise Services</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Provide solutions and business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker options.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Meets enterprise security requirements and protects user data.</t>
+          <t>Expands market reach and offers flexible service models.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IT, Security, Enterprise Customers</t>
+          <t>Business Development, Service, End Users</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hardware and firmware design, compliance standards.</t>
+          <t>Requires integration with HPX, HP One, SMB Portal, and ECP.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Security features pass penetration and compliance tests.</t>
+          <t>Service options are available and functional for all target segments at launch.</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -3148,45 +3204,45 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>REQ-031</t>
+          <t>REQ-017</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+          <t>Scan Solution and SMB Manageability</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Design solutions, services, and business models to address needs of consumer, SMB, and enterprise markets.</t>
+          <t>Integrate scan solution and SMB manageability features, including support for WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Expands addressable market and supports diverse customer requirements.</t>
+          <t>Meets needs of SMB and enterprise customers for device management and workflow integration.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Marketing</t>
+          <t>Enterprise IT, SMB Customers, Product Management</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Feature set, service offerings, pricing models.</t>
+          <t>Requires software and firmware integration.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Solutions and services available and validated for each segment at launch.</t>
+          <t>Device supports scan and management features as validated by functional testing.</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -3202,49 +3258,49 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REQ-032</t>
+          <t>REQ-018</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SMB Manageability and Enterprise Support</t>
+          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients and Drivers</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Include SMB manageability and enterprise support features such as WJA, HPSM, and JAM.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad deployment.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Meets IT requirements for business customers and enhances manageability.</t>
+          <t>Supports diverse customer IT environments and simplifies deployment.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SMB, Enterprise Customers, IT</t>
+          <t>IT Administrators, End Users, Product Management</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Software integration, feature development.</t>
+          <t>Requires driver and client software updates.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Manageability features functional and validated in enterprise test environments.</t>
+          <t>Device installs and operates with all listed clients and drivers in supported OS environments.</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3256,25 +3312,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>REQ-033</t>
+          <t>REQ-019</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients &amp; Drivers</t>
+          <t>Leverage Sayan Sibstar Tubes with New Routing</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Utilize Sayan Sibstar tubes for ink delivery, with new routing and integration for the 4-tube platform.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Supports wide range of deployment scenarios and user environments.</t>
+          <t>Improves ink delivery reliability and supports new tank design.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3284,21 +3340,21 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IT, End Users, Support</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Driver and client integration.</t>
+          <t>Requires mechanical and routing design updates.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>All clients and drivers pass compatibility and installation tests.</t>
+          <t>Ink delivery system operates without leaks or flow interruptions in all test scenarios.</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3310,53 +3366,53 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>REQ-034</t>
+          <t>REQ-020</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Protect Micro/SMB Segments and HP's Ink/Laser Profit Pool</t>
+          <t>Factory Configuration for NOA-F, Magi and Nessie Ink Cart, and Labelling Tool</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Design product features and pricing to protect HP's micro/SMB segments and profit pool from competitors.</t>
+          <t>Modify existing factory line SA14 for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provide mold for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strategic business objective to maintain market share and profitability.</t>
+          <t>Ensures efficient manufacturing and supports new product features.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Business Leadership, Product Management, Sales</t>
+          <t>Manufacturing, R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Feature set, pricing, market analysis.</t>
+          <t>Requires factory process updates and tooling investments.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Market share and profit pool metrics maintained or improved post-launch.</t>
+          <t>Factory lines are updated and validated for new production requirements before mass production.</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -3364,53 +3420,53 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REQ-035</t>
+          <t>REQ-021</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lead with LaserJet, Flank with PDL in Medium and Enterprise Segments</t>
+          <t>Support for SuperAmp PHA, Magi, and Nessie Pigment Inks</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Strategically position LaserJet as lead and PDL as flank in medium and enterprise segments to win over competitors like Epson as CISS grows.</t>
+          <t>Ensure product supports SuperAmp PHA, Magi, and Nessie pigment inks with new 140ml K bottles and new CMY bottles.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Supports HP's competitive positioning in the growing CISS market.</t>
+          <t>Maintains ink compatibility and supports high yield requirements.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>R&amp;D, Consumables Team, End Users</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Product positioning, marketing strategy.</t>
+          <t>Requires ink system and firmware compatibility.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Market share in medium/enterprise segments grows versus competitors.</t>
+          <t>Device operates reliably with all specified inks and bottle sizes.</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3418,25 +3474,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>REQ-036</t>
+          <t>REQ-022</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Grow Profitable CISS Share in New Segments</t>
+          <t>Reuse Marconi Hi PDL and Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Expand CISS offerings to new segments to grow HP's profitable market share.</t>
+          <t>Leverage existing Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU components for cost and time savings.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Increases revenue and market penetration.</t>
+          <t>Reduces development cost and time by reusing proven components.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3446,25 +3502,25 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Product Management, Business Leadership, Sales</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Feature development, market research.</t>
+          <t>Requires compatibility validation with new design.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CISS share in new segments increases post-launch.</t>
+          <t>All reused components pass functional and integration testing in new product.</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3472,25 +3528,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>REQ-037</t>
+          <t>REQ-023</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Highly Leverage Watt-LE Mech Platform and Marconi-Hi Product</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Leverage Watt-LE mechanical platform and Marconi-Hi product (Reddington ID) for new Magellan solution.</t>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Speeds development and reduces investment by reusing proven platforms.</t>
+          <t>Supports modern connectivity requirements for all customer segments.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3500,25 +3556,25 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Platform compatibility, feature integration.</t>
+          <t>Requires hardware and firmware integration.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Platform integration validated in system tests.</t>
+          <t>Device connects to Wi-Fi networks using Stingray module in all supported regions.</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3526,45 +3582,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>REQ-038</t>
+          <t>REQ-024</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
+          <t>Firmware (FW) Dune Platform</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and ink tanks into the new product platform.</t>
+          <t>Utilize Dune firmware platform for device operation and feature support.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Supports modern CISS features and improves product competitiveness.</t>
+          <t>Ensures consistent firmware experience and supports new hardware features.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Firmware Team, End Users</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Component integration, system design.</t>
+          <t>Requires firmware customization and validation.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>All components function as integrated system in validation tests.</t>
+          <t>Device operates reliably with Dune firmware and supports all required features.</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3572,7 +3628,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3580,25 +3636,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>REQ-039</t>
+          <t>REQ-025</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New NGB Keyed Ink Bottles</t>
+          <t>Gauss4.xx Security for Hardware and Firmware</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles for the platform.</t>
+          <t>Implement Gauss4.xx security features for both hardware and firmware.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Prevents mis-filling and supports new tank and IDS system.</t>
+          <t>Protects against unauthorized access and enhances device security posture.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3608,17 +3664,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Security Team, IT, Enterprise Customers</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bottle design, IDS, tank integration.</t>
+          <t>Requires security validation and integration.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Keyed bottles prevent mis-filling in &gt;99% test cases.</t>
+          <t>Device passes HP security certification for Gauss4.xx features.</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -3626,7 +3682,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -3634,25 +3690,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>REQ-040</t>
+          <t>REQ-026</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Schedule as Constrained Priority</t>
+          <t>Schedule Adherence (Q3'25-Q4'27)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Adhere to schedule as the least flexible business constraint for the program.</t>
+          <t>Meet program schedule with key checkpoints from Q3'25 to Q4'27 as detailed in project plan.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ensures timely market entry and supports business objectives.</t>
+          <t>Ensures timely market entry and aligns with business objectives.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3662,17 +3718,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Program Management, R&amp;D, Business Leadership</t>
+          <t>Program Management, R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>All development activities, resource allocation.</t>
+          <t>All development and validation activities must align to schedule.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>All key milestones met as per published schedule.</t>
+          <t>All program milestones are completed on or before scheduled dates.</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3680,7 +3736,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3688,25 +3744,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>REQ-041</t>
+          <t>REQ-027</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K as Constrained Priority</t>
+          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages as a constrained program requirement.</t>
+          <t>Design SuperAmp PHA to support a life of 65,000 pages as a fixed constraint.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Critical for warranty, reliability, and cost targets.</t>
+          <t>Sets a boundary for PHA durability and impacts service strategy.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3716,21 +3772,21 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Product Management</t>
+          <t>R&amp;D, Service, Product Management</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SuperAmp PHA design, reliability modeling.</t>
+          <t>Impacts warranty and service parts planning.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing for 65,000 pages with &lt;1% failure rate.</t>
+          <t>SuperAmp PHA passes durability tests for 65,000 pages in accelerated testing.</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3742,25 +3798,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>REQ-042</t>
+          <t>REQ-028</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years and 80,000 Pages as Optimized Priority</t>
+          <t>Warranty Life of 2 Years or Page Target</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Optimize for warranty life of 2 years and 80,000 pages.</t>
+          <t>Product warranty to cover 2 years or the specified page life, whichever comes first.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Meets customer expectations for durability and value.</t>
+          <t>Aligns with industry norms and customer expectations.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3770,21 +3826,21 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Component reliability, maintenance schedule.</t>
+          <t>Impacts reliability and service parts planning.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Product passes reliability testing for 2 years/80,000 pages without critical failure.</t>
+          <t>Warranty documentation clearly states coverage terms and is validated by legal and service teams.</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3796,53 +3852,53 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>REQ-043</t>
+          <t>REQ-029</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority</t>
+          <t>Throughput: 25/20 ppm (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Optimize for print throughput of 25/20 ppm (PDL: 25/19 ppm).</t>
+          <t>Printer must achieve a throughput of 25/20 pages per minute (ppm), with PDL variant achieving 25/19 ppm.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Competitive performance metric for target market.</t>
+          <t>Meets competitive benchmarks for speed.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>End Users, Product Management, R&amp;D</t>
+          <t>End Users, Product Management, Marketing</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Print engine, firmware, hardware.</t>
+          <t>Requires hardware and firmware optimization.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Printer achieves rated throughput in standard performance tests.</t>
+          <t>Device achieves specified throughput in ISO speed tests.</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3850,25 +3906,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>REQ-044</t>
+          <t>REQ-030</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serviceability (Maintenance Box) as Optimized Priority</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Optimize serviceability, focusing on maintenance box accessibility and replacement.</t>
+          <t>Ensure printer includes a serviceable maintenance box for ink waste and maintenance cycles.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Reduces service time and improves customer satisfaction.</t>
+          <t>Improves uptime and reduces service intervention frequency.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3878,21 +3934,21 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Service, End Users, R&amp;D</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation.</t>
+          <t>Requires modular design for easy replacement.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Maintenance box is replaceable within defined service time.</t>
+          <t>Maintenance box can be replaced by service personnel within 10 minutes as validated by service testing.</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3900,922 +3956,6 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>REQ-045</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>45</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>SMB Solution as Optimized Priority</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Optimize product features and solutions for SMB market needs.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Increases product adoption and satisfaction in SMB segment.</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SMB Customers, Product Management, Sales</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Feature set, solution integration.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>SMB features validated in customer pilots and feedback.</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>REQ-046</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>46</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>PaaS (Platform as a Service) as Optimized Priority</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Optimize for PaaS business model and schedule.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Enables new revenue streams and flexible deployment.</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Product Management, Business Leadership, IT</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Feature enablement, service integration.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>PaaS features operational and validated in pilot deployments.</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>REQ-047</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>47</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Host 12K-CMYK and Trade Page 6K as Flexible Priority</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Host 12,000-page CMYK and trade page 6,000 as flexible priorities for the program.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Provides flexibility for future product enhancements or market demands.</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Product Management, R&amp;D, Business Leadership</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Future development, market trends.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>12K-CMYK and 6K trade page features can be enabled as needed.</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>REQ-001</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AI Productivity and Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Integrate advanced AI-powered productivity and manageability solutions, including AI-driven print and scan workflows, to simplify business operations for SMB customers.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>SMBs require solutions that minimize manual intervention and streamline workflows, as they lack dedicated IT staff.</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Requires integration with SMB portal and device management systems.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Demonstrated deployment of AI-driven productivity features in print and scan workflows; user testing with SMBs shows &gt;80% satisfaction with workflow simplification.</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>REQ-002</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>2</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Deliver HP’s lowest business TCO through a combination of cost-efficient ink tank technology and minimal maintenance requirements.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Cost efficiency is a primary decision driver for SMBs with limited budgets.</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Marketing, DVAR, BA</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Dependent on ink tank system design and maintenance strategy.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Independent benchmark shows TCO at least 10% lower than previous HP SMB products and competitive offerings.</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>REQ-003</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>High Serviceability and Customer Replaceable Parts</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Design the printer for high serviceability with customer-replaceable key components (e.g., maintenance box, printhead assembly), and ensure service center support for non-customer-replaceable items.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Unmanaged SMBs lack IT support; easy maintenance reduces downtime and service costs.</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Requires modular hardware design and clear documentation.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>At least 80% of common maintenance tasks can be performed by end users; documentation and training materials provided.</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>REQ-004</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>4</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>SMB Portal for Device Management</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers, targeting office managers and generalist IT users in SMBs.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>SMBs need a simple, unified interface for managing fleets of printers without IT expertise.</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Requires integration with telemetry and device firmware.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Portal supports management of at least 10 devices per customer; user testing with SMBs shows &gt;80% usability rating.</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>REQ-005</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>5</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Keyed Ink Bottles for Error Prevention</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and reduce user errors.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Reduces service incidents and improves user experience for non-technical users.</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Supplies Quality, Quality, Prod Steward</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Requires new bottle and tank interface design.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Field testing shows &lt;2% incorrect refill incidents over 12 months of use.</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>REQ-006</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>6</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Support for PaaS and Advanced View SMB Portal</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Ensure printer supports Platform-as-a-Service (PaaS) and the new Advanced View SMB portal for enhanced business solutions.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Future-proofs the product and supports HP’s strategic move towards solutions and services.</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, BA, R&amp;D Telemetry</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Requires software and firmware compatibility with HP’s evolving platforms.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Printer is certified compatible with PaaS and Advanced View SMB portal at launch.</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>REQ-007</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>7</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>PDL/PS Support and Improved Print Speed</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>For PDL SKU, provide PDL/PS (Page Description Language/PostScript) support and improve print speed to 25/20 ppm (from current 25/19).</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Addresses needs of higher-end SMBs requiring advanced print job compatibility and higher throughput.</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, Marketing, DVAR</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Requires hardware and firmware enhancements.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>PDL SKU demonstrates print speed of at least 25/20 ppm and passes PDL/PS compatibility tests.</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>REQ-008</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>8</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Blue Angel Environmental Certification</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Obtain Blue Angel certification for the printer to meet environmental and sustainability standards.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Supports HP’s sustainability goals and competitive positioning in environmentally conscious markets.</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Prod Steward, Tech Reg, Quality</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Requires compliance with Blue Angel criteria.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Blue Angel certification awarded by launch date.</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>REQ-009</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>9</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>High Recycled Content in Plastics (60% RCP)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Ensure that at least 60% of the printer’s plastics are made from recycled content, exceeding key competitors.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Differentiates HP on sustainability and meets growing customer demand for eco-friendly products.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Prod Steward, Marketing, Quality</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Requires supply chain and materials engineering alignment.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Bill of materials and third-party audit confirm ≥60% RCP in plastics.</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>REQ-010</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>10</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AI Solutions for Print, Scan, and Support</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Deploy AI-driven solutions in print, scan, and support functions to optimize workflows and reduce manual intervention.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AI-driven automation is a key differentiator for SMBs seeking efficiency and minimal IT burden.</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, GXD, Marketing, BA</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Requires integration with device firmware and cloud services.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>AI features are operational at launch and reduce manual steps by at least 30% in key workflows.</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>REQ-011</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>11</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Mobile Printing via HP App</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing capabilities through the HP App for SMB users.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Supports modern, flexible work environments and BYOD trends in SMBs.</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, BA</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Requires app integration and device firmware support.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Printer is discoverable and usable via HP App for all supported mobile OS at launch.</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>REQ-012</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>12</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Warranty and Serviceability Thresholds</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Provide a warranty of 80,000 pages or 2 years (whichever comes first) and establish serviceability thresholds for key components.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Ensures predictable support costs and aligns with SMB expectations for reliability.</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Quality, Supplies Quality, Prod Steward, Tech Reg</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Requires warranty policy alignment and service documentation.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Warranty terms published and service processes validated before launch.</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>REQ-013</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>13</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Maintenance-Free or Low Maintenance Design</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Design the printer to be maintenance-free or require minimal maintenance, with fewer parts to replace over product life.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Reduces total cost of ownership and appeals to SMBs lacking technical staff.</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Quality, Supplies Quality, Prod Steward, Marketing</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Subject to feasibility investigation and hardware design constraints.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Maintenance requirements are at least 30% lower than comparable products; validated by field testing.</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>The Out-of-Box Experience (OOBE) for 123.hp.com must present only one consistent product name/reference for the HP OfficeJet Pro 9010 series, to minimize user confusion and errors.</t>
+          <t>The customer should see only one consistent product name/reference for the HP OfficeJet Pro 9010 series on 123.hp.com to prevent user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>The printer must reliably print on all new and current Electromagnetic (EM) and market segment-specific media types, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
+          <t>The printer must operate reliably and meet intervention specifications for all new and current EM (Evaluation Media) and market segment media types under various climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The printer must operate without hardware failure when placed on uneven surfaces such as sofas, table cloths, or carpets, specifically ensuring the input tray sensor flag does not break.</t>
+          <t>The printer must function correctly and without hardware failures (e.g., input tray sensor flag) when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>The printer must be assessed for functional failure when tilted 20 degrees left and right during printing, to determine if it meets customer requirements.</t>
+          <t>Assess whether the printer experiences any functional failures when tilted 20 degrees left or right during printing, as per CISS product evaluation protocol.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The printer must maintain print quality and operate reliably when placed on a moving trolley during printing.</t>
+          <t>The printer must maintain print quality and function correctly when printing while placed on a trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,16 +1344,6 @@
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Requirement ID</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Verification_Status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1402,8 +1392,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1452,8 +1440,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1502,8 +1488,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1552,8 +1536,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1602,8 +1584,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1652,8 +1632,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1702,8 +1680,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1752,8 +1728,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1802,8 +1776,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1852,8 +1824,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,8 +1872,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1952,8 +1920,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,8 +1968,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2052,8 +2016,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2102,8 +2064,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2152,8 +2112,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2202,8 +2160,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2252,8 +2208,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2302,8 +2256,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2352,8 +2304,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2402,8 +2352,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2452,8 +2400,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2502,8 +2448,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2552,8 +2496,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2602,8 +2544,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2652,8 +2592,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2702,8 +2640,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2752,8 +2688,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2802,8 +2736,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2852,8 +2784,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2902,8 +2832,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2952,8 +2880,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3002,8 +2928,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3052,8 +2976,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3102,8 +3024,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3152,8 +3072,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3202,8 +3120,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3252,8 +3168,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3302,8 +3216,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3352,8 +3264,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3402,8 +3312,6 @@
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3411,17 +3319,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Business Ink Tank Printing Solution</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Implement advanced AI-driven productivity features and manageability solutions, including AI-assisted print, scan, and support workflows, to simplify business operations for SMB customers.</t>
+          <t>Develop HP's first business ink tank printer targeting unmanaged/lightly managed SMBs, designed for 5-250 employees, 6-15 printers per business, and AMPV ~500 pages. The printer must deliver high ROI, efficiency, and require minimal IT intervention.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Addresses the need for increased efficiency and ease of management for SMBs with limited IT resources. Differentiates HP Magellan from competitors.</t>
+          <t>Addresses a new, untapped SMB segment with cost-effective, low-intervention printing, filling a portfolio gap (CISS PLE Hi).</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3431,17 +3339,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solution stack.</t>
+          <t>Requires support for tank technology, CISS PLE Hi segment, and SMB-specific manageability features.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>AI-driven features are available at launch, demonstrably improve workflow efficiency, and are accessible via the SMB portal.</t>
+          <t>A business ink tank printer is launched with features and performance aligned to the SMB target group (5-250 employees, 6-15 printers, AMPV ~500), and can be used without dedicated IT support.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3449,17 +3357,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>REQ-001</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4, 5, 6, 7</t>
         </is>
       </c>
     </row>
@@ -3469,17 +3367,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver HP's lowest business TCO for SMB customers, minimizing intervention and ongoing costs over the product lifecycle.</t>
+          <t>Integrate advanced AI-powered productivity, scan workflow, and printer manageability solutions, including Perfect Print and Perfect Scan, to make business operations easier for SMBs.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top priority for SMBs and a key differentiator in the market.</t>
+          <t>SMBs need easy-to-use, intelligent solutions to maximize productivity and reduce manual intervention.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3489,17 +3387,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marketing, BA, Prod Steward</t>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires sustainable components and efficient consumables management.</t>
+          <t>Requires AI software integration and compatibility with hardware and SMB portal.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>TCO is calculated and benchmarked to be lower than previous HP models and key competitors.</t>
+          <t>AI features such as Perfect Print and Perfect Scan are available, functional, and demonstrably improve workflow efficiency in SMB environments.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3507,17 +3405,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>REQ-002</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -3527,17 +3415,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>SMB Device Management Portal</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be serviced by the customer, reducing the need for technician intervention and downtime.</t>
+          <t>Develop a consolidated portal (SMB portal) for managing multiple printers, tailored for office managers and generalist IT users in SMBs.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Addresses new SMB segment needs and pain points related to serviceability and maintenance costs.</t>
+          <t>SMBs lack dedicated IT; a user-friendly portal is essential for efficient multi-device management.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3547,35 +3435,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, DVAR, Tech Reg</t>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Design must ensure ease of replacement and clear instructions for end-users.</t>
+          <t>Requires portal software development and integration with printer firmware and AI features.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by an end-user without technical assistance; validated via usability testing.</t>
+          <t>Portal is live, supports management of 6-15 printers, and is usable by non-IT trained staff (office managers/generalists).</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>REQ-003</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 7, 10, 11</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3463,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal specifically for SMBs to manage all Magellan printers, including device status, usage analytics, and support access.</t>
+          <t>Ensure Magellan has HP's lowest business TCO among SMB tank printers, through efficient ink usage, minimal maintenance, and sustainable design.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT staff and require simple, centralized management tools.</t>
+          <t>TCO is a key purchase driver for SMBs seeking ROI and efficiency.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3605,35 +3483,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA</t>
+          <t>Marketing, Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Integration with AI solutions and Magellan device firmware.</t>
+          <t>Requires efficient ink tank design, low maintenance, and sustainability features.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Portal is live at launch, supports all required management functions, and is accessible to SMB users.</t>
+          <t>Independent testing confirms Magellan's TCO is lowest among HP business tank printers for SMB use cases.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>REQ-004</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -3643,17 +3511,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Consumables</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Utilize keyed bottles for ink and other consumables to prevent incorrect refilling and ensure compatibility with Magellan devices.</t>
+          <t>Design the maintenance box to be customer-replaceable, with a target for replacement outside warranty at service centers if necessary.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Reduces consumable errors, minimizes service calls, and ensures product reliability.</t>
+          <t>Minimizes downtime and service costs for SMBs with limited IT resources.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3663,17 +3531,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Supplies Quality, Quality, DVAR</t>
+          <t>Quality, Supplies Quality, DVAR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Requires redesign of consumable packaging and printer interface.</t>
+          <t>Requires hardware design supporting easy maintenance box replacement.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Keyed bottles are available at launch and are not interchangeable with previous models.</t>
+          <t>Maintenance box can be replaced by end users without HP technician intervention, as validated by usability testing.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3681,17 +3549,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>REQ-005</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4</t>
         </is>
       </c>
     </row>
@@ -3701,55 +3559,45 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Warranty and Serviceability Standards</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Provide a warranty of 80,000 pages or 2 years (whichever is first). Support customer-replaceable parts (PHA) and service center replaceable parts (MINK), with a target for more parts to be customer replaceable.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure proper maintenance of the ink tank system.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Reduces downtime and increases customer satisfaction for SMBs with minimal IT support.</t>
+          <t>Reduces user error and maintenance issues, improving reliability for SMBs.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, DVAR, Tech Reg, Prod Steward</t>
+          <t>Quality, Supplies Quality, Prod Steward</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Design for serviceability and robust part supply chain.</t>
+          <t>Requires supply chain and hardware compatibility with keyed bottles.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Warranty terms are met and documented; at least 80% of identified serviceable parts are customer replaceable.</t>
+          <t>Ink bottles are keyed and only fit the correct tanks, as confirmed by hardware validation.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>REQ-006</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4</t>
         </is>
       </c>
     </row>
@@ -3759,55 +3607,45 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Support for PaaS and Non-PDL/PDL SKUs</t>
+          <t>Non-PDL SKU Features</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ensure Magellan supports Platform-as-a-Service (PaaS) models and both Non-PDL and PDL SKUs, with specific speed and protocol support (PDL SKU: 25/20 ppm, PDL/PS support, Blue Angel compliance).</t>
+          <t>For the Non-PDL SKU, include support for SMB2.0 Solutions, Advanced View SMB portal, and PaaS (Printing as a Service).</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Addresses diverse SMB needs and aligns with HP's strategic intent to expand service-based offerings.</t>
+          <t>Addresses different SMB needs and supports new service models.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, Tech Reg</t>
+          <t>Marketing, GXD, BA, DVAR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Firmware and hardware compatibility, compliance with Blue Angel and other standards.</t>
+          <t>Requires software and hardware support for these features.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Both SKU types available at launch, meet specified speed and compliance requirements.</t>
+          <t>Non-PDL SKU is available with SMB2.0 Solutions, Advanced View, and PaaS integration.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>REQ-007</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4</t>
         </is>
       </c>
     </row>
@@ -3817,55 +3655,45 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>PDL SKU Features</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manufacture Magellan with at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%, Canon TBC).</t>
+          <t>For the PDL SKU, deliver improved print speeds (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and aligns with HP's environmental goals.</t>
+          <t>Targets higher-end SMBs needing advanced printing and regulatory compliance.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, BA</t>
+          <t>Marketing, Tech Reg, BA, DVAR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Supply chain and material sourcing for RCP.</t>
+          <t>Requires hardware/firmware for speed and PDL/PS, and Blue Angel certification process.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Product BOM and external certification confirm at least 60% RCP.</t>
+          <t>PDL SKU achieves 25/20 ppm, supports PDL/PS, and is Blue Angel certified.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>REQ-008</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 4</t>
         </is>
       </c>
     </row>
@@ -3875,17 +3703,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Advanced Telemetry Requirements</t>
+          <t>Sustainability: 60% RCP Content</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Integrate telemetry features to monitor device health, usage, and proactively support SMB customers through the portal and AI solutions.</t>
+          <t>Ensure the printer is built with at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Enables predictive maintenance, reduces downtime, and provides valuable insights for SMBs and HP support teams.</t>
+          <t>Sustainability is a key differentiator and market demand for SMBs.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3895,17 +3723,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, GXD, BA</t>
+          <t>Prod Steward, Marketing, Quality</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Integration with SMB portal and AI stack.</t>
+          <t>Requires sourcing and manufacturing with high RCP.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Telemetry data is available in real-time via the portal and supports proactive support interventions.</t>
+          <t>Printer is independently verified to use at least 60% RCP in its construction.</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3913,17 +3741,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>REQ-009</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Approved</t>
+          <t>Magellan MRD, page 11</t>
         </is>
       </c>
     </row>
@@ -3933,55 +3751,189 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Warranty and Serviceability</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing capabilities through the HP App, supporting key SMB use cases for on-the-go printing and management.</t>
+          <t>Provide a warranty of 80k pages or 2 years (whichever comes first), with serviceability features: PHA (customer replaceable) and MINK (service center, if out of warranty).</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Addresses modern SMB needs for flexibility and remote work support.</t>
+          <t>Ensures reliability and reduces SMB downtime.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Requires hardware/service design for warranty and customer replaceability.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Warranty and serviceability model is implemented and documented; validated by service/support teams.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Implement telemetry features to collect usage, performance, and error data for remote diagnostics and product improvement.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Supports proactive support, quality improvements, and future product enhancements.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, BA</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>App integration with Magellan firmware and SMB portal.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Mobile printing is available, reliable, and user-friendly at launch.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Requires secure telemetry software and privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Telemetry is active, securely transmits key metrics, and is accessible to HP support/engineering teams.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
         <v>0.85</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, Page 10</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>REQ-010</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Approved</t>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, page 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Support mobile printing and seamless integration with the HP App for print, scan, and device management.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Mobile workflows are increasingly important for SMBs.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Requires app and firmware compatibility.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Users can print/scan/manage devices via the HP App on iOS/Android.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, page 9, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>13</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Solutions/Services Monetization</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Enable monetization of AI and management solutions/services as part of the Magellan offering over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Supports HP's business goal for sustainable revenue growth via services.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Requires business model and technical enablement for solution monetization.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Solutions/services are available for purchase or subscription, with revenue tracking in place.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan MRD, page 9, 10</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,160 +430,160 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -1294,52 +1306,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,165 +418,165 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Additional_Comments</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -1336,52 +1324,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,35 +548,55 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>Additional_Comments</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Additional_Comments</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -710,27 +730,47 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Minimize the number of printer reference names shown to customers on 123.hp.com for HP OfficeJet Pro 9010 series to a single, consistent name to avoid user confusion.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>The out-of-box experience (OOBE) on 123.hp.com must present only one product name/reference to customers for the HP OJP 9010 series, to reduce user confusion and errors.</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Is there a reason to have 3 names for the same reference? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Having too many names isn't efficient and can induce user errors. Threshold: two names/reference are proposed, currently 4 references for Office Jet Pro 9010. Goal: Only one name/reference is proposed to customer. Priority: MUST. Lead Function: Solution. Lead: Chris. Status: Grey. Remarks: Quality team is following-up with Tais Bellini. 20210702 (Chris/Jess) Not possible to change in 123.hp.com as it references Product Master List shared with PC group. Only possible at support.hp.com. Proposed to Drop.</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -849,27 +889,47 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Printer must reliably print on all current and new evaluation media (EM) and market segment media, meeting regional print quality and intervention specifications for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>The printer must reliably operate and meet minimum print quality (PQ) and intervention specifications for all new and current EM (Evaluation Media) and market segment media under all relevant climatic conditions for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform. Threshold: Minimum PQ acceptable by region. Goal: Pass intervention rate and NO PQ issue. Priority: MUST. Lead Function: ME Platform. Lead: Sau Pin. Status: Green. Remarks: 20220920(Sau Pin): LP2 Life test are meeting Intervention rate(Qual). 20220316 (Sau Pin): Baseline assumed same as Manhattan. Status as 'Yellow' as need to review intervention performance. Accept threshold. EM media as Eval media.</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,27 +1048,47 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Printer must operate without input tray sensor flag breakage or functional failure when placed on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>The product must operate reliably and without damage to components (such as the input tray sensor flag) when placed on uneven surfaces including sofas, table cloths, and carpets.</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>As the complaint on Vasari, input tray sensor flag broken when printer is placed on uneven surface, this issue should be fixed in new product. Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead Function: ME Platform. Lead: Sau Pin. Status: Green. Remarks: 20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. Only Malbec Hi had issue with input tray flag broken. Need TME input on field data for 3M. Aiqiang: Manhattan field data shows tray 'fang' broken. ME will look at solutions to solve fang broken issue such as to strengthen the fang.</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,27 +1216,47 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Assess printer functionality and ensure no failures occur when the printer is tilted 20 degrees left or right during printing.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>The printer should be evaluated for functional failures when tilted 20 degrees left or right during printing, as per CISS product test procedures.</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing. (Sayan tilt left and right each at 20 degree while printing). Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead Function: ME Platform. Lead: Sau Pin. Status: Grey. Remarks: tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1287,27 +1387,47 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Printer must maintain print quality and function correctly when printing while placed on a moving trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>The printer must maintain print quality with no functional issues when printing while placed on a trolley.</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley. Threshold: Meet customer requirement. Goal: Meet customer requirement. Priority: MUST. Lead Function: ME Platform. Lead: Sau Pin. Status: Green. Remarks: (Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going. Interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.20220315</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1320,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1386,12 +1506,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity, scanning workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs.</t>
+          <t>Integrate advanced AI-powered productivity features, scan workflow automation, and manageability solutions into the Magellan printer to simplify business operations for SMBs.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI-powered features will enhance productivity and streamline workflows.</t>
+          <t>To deliver breakthrough productivity and ease of management, differentiating HP from competitors and addressing SMB customer needs for efficiency.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1406,12 +1526,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solutions platform.</t>
+          <t>Requires AI software integration and SMB portal support.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI features are available and functional in production units; user testing confirms ease-of-use and workflow improvement.</t>
+          <t>AI-powered productivity, scan, and management features are available and verifiable in the product UI; features function as documented and pass UAT.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1429,17 +1549,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowest Business TCO with Minimal Intervention</t>
+          <t>Lowest Business TCO (Total Cost of Ownership)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design the Magellan printer to achieve HP’s lowest total cost of ownership (TCO) for business customers, with minimal user intervention required for maintenance.</t>
+          <t>Design Magellan to deliver the lowest total cost of ownership for SMBs among HP business printers, including minimal intervention and optimized consumables.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cost efficiency and reduced maintenance are top needs for SMBs and key differentiators against competitors.</t>
+          <t>To attract cost-conscious SMBs and compete effectively in the CISS PLE Hi segment.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1449,25 +1569,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires durable design, high-yield consumables, and reliable components.</t>
+          <t>Requires optimized hardware, ink tank design, and efficient consumables.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TCO is demonstrably lower than comparable HP and competitor models in independent testing; maintenance intervals are extended.</t>
+          <t>TCO calculations demonstrate lower ownership costs than previous HP models and key competitors in third-party benchmarks.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
@@ -1477,17 +1597,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Business Ink Tank Printer for SMBs</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Develop and launch HP’s first business-class ink tank printer (CISS) targeting unmanaged/lightly managed SMBs.</t>
+          <t>Introduce a replaceable maintenance box that customers can easily swap without technical support, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Addresses a new market segment and closes a gap in HP’s CISS PLE Hi offering.</t>
+          <t>Addresses new SMB customer segment needs and reduces reliance on service centers, increasing customer satisfaction.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1497,25 +1617,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Requires new hardware platform; alignment with HP’s existing product portfolio.</t>
+          <t>Design must ensure ease of replacement and minimal risk of error.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Product is launched as HP’s first business ink tank printer; marketing materials and technical documentation reflect this positioning.</t>
+          <t>Customer can replace maintenance box within 5 minutes using only supplied instructions; no tools required; validated in usability testing.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 6, 7, 12</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -1525,17 +1645,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Implement a user-replaceable maintenance box to reduce downtime and service costs for SMB customers.</t>
+          <t>Utilize uniquely keyed ink bottles to prevent incorrect refilling and ensure compatibility, reducing user error and warranty claims.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SMBs need simple, low-maintenance solutions due to lack of IT support. This is a new feature for this segment.</t>
+          <t>Improves user experience and reduces support costs due to incorrect ink usage.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1545,21 +1665,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires redesign of maintenance subsystem; must be customer-replaceable.</t>
+          <t>Requires new bottle design and printer detection mechanism.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>End users can replace the maintenance box without service calls; successful completion of usability testing.</t>
+          <t>Ink bottles are physically keyed and only compatible with intended slots; verified in QA and field tests.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1573,45 +1693,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Customer Replaceable Parts (PHA) and Serviceability (MINK)</t>
+          <t>SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Design key printer components to be customer-replaceable (PHA) and ensure MINK parts are serviceable at authorized centers, with a target for most to be customer-replaceable even out of warranty.</t>
+          <t>Develop a consolidated SMB portal for managing multiple printers, targeting unmanaged or lightly managed SMBs without dedicated IT staff.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and aligns with SMBs’ need for minimal IT intervention.</t>
+          <t>Enables easy fleet management for SMBs, a key differentiator for Magellan.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires modular design and documentation; warranty process alignment.</t>
+          <t>Requires backend infrastructure and secure authentication.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Documented list of customer-replaceable parts; verified by service and user testing.</t>
+          <t>Portal is accessible, supports management of at least 15 printers, and passes security and usability tests.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
@@ -1621,45 +1741,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>PaaS (Platform as a Service) Support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure reliability.</t>
+          <t>Ensure Magellan is compatible with HP's PaaS offerings, enabling subscription-based services and remote management features.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prevents user errors, reduces support calls, and ensures product reliability for SMBs.</t>
+          <t>Supports HP's business model shift and customer demand for flexible, scalable solutions.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>['Marketing', 'DVAR', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires new bottle design and supply chain adjustments.</t>
+          <t>Integration with HP PaaS infrastructure.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>All ink bottles are keyed and only fit correct tanks; tested in production units.</t>
+          <t>Magellan can be provisioned, managed, and monitored via HP PaaS platform; validated in integration testing.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
     </row>
@@ -1669,41 +1789,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>PDL/PS Support for PDL SKU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first) for the Magellan printer.</t>
+          <t>Provide full PDL (Page Description Language) and PostScript support for the PDL SKU, with print speeds of 25/20 ppm (improvement over current 25/19).</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Addresses SMBs’ need for reliability and cost predictability.</t>
+          <t>Enables compatibility with business printing workflows and differentiates Magellan in the SMB segment.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing']</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires reliability testing and warranty program setup.</t>
+          <t>Firmware and driver development for PDL/PS support.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Warranty terms are included in all sales materials and honored in support systems.</t>
+          <t>PDL SKU achieves 25/20 ppm in standardized print tests; PDL/PS compatibility validated with common business software.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1717,45 +1837,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Develop a non-PDL SKU that includes SMB2.0 Solutions and an Advanced View SMB Portal for device management.</t>
+          <t>Achieve Blue Angel environmental certification for the PDL SKU, demonstrating commitment to sustainability and eco-friendly design.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Addresses SMBs’ need for easy device management and modern workflows.</t>
+          <t>Meets regulatory requirements and enhances appeal to environmentally conscious SMBs.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg', 'Quality']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires portal and solution development; integration with printer firmware.</t>
+          <t>Design and materials must meet Blue Angel criteria.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Non-PDL SKU is available with full portal and solutions functionality.</t>
+          <t>Certification is obtained and documented prior to launch.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -1765,41 +1885,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PDL SKU: Speed and Protocol Support</t>
+          <t>80k/2 Year Warranty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop a PDL SKU with improved print speed (25/20 ppm), PDL/PS support, and Blue Angel certification.</t>
+          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Meets advanced customer needs and regulatory requirements for certain SMBs.</t>
+          <t>Provides peace of mind for SMB customers and aligns with market expectations.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+          <t>['Quality', 'Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware enhancements; certification processes.</t>
+          <t>Requires reliability testing and service planning.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PDL SKU achieves target speed, protocol support, and Blue Angel certification.</t>
+          <t>Warranty terms are published and supported; warranty claims tracked for compliance.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1813,45 +1933,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sustainability: 60% RCP Content</t>
+          <t>Serviceability: PHA and MINK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ensure that the Magellan printer is manufactured with at least 60% recycled content plastic (RCP), surpassing key competitors.</t>
+          <t>Enable customer-replaceable PHA components and MINK at service centers, with a target of making MINK customer-replaceable if out of warranty.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products; differentiates HP.</t>
+          <t>Reduces downtime and service costs, improving SMB satisfaction and lowering HP support burden.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing', 'Tech Reg']</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Requires sourcing and supply chain alignment.</t>
+          <t>Component design for easy replacement; documentation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BOM and manufacturing process confirm 60% RCP; verified by sustainability audit.</t>
+          <t>PHA and MINK can be replaced per service guide; validated in field trials.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -1861,17 +1981,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal for Manageability</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Provide a unified portal for SMBs to manage their fleet of printers, including device status, configuration, and support features.</t>
+          <t>Integrate advanced AI algorithms for print and scan quality enhancement, ensuring optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT and need simple, consolidated tools for device management.</t>
+          <t>Delivers superior print/scan quality and differentiates Magellan from competitors.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1881,17 +2001,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['GXD', 'BA', 'Marketing']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'Marketing']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires portal development and integration with device firmware.</t>
+          <t>Requires AI software integration and hardware compatibility.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Portal is accessible, functional, and supports all key management features in user acceptance testing.</t>
+          <t>AI features demonstrably improve print/scan quality in benchmark tests; user satisfaction &gt;90% in surveys.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1899,7 +2019,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
@@ -1909,17 +2029,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AI Solutions: Print, Scan, Support</t>
+          <t>Sustainability: 60% RCP Content</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Integrate AI-driven features for print optimization, scanning workflow, and support automation.</t>
+          <t>Ensure Magellan is manufactured with at least 60% recycled content plastic (RCP), exceeding competitor benchmarks (Epson 30%).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AI solutions improve efficiency and reduce manual errors, directly addressing SMB pain points.</t>
+          <t>Appeals to environmentally conscious customers and aligns with HP sustainability goals.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1929,17 +2049,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'GXD', 'BA']</t>
+          <t>['Prod Steward', 'Quality', 'Marketing']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires AI platform integration and validation.</t>
+          <t>Supply chain and manufacturing process updates.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>AI features are functional and validated in real-world SMB environments.</t>
+          <t>Product Bill of Materials demonstrates 60% RCP; verified by third-party audit.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1947,7 +2067,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
@@ -1957,45 +2077,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Platform Support for PaaS</t>
+          <t>Mobile Printing via HP App</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ensure Magellan supports Platform-as-a-Service (PaaS) business models, including remote management and service subscriptions.</t>
+          <t>Support mobile printing workflows through the HP App, enabling users to print from smartphones and tablets.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Enables recurring revenue streams and modern service offerings for SMBs.</t>
+          <t>Addresses modern SMB mobility needs and enhances user convenience.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>['GXD', 'Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires software and service integration.</t>
+          <t>App integration and cross-platform compatibility.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PaaS features are available and operational in production units.</t>
+          <t>Users can print from iOS and Android HP Apps; feature passes cross-device testing.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
     </row>
@@ -2005,45 +2125,1725 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Advanced Telemetry Requirements</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
+          <t>Implement telemetry features for remote diagnostics, usage tracking, and predictive maintenance, aligned with HP enterprise standards.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mobile printing is a top use case for SMBs and a competitive necessity.</t>
+          <t>Enables proactive support, reduces downtime, and supports PaaS business model.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality', 'Tech Reg', 'BA']</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Backend infrastructure and secure data handling.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Telemetry data is available in the SMB portal and HP support tools; GDPR compliance verified.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Page Yield</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield; CMY bottle size must support &gt;8K pages.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>To increase ink capacity and reduce customer intervention, supporting higher print volumes and competitive positioning.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>['GXD', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Requires app integration and testing with Magellan firmware.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Mobile printing is fully supported and validated on iOS and Android devices.</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ink formulation compatibility, bottle manufacturing updates</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Bottles must be able to deliver at least 6,000 pages (Black/CMY) and &gt;8,000 pages (CMY) as validated by standardized yield tests.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ensure the new ink bottles and tank system deliver spill-free reliability during user refill and maintenance operations.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Improves user experience and minimizes mess/errors, reducing support costs and customer complaints.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>End Users, Customer Support</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bottle and tank design, IDS integration</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Less than 1% of user refill events result in ink spills, as measured in field trials and lab tests.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.9</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, 10</t>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Integrate NOA-F (Non-OEM Accessory-Filter) with a metal foiled labyrinth and lid label. No changes to click-on push-push and TDF mechanisms.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enhances security, reliability, and differentiation from competitors while maintaining user familiarity.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Security, End Users</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NOA-F supply chain, mechanical design constraints</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NOA-F units must pass reliability and security tests with the new labyrinth and label, and be compatible with existing mechanisms.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Leverage existing SuperAmp Si PHA hardware and Magi/Nessie pigment ink without reformulation.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Reduces R&amp;D cost, accelerates time-to-market, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Engineering, Product Management, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Compatibility of new system with legacy components</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>100% compatibility of reused components in prototype and pilot production builds.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ink System Reliability and Characterization</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Model and characterize reliability, water vapor transmission rate (WVTR), air gain, flow rate, and IDS including startup and NOA-F end-of-life.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ensures consistent print quality and system reliability over product lifecycle.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>IDS development, system integration</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Validated models and test data for all key reliability metrics before design freeze.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ink Stability Modeling and PQ Impact Analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Model ink stability in the tank and analyze its impact on print quality (PQ).</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Maintains high print quality and reduces risk of ink degradation over time.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Access to ink chemistry data, tank design</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Documented ink stability model and PQ impact report reviewed and approved by R&amp;D.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NOA-F as Service Parts in Warranty Support</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NOA-F must be available as service parts for warranty support and field replacements.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ensures serviceability and customer satisfaction during warranty period.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Service, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Service supply chain, inventory planning</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NOA-F service parts available in service centers within 3 months of product launch.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Acumen 6 on Lid</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Integrate Acumen 6 technology onto the ink bottle lid for authentication or tracking.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Improves anti-counterfeiting and supply chain traceability.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Product Security, Supply Chain</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lid design, Acumen 6 system integration</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Acumen 6 feature fully functional and passes security validation tests.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Modify Factory Line for NOA-F and New Bottles</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Modify SA14 production line for NOA-F assembly; add Magi ink cart and labeling tool in Orcus 5. Mold for 1-4 new keyed caps required.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Supports manufacturing of new consumables and assemblies.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Manufacturing, Operations</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Factory retooling schedules, cap design finalization</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Factory lines operational and producing new components at required yield rates before launch.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Design the system to allow customers to easily replace PHA (Printhead Assembly) and NOA-F without professional service.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Improves user experience and reduces service costs.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>End Users, Service</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Design for serviceability, user documentation</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Replacement process can be performed by end users in under 5 minutes with no tools, as validated in usability studies.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>New Warranty Page Life Goal: 80K Pages</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Extends product life and supports higher duty cycle use-cases, competitive advantage.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, Service</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Component durability, consumable yield, warranty policy</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Printer must reliably print 80,000 pages without major failure, as verified in accelerated life testing.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Reddington ID with Increased Tank Size</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Adopt Reddington ID with a size increase for the ink tank. No change to Marconi-HI ADF (Automatic Document Feeder).</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and aligns with existing industrial design.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Industrial Design, Product Management</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tank design, chassis compatibility</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>New tank design integrated into Reddington ID and passes mechanical and aesthetic validation.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Utilize EPS foam packaging for the printer and consumables.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Protects product during shipping and handling.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Logistics, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Packaging design, material sourcing</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Products pass drop and vibration tests with EPS packaging.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ensure compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Meets regulatory and market requirements for sustainability and eco-labels.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Regulatory, Product Management</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Design and material choices, certification processes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves EPEAT3, LOT4, and Blue Angel certifications before launch.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Modifications for Tank Protrusion</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Modify input and output trays to align with the increased tank protrusion.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and usability.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mechanical Design, End Users</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tank design finalization</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank and pass fit/form/function tests.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Size Optimization of Printer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Optimize overall printer size, considering the increased tank and new components.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Maintains competitive footprint and maximizes desk space efficiency.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Industrial Design, Product Management</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Component layout, tank design</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Final product dimensions do not exceed agreed size envelope and pass ergonomic review.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display Integration</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3” CGD (Color Graphic Display) into the printer for enhanced user interface.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Improves user experience and modernizes product appearance.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>End Users, UI/UX Team</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Electrical and mechanical integration, UI software</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Display is fully functional and passes usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4-Tube Platform with Sayan Sibstar Tubes and New Routing</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar tubes, introduce new tube routing and integration for the 4-tube platform.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Supports new ink system architecture and reliability.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tube design, routing validation</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Tube routing supports reliable ink delivery and passes stress and reliability tests.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Update service station for aerosol management with spit platform changes due to new tank design.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Prevents contamination and maintains print quality.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Service station and tank design</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Aerosol emissions are within regulatory and HP internal limits.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Update carriage dynamic and force models to account for new tube routing and weights.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tube and carriage design</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Carriage operates within force budget and passes mechanical reliability tests.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Paper Path Support for Increased Page Life</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Redesign paper path to support increased page life (80K pages).</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ensures durability and reliability for higher duty cycles.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, End Users</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paper path material and design updates</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Paper path components pass 80K page accelerated wear tests.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>140ml K and XXml CMY Bottles</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Introduce new 140ml Black (K) bottles and appropriately sized CMY bottles for the new system.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Aligns with increased yield and system design.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bottle design, supply chain</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bottles meet yield and compatibility requirements in system validation tests.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>24</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>New Make-Break and FI Connection for IDS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Develop new make-break and fluidic interconnect (FI) connection for the IDS (Ink Delivery System).</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Improves reliability and serviceability of the ink system.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>IDS and bottle design</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>New connection passes leak, durability, and usability tests.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>25</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Increased Size, Keying, and LOI for LEBI Ink-Tank</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Increase LEBI (Low-End Bulk Ink) ink-tank size, implement new keying, and integrate LOI (Level of Integration) with one SHAID (Security Hardware Authentication ID).</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Prevents misinstallation, supports higher capacity, and enhances security.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Product Security, R&amp;D, End Users</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tank and keying design, SHAID integration</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Tank passes installation, capacity, and security validation tests.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>26</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Develop a new IDS startup algorithm and air management system for reliable operation.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ensures consistent startup and prevents air entrapment issues.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>IDS and firmware development</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>System starts up reliably in 99% of power-on cycles in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>New Servicing and Startup Algorithm</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Implement new servicing and startup algorithms for improved reliability and user experience.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Reduces errors and improves printer uptime.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>R&amp;D, End Users</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Firmware development, IDS integration</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Algorithms reduce startup and servicing errors by 50% over previous generation in controlled trials.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>New PQ Goals and Depletion Definition</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Establish new print quality (PQ) goals and depletion definitions to align with new page yield targets.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ensures product meets customer expectations and marketing claims.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Yield testing, PQ evaluation</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PQ and depletion metrics approved by cross-functional team and validated in system tests.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>29</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi, Dune FW</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, and Dune firmware for the new printer.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Reduces development time and leverages proven, reliable components.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Engineering, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Compatibility with new platform</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>All reused components function as required in system integration tests.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>30</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Integrate Gauss4.xx hardware and firmware security features into the printer.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Protects product and user data from security threats.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Product Security, IT, End Users</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HW/FW integration, security validation</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Security features pass internal and external penetration testing.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>31</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Printer must support print speeds of 25/20 pages per minute (ppm) for standard and 25/19 ppm for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Meets market expectations for performance and competitiveness.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, Marketing</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Print engine and firmware capability</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Printer achieves required speeds in standardized performance tests.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>32</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Serviceability: Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Design printer with a serviceable maintenance box for easy end-user or service center replacement.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Improves uptime and reduces repair costs.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Maintenance box design, service documentation</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Box can be replaced in under 10 minutes by trained personnel or end users.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>33</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SMB Solution and PaaS Support</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Support SMB solution features and Printer-as-a-Service (PaaS) business models.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Expands addressable market and supports new revenue streams.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Business Development, SMB Customers, IT</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Solution software, service integration</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Printer integrates with SMB solution and PaaS platforms as required by business model.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>34</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Support hosting of 12K-CMYK and trade page yield of 6K as flexible business requirements.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Provides flexibility for different market segments and promotions.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Yield validation, SKU management</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Printer supports 12K-CMYK and 6K trade page configurations as validated in market trials.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>35</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Solution and Services Integration: Scan, Manageability, Enterprise Support</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Integrate scan solutions, SMB manageability, and enterprise support including WJA (Web Jetadmin), HPSM, JAM.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Meets enterprise and SMB customer requirements for fleet management and workflow.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Enterprise IT, SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Software integration, platform compatibility</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>All solution features are functional and validated in enterprise and SMB pilot deployments.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>36</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Maximizes compatibility and ease of use for customers across segments.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>End Users, IT, Support</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Driver and client software updates</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers are supported and pass compatibility tests.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,60 +543,35 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Accept_Goal</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -730,47 +705,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>Reduce the number of product references (names) for HP OfficeJet Pro 9010 series on 123.hp.com to a maximum of one, to avoid user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>The out-of-box experience (OOBE) on 123.hp.com must present only one product name/reference to customers for the HP OJP 9010 series, to reduce user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,47 +839,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting regional intervention specifications and climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>The printer must reliably operate and meet minimum print quality (PQ) and intervention specifications for all new and current EM (Evaluation Media) and market segment media under all relevant climatic conditions for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,47 +973,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>Printer must operate without functional or hardware issues when placed and used on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>The product must operate reliably and without damage to components (such as the input tray sensor flag) when placed on uneven surfaces including sofas, table cloths, and carpets.</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1216,47 +1116,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Printer must function without failure if tilted left or right up to 20 degrees while printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>The printer should be evaluated for functional failures when tilted 20 degrees left or right during printing, as per CISS product test procedures.</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1387,47 +1262,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Printer must print without print quality issues when placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality with no functional issues when printing while placed on a trolley.</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1440,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1501,17 +1351,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity features, scan workflow automation, and manageability solutions into the Magellan printer to simplify business operations for SMBs.</t>
+          <t>Develop NGB keyed bottles for the Magellan printer with 6,000-page yield for Black and CMY, and &gt;8,000-page size for CMY.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To deliver breakthrough productivity and ease of management, differentiating HP from competitors and addressing SMB customer needs for efficiency.</t>
+          <t>To ensure high page yield and compatibility with the new printer, reducing user intervention and supporting high-volume printing.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1521,17 +1371,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires AI software integration and SMB portal support.</t>
+          <t>Dependent on new bottle design and compatibility with existing ink system.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI-powered productivity, scan, and management features are available and verifiable in the product UI; features function as documented and pass UAT.</t>
+          <t>NGB bottles are available for Black and CMY; Black yields 6,000 pages, CMY bottles are &gt;8,000-page size, and bottles are keyed for system compatibility.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1539,7 +1389,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1399,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowest Business TCO (Total Cost of Ownership)</t>
+          <t>Spill-Free Bottle Reliability</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver the lowest total cost of ownership for SMBs among HP business printers, including minimal intervention and optimized consumables.</t>
+          <t>Ensure new NGB bottles provide spill-free reliability when used with the Magellan printer.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To attract cost-conscious SMBs and compete effectively in the CISS PLE Hi segment.</t>
+          <t>To improve user experience and minimize mess or ink wastage during refilling.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1569,25 +1419,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
+          <t>End Users, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires optimized hardware, ink tank design, and efficient consumables.</t>
+          <t>Requires bottle and ink system integration.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TCO calculations demonstrate lower ownership costs than previous HP models and key competitors in third-party benchmarks.</t>
+          <t>No spills occur during bottle installation or removal in 100% of test cases across 100 cycles.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1597,17 +1447,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that customers can easily swap without technical support, reducing downtime and service costs.</t>
+          <t>Integrate NOA-F with a metal foiled labyrinth and lid label; maintain current click on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Addresses new SMB customer segment needs and reduces reliance on service centers, increasing customer satisfaction.</t>
+          <t>To enhance reliability and maintain established user experience features.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1617,17 +1467,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward', 'BA']</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Design must ensure ease of replacement and minimal risk of error.</t>
+          <t>NOA-F design update, compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Customer can replace maintenance box within 5 minutes using only supplied instructions; no tools required; validated in usability testing.</t>
+          <t>NOA-F units include metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms, verified in production samples.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1635,7 +1485,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1495,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Utilize uniquely keyed ink bottles to prevent incorrect refilling and ensure compatibility, reducing user error and warranty claims.</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie ink formulations without requiring ink reformulation for Magellan.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces support costs due to incorrect ink usage.</t>
+          <t>To reduce development time, leverage proven technology, and minimize risk.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1665,25 +1515,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires new bottle design and printer detection mechanism.</t>
+          <t>Compatibility verification with new printer system.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ink bottles are physically keyed and only compatible with intended slots; verified in QA and field tests.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie ink operate within performance specs in the Magellan system with no reformulation required.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1543,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMB Portal for Device Management</t>
+          <t>NOA-F as Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers, targeting unmanaged or lightly managed SMBs without dedicated IT staff.</t>
+          <t>NOA-F units must be available as service parts for warranty support.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Enables easy fleet management for SMBs, a key differentiator for Magellan.</t>
+          <t>To ensure serviceability and maintain warranty commitments for customers.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1713,25 +1563,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>Service, Support, End Users</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires backend infrastructure and secure authentication.</t>
+          <t>Supply chain and service logistics.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Portal is accessible, supports management of at least 15 printers, and passes security and usability tests.</t>
+          <t>NOA-F service parts are available and supplied for warranty claims within standard SLA.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1741,17 +1591,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PaaS (Platform as a Service) Support</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure Magellan is compatible with HP's PaaS offerings, enabling subscription-based services and remote management features.</t>
+          <t>Integrate Acumen 6 feature into the printer lid.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Supports HP's business model shift and customer demand for flexible, scalable solutions.</t>
+          <t>To support advanced features or security as per platform standards.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1761,25 +1611,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Marketing', 'DVAR', 'Tech Reg', 'BA']</t>
+          <t>R&amp;D, Security, Product Management</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Integration with HP PaaS infrastructure.</t>
+          <t>Lid design update and platform integration.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Magellan can be provisioned, managed, and monitored via HP PaaS platform; validated in integration testing.</t>
+          <t>Acumen 6 feature is operational and tested on the production lid.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1789,17 +1639,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PDL/PS Support for PDL SKU</t>
+          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide full PDL (Page Description Language) and PostScript support for the PDL SKU, with print speeds of 25/20 ppm (improvement over current 25/19).</t>
+          <t>Modify existing SA14 factory line for NOA-F, and add Magi ink cart and labelling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enables compatibility with business printing workflows and differentiates Magellan in the SMB segment.</t>
+          <t>To enable efficient manufacturing of the new printer and consumables.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1809,25 +1659,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Firmware and driver development for PDL/PS support.</t>
+          <t>Capex approval, tool procurement, line reconfiguration.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm in standardized print tests; PDL/PS compatibility validated with common business software.</t>
+          <t>SA14 line is modified and operational for NOA-F; Magi ink cart and labelling tool are installed in Orcus 5.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1837,45 +1687,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Achieve Blue Angel environmental certification for the PDL SKU, demonstrating commitment to sustainability and eco-friendly design.</t>
+          <t>Design Magellan printer to allow customer-replaceable PHA and NOA-F units.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Meets regulatory requirements and enhances appeal to environmentally conscious SMBs.</t>
+          <t>To improve user serviceability and reduce support costs.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Quality']</t>
+          <t>End Users, Service, Support</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Design and materials must meet Blue Angel criteria.</t>
+          <t>Mechanical design for easy access and replacement.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Certification is obtained and documented prior to launch.</t>
+          <t>Users can replace PHA and NOA-F without tools in under 5 minutes, verified by usability testing.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1885,17 +1735,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>80k/2 Year Warranty</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Offer a warranty of 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
+          <t>Set new warranty page life goal for Magellan printer at 80,000 pages.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Provides peace of mind for SMB customers and aligns with market expectations.</t>
+          <t>To meet market expectations for durability and reduce warranty claims.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1905,25 +1755,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing', 'BA']</t>
+          <t>Product Management, Quality, End Users</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires reliability testing and service planning.</t>
+          <t>Component reliability, consumable life.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Warranty terms are published and supported; warranty claims tracked for compliance.</t>
+          <t>Printer and consumables function to spec for 80,000 pages under standard test conditions.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1933,17 +1783,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serviceability: PHA and MINK</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Enable customer-replaceable PHA components and MINK at service centers, with a target of making MINK customer-replaceable if out of warranty.</t>
+          <t>Adopt Reddington ID for Magellan with increased tank size; no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs, improving SMB satisfaction and lowering HP support burden.</t>
+          <t>To support higher ink capacity while maintaining design identity.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1953,25 +1803,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>Design, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design for easy replacement; documentation.</t>
+          <t>Tank design update, compatibility with Reddington ID.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PHA and MINK can be replaced per service guide; validated in field trials.</t>
+          <t>Tank size increased as per spec, Reddington ID is maintained, and ADF unchanged.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -1981,17 +1831,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Integrate advanced AI algorithms for print and scan quality enhancement, ensuring optimal output with minimal user intervention.</t>
+          <t>Ensure Magellan printer meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Delivers superior print/scan quality and differentiates Magellan from competitors.</t>
+          <t>To comply with environmental regulations and market requirements.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2001,25 +1851,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'Marketing']</t>
+          <t>Compliance, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires AI software integration and hardware compatibility.</t>
+          <t>Design and documentation for certification.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>AI features demonstrably improve print/scan quality in benchmark tests; user satisfaction &gt;90% in surveys.</t>
+          <t>Printer is certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2029,45 +1879,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sustainability: 60% RCP Content</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure Magellan is manufactured with at least 60% recycled content plastic (RCP), exceeding competitor benchmarks (Epson 30%).</t>
+          <t>Modify input and output trays to align with increased tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Appeals to environmentally conscious customers and aligns with HP sustainability goals.</t>
+          <t>To ensure mechanical compatibility and optimize product footprint.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Quality', 'Marketing']</t>
+          <t>Design, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Supply chain and manufacturing process updates.</t>
+          <t>Tray and tank design coordination.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Product Bill of Materials demonstrates 60% RCP; verified by third-party audit.</t>
+          <t>Trays fit and operate correctly with new tank design; printer passes mechanical fit and finish tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2077,45 +1927,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Support mobile printing workflows through the HP App, enabling users to print from smartphones and tablets.</t>
+          <t>Integrate a 4.3-inch CGD display into the Magellan printer.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Addresses modern SMB mobility needs and enhances user convenience.</t>
+          <t>To provide a modern and user-friendly interface.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing', 'BA']</t>
+          <t>End Users, Product Management, Design</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>App integration and cross-platform compatibility.</t>
+          <t>Electrical and mechanical integration of display.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Users can print from iOS and Android HP Apps; feature passes cross-device testing.</t>
+          <t>4.3” CGD display is functional, passes UI and reliability testing.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2125,17 +1975,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Advanced Telemetry Requirements</t>
+          <t>4-Tube Platform with New Tube Routing and Integration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Implement telemetry features for remote diagnostics, usage tracking, and predictive maintenance, aligned with HP enterprise standards.</t>
+          <t>Leverage Sayan Sibstar tubes for a 4-tube platform, with new tube routing and integration for Magellan.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enables proactive support, reduces downtime, and supports PaaS business model.</t>
+          <t>To improve ink delivery and system reliability.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2145,69 +1995,69 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'Tech Reg', 'BA']</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Backend infrastructure and secure data handling.</t>
+          <t>Tube design and routing, system integration.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Telemetry data is available in the SMB portal and HP support tools; GDPR compliance verified.</t>
+          <t>Four tubes are routed and integrated per design, system passes ink delivery and reliability tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, 12</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield; CMY bottle size must support &gt;8K pages.</t>
+          <t>Update service station for aerosol management with spit platform changes due to new tank.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To increase ink capacity and reduce customer intervention, supporting higher print volumes and competitive positioning.</t>
+          <t>To ensure proper aerosol handling and maintain print quality.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ink formulation compatibility, bottle manufacturing updates</t>
+          <t>Service station and tank design updates.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bottles must be able to deliver at least 6,000 pages (Black/CMY) and &gt;8,000 pages (CMY) as validated by standardized yield tests.</t>
+          <t>Service station manages aerosols effectively, verified by print quality and emissions testing.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2217,45 +2067,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ensure the new ink bottles and tank system deliver spill-free reliability during user refill and maintenance operations.</t>
+          <t>Update carriage dynamic and force model to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Improves user experience and minimizes mess/errors, reducing support costs and customer complaints.</t>
+          <t>To ensure reliable operation and print quality with new system configuration.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, Customer Support</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bottle and tank design, IDS integration</t>
+          <t>Tube and carriage design.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Less than 1% of user refill events result in ink spills, as measured in field trials and lab tests.</t>
+          <t>Carriage operates within force and dynamic parameters with new tubes and weights in testing.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2265,21 +2115,21 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Paper Path Durability for Increased Page Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrate NOA-F (Non-OEM Accessory-Filter) with a metal foiled labyrinth and lid label. No changes to click-on push-push and TDF mechanisms.</t>
+          <t>Enhance paper path to support increased page life of 80,000 pages.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Enhances security, reliability, and differentiation from competitors while maintaining user familiarity.</t>
+          <t>To ensure printer reliability over its extended life expectancy.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2289,21 +2139,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Security, End Users</t>
+          <t>R&amp;D, Quality, End Users</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NOA-F supply chain, mechanical design constraints</t>
+          <t>Paper path component selection and testing.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NOA-F units must pass reliability and security tests with the new labyrinth and label, and be compatible with existing mechanisms.</t>
+          <t>Paper path components show no significant wear after 80,000 pages in accelerated life testing.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2313,45 +2163,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Ink Maintenance Serviceable Part Post-80k Life</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA hardware and Magi/Nessie pigment ink without reformulation.</t>
+          <t>Provide ink maintenance as a serviceable part at service centers after 80,000-page life is reached.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D cost, accelerates time-to-market, and leverages proven technology.</t>
+          <t>To extend printer service life and reduce total cost of ownership.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Engineering, Product Management, Manufacturing</t>
+          <t>Service, End Users, Support</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Compatibility of new system with legacy components</t>
+          <t>Part design and service documentation.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>100% compatibility of reused components in prototype and pilot production builds.</t>
+          <t>Ink maintenance part can be replaced at service centers post-80k life, verified by service procedures.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2361,45 +2211,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ink System Reliability and Characterization</t>
+          <t>140ml Black Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Model and characterize reliability, water vapor transmission rate (WVTR), air gain, flow rate, and IDS including startup and NOA-F end-of-life.</t>
+          <t>Provide 140ml Black bottles and new capacity CMY bottles for Magellan printer.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality and system reliability over product lifecycle.</t>
+          <t>To support higher print volumes and reduce refill frequency.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Product Management, End Users, Supply Chain</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IDS development, system integration</t>
+          <t>Bottle design and supply chain readiness.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Validated models and test data for all key reliability metrics before design freeze.</t>
+          <t>140ml Black bottles and new CMY bottles are available and compatible with Magellan system.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2409,21 +2259,21 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling and PQ Impact Analysis</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and analyze its impact on print quality (PQ).</t>
+          <t>Implement a new IDS startup algorithm and air management system for Magellan.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Maintains high print quality and reduces risk of ink degradation over time.</t>
+          <t>To optimize ink delivery system performance and startup reliability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2433,17 +2283,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Access to ink chemistry data, tank design</t>
+          <t>IDS design and firmware development.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Documented ink stability model and PQ impact report reviewed and approved by R&amp;D.</t>
+          <t>IDS startup algorithm passes performance and reliability tests; air management is verified in system tests.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2457,45 +2307,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts in Warranty Support</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NOA-F must be available as service parts for warranty support and field replacements.</t>
+          <t>Develop new servicing and startup algorithm for Magellan printer.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures serviceability and customer satisfaction during warranty period.</t>
+          <t>To improve reliability and user experience during initial setup and servicing.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Service supply chain, inventory planning</t>
+          <t>Firmware development and integration.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NOA-F service parts available in service centers within 3 months of product launch.</t>
+          <t>Servicing and startup algorithm passes reliability and usability testing.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2505,21 +2355,21 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology onto the ink bottle lid for authentication or tracking.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan printer.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Improves anti-counterfeiting and supply chain traceability.</t>
+          <t>To leverage proven electronics and reduce development cost and risk.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2529,21 +2379,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Product Security, Supply Chain</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 system integration</t>
+          <t>Compatibility verification with Magellan platform.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Acumen 6 feature fully functional and passes security validation tests.</t>
+          <t>All reused components operate to spec in Magellan printer.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2553,45 +2403,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Modify Factory Line for NOA-F and New Bottles</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Modify SA14 production line for NOA-F assembly; add Magi ink cart and labeling tool in Orcus 5. Mold for 1-4 new keyed caps required.</t>
+          <t>Integrate Stingray Wi-Fi module into Magellan printer.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Supports manufacturing of new consumables and assemblies.</t>
+          <t>To provide wireless connectivity as per current standards.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>End Users, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Factory retooling schedules, cap design finalization</t>
+          <t>Electrical and firmware integration.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Factory lines operational and producing new components at required yield rates before launch.</t>
+          <t>Wi-Fi module is operational and passes connectivity and compliance tests.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2601,21 +2451,21 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Support Customer-Replaceable PHA and NOA-F</t>
+          <t>FW Dune and Gauss4.xx Security Integration</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Design the system to allow customers to easily replace PHA (Printhead Assembly) and NOA-F without professional service.</t>
+          <t>Integrate FW Dune and Gauss4.xx security features into Magellan printer (hardware and firmware).</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces service costs.</t>
+          <t>To ensure security compliance and protect user data.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2625,21 +2475,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>End Users, Service</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Design for serviceability, user documentation</t>
+          <t>Firmware and hardware integration, compliance testing.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Replacement process can be performed by end users in under 5 minutes with no tools, as validated in usability studies.</t>
+          <t>FW Dune and Gauss4.xx security features are operational and pass security validation tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2649,21 +2499,21 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal: 80K Pages</t>
+          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
+          <t>Magellan must support business models for Consumer, SMB, and Enterprise segments, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Extends product life and supports higher duty cycle use-cases, competitive advantage.</t>
+          <t>To maximize market reach and adapt to diverse customer needs.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2673,21 +2523,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>Business, Sales, Product Management</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Component durability, consumable yield, warranty policy</t>
+          <t>Service and solution development.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Printer must reliably print 80,000 pages without major failure, as verified in accelerated life testing.</t>
+          <t>Printer is offered in configurations and bundles supporting the specified segments and services.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2697,45 +2547,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>Solution Integration: Scan, SMB Manageability, Enterprise Support</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID with a size increase for the ink tank. No change to Marconi-HI ADF (Automatic Document Feeder).</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into Magellan platform.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Supports higher ink capacity and aligns with existing industrial design.</t>
+          <t>To enhance solution offering and address business customer requirements.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Industrial Design, Product Management</t>
+          <t>Business, R&amp;D, Product Management, Enterprise Customers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tank design, chassis compatibility</t>
+          <t>Solution and software integration.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>New tank design integrated into Reddington ID and passes mechanical and aesthetic validation.</t>
+          <t>All listed solutions are functional and pass integration and user acceptance testing.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2745,41 +2595,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Utilize EPS foam packaging for the printer and consumables.</t>
+          <t>Provide client and driver support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Protects product during shipping and handling.</t>
+          <t>To ensure broad compatibility and ease of use across platforms and customer environments.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Logistics, Manufacturing</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Packaging design, material sourcing</t>
+          <t>Driver and software development.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Products pass drop and vibration tests with EPS packaging.</t>
+          <t>All listed clients and drivers are available, tested, and documented for Magellan printer.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2793,21 +2643,21 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+          <t>Leverage Watt-LE/Marconi Hi Mech + CISS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ensure compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+          <t>Leverage Watt-LE/Marconi Hi mechanical platform and integrate with CISS for Magellan.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Meets regulatory and market requirements for sustainability and eco-labels.</t>
+          <t>To reduce development cost and time to market while incorporating CISS benefits.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2817,141 +2667,141 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Design and material choices, certification processes</t>
+          <t>Mechanical and system integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PDL SKU achieves EPEAT3, LOT4, and Blue Angel certifications before launch.</t>
+          <t>Watt-LE/Marconi Hi Mech platform is used and CISS is integrated and passes system tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Input/Output Tray Modifications for Tank Protrusion</t>
+          <t>Schedule as Least Flexible Constraint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with the increased tank protrusion.</t>
+          <t>Meet the schedule as the highest business constraint for Magellan program.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and usability.</t>
+          <t>To ensure timely market entry and competitive positioning.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mechanical Design, End Users</t>
+          <t>Business, Program Management, R&amp;D</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tank design finalization</t>
+          <t>All critical path activities.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Trays function correctly with new tank and pass fit/form/function tests.</t>
+          <t>All program milestones are met as per published schedule.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Size Optimization of Printer</t>
+          <t>SuperAmp PHA Life at 65K as Least Flexible Constraint</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Optimize overall printer size, considering the increased tank and new components.</t>
+          <t>SuperAmp PHA must achieve a life of at least 65,000 pages for Magellan.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Maintains competitive footprint and maximizes desk space efficiency.</t>
+          <t>To ensure reliability and meet business constraints for consumable life.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Industrial Design, Product Management</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Component layout, tank design</t>
+          <t>PHA design and testing.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Final product dimensions do not exceed agreed size envelope and pass ergonomic review.</t>
+          <t>SuperAmp PHA is verified to last at least 65,000 pages in standard test cycles.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Warranty Life of 2 Years as Optimized Priority</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Integrate a 4.3” CGD (Color Graphic Display) into the printer for enhanced user interface.</t>
+          <t>Magellan printer must be warranted for 2 years or up to the page life goal, whichever comes first.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Improves user experience and modernizes product appearance.</t>
+          <t>To align with market expectations and business priorities.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2961,17 +2811,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>End Users, UI/UX Team</t>
+          <t>Product Management, End Users, Sales</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Electrical and mechanical integration, UI software</t>
+          <t>Component reliability, service policies.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Display is fully functional and passes usability and reliability tests.</t>
+          <t>Product warranty is offered for 2 years or 80,000 pages, with support processes in place.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2979,27 +2829,27 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4-Tube Platform with Sayan Sibstar Tubes and New Routing</t>
+          <t>Throughput of 25/20 ppm (PDL) as Optimized Priority</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes, introduce new tube routing and integration for the 4-tube platform.</t>
+          <t>Magellan printer must achieve throughput of 25 ppm (mono) and 20 ppm (color) for PDL SKU.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Supports new ink system architecture and reliability.</t>
+          <t>To meet performance requirements and market competitiveness.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3009,45 +2859,45 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>End Users, Product Management, Sales</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tube design, routing validation</t>
+          <t>Print engine and firmware performance.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tube routing supports reliable ink delivery and passes stress and reliability tests.</t>
+          <t>Printer achieves 25 ppm mono and 20 ppm color in PDL SKU during standard performance tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Serviceability of Maintenance Box as Optimized Priority</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Update service station for aerosol management with spit platform changes due to new tank design.</t>
+          <t>Design Magellan printer for easy servicing of the maintenance box.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Prevents contamination and maintains print quality.</t>
+          <t>To improve post-sale support and reduce downtime.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3057,17 +2907,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>Service, End Users, Support</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Service station and tank design</t>
+          <t>Mechanical design for access and replacement.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Aerosol emissions are within regulatory and HP internal limits.</t>
+          <t>Maintenance box can be serviced or replaced within 10 minutes by service personnel.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -3075,75 +2925,75 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>SMB Solution Support as Optimized Priority</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and weights.</t>
+          <t>Magellan must support SMB solutions as an optimized business priority.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality with new system configuration.</t>
+          <t>To ensure the printer meets the needs of small and medium business customers.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, R&amp;D</t>
+          <t>SMB Customers, Sales, Product Management</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tube and carriage design</t>
+          <t>Solution integration and support.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Carriage operates within force budget and passes mechanical reliability tests.</t>
+          <t>SMB solutions are available and functional for Magellan printer.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>PaaS Schedule as Optimized Priority</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life (80K pages).</t>
+          <t>Ensure PaaS (Printing as a Service) is delivered according to schedule for Magellan.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ensures durability and reliability for higher duty cycles.</t>
+          <t>To support new business models and revenue streams.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3153,141 +3003,141 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Paper path material and design updates</t>
+          <t>PaaS development and integration.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paper path components pass 80K page accelerated wear tests.</t>
+          <t>PaaS is available for Magellan as per published schedule and passes customer acceptance.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>140ml K and XXml CMY Bottles</t>
+          <t>Host 12K-CMYK as Flexible Priority</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Introduce new 140ml Black (K) bottles and appropriately sized CMY bottles for the new system.</t>
+          <t>Provide support for hosting 12K-CMYK as a flexible business priority.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aligns with increased yield and system design.</t>
+          <t>To allow for future scalability and market adaptation.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bottle design, supply chain</t>
+          <t>System design for scalability.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bottles meet yield and compatibility requirements in system validation tests.</t>
+          <t>System design can accommodate 12K-CMYK hosting if required in future roadmap.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>Trade Page 6K as Flexible Priority</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Develop new make-break and fluidic interconnect (FI) connection for the IDS (Ink Delivery System).</t>
+          <t>Support trade page 6K as a flexible business priority.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Improves reliability and serviceability of the ink system.</t>
+          <t>To provide options for market-specific or promotional SKUs.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Product Management, Sales</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>IDS and bottle design</t>
+          <t>SKU and configuration management.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>New connection passes leak, durability, and usability tests.</t>
+          <t>Trade page 6K option is available as a configurable SKU.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Increased Size, Keying, and LOI for LEBI Ink-Tank</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Increase LEBI (Low-End Bulk Ink) ink-tank size, implement new keying, and integrate LOI (Level of Integration) with one SHAID (Security Hardware Authentication ID).</t>
+          <t>Integrate advanced AI-driven productivity solutions for print, scan, and workflow management, tailored for SMBs with minimal IT support.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Prevents misinstallation, supports higher capacity, and enhances security.</t>
+          <t>Addresses the need for efficient management and automation in SMBs lacking dedicated IT, delivering breakthrough productivity as a key differentiator.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3297,45 +3147,45 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Product Security, R&amp;D, End Users</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tank and keying design, SHAID integration</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tank passes installation, capacity, and security validation tests.</t>
+          <t>AI solutions are available for print, scan, and workflow tasks; demonstrated efficiency gains in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Consolidated SMB Portal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Develop a new IDS startup algorithm and air management system for reliable operation.</t>
+          <t>Develop a unified portal for device management, enabling Office Managers and Generalist IT staff to easily manage multiple printers from a single interface.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ensures consistent startup and prevents air entrapment issues.</t>
+          <t>Unmanaged/Lightly Managed SMBs require simple, centralized management to reduce IT burden and improve control.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3345,93 +3195,93 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>['Marketing', 'GXD', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IDS and firmware development</t>
+          <t>Requires backend portal development and printer firmware support.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>System starts up reliably in 99% of power-on cycles in lab and field tests.</t>
+          <t>Portal allows management of at least 6-15 printers, supports key admin tasks, and is validated by user testing with SMBs.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithms for improved reliability and user experience.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO in the SMB segment, focusing on minimal intervention, high yield, and cost-efficient consumables.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Reduces errors and improves printer uptime.</t>
+          <t>SMBs value ROI and efficiency; lowest TCO is a primary purchase driver and competitive differentiator.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R&amp;D, End Users</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Firmware development, IDS integration</t>
+          <t>Requires high-yield consumables, efficient hardware design, and supply chain optimization.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Algorithms reduce startup and servicing errors by 50% over previous generation in controlled trials.</t>
+          <t>TCO analysis demonstrates lowest cost in segment compared to key competitors (Epson, Canon).</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New PQ Goals and Depletion Definition</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Establish new print quality (PQ) goals and depletion definitions to align with new page yield targets.</t>
+          <t>Introduce a replaceable maintenance box that can be easily swapped by the customer, reducing service calls and printer downtime.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ensures product meets customer expectations and marketing claims.</t>
+          <t>Reduces maintenance burden for SMBs with limited IT resources and addresses new customer needs.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3441,17 +3291,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Marketing</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yield testing, PQ evaluation</t>
+          <t>Requires hardware redesign and documentation for end-user replacement.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PQ and depletion metrics approved by cross-functional team and validated in system tests.</t>
+          <t>Maintenance box can be replaced by users without tools in under 5 minutes, validated in usability tests.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3459,75 +3309,75 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi, Dune FW</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, and Dune firmware for the new printer.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility, minimizing user errors and support incidents.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Reduces development time and leverages proven, reliable components.</t>
+          <t>Improves user experience and reduces support costs by preventing ink mix-ups.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Engineering, Manufacturing</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Compatibility with new platform</t>
+          <t>Requires design of bottle and tank interface.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>All reused components function as required in system integration tests.</t>
+          <t>Keyed bottles are only compatible with correct tank, validated by lab and field tests.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Integrate Gauss4.xx hardware and firmware security features into the printer.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB usage patterns and expectations.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Protects product and user data from security threats.</t>
+          <t>Supports SMB purchasing decisions and provides assurance for high-usage environments.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3537,93 +3387,93 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Product Security, IT, End Users</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HW/FW integration, security validation</t>
+          <t>Requires durability testing and warranty policy alignment.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Security features pass internal and external penetration testing.</t>
+          <t>Warranty terms are included in product materials and supported by reliability testing.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Serviceability – PHA and MINK</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Printer must support print speeds of 25/20 pages per minute (ppm) for standard and 25/19 ppm for PDL SKU.</t>
+          <t>Enable customer-replaceable PHA components and MINK servicing at authorized centers, targeting customer replaceability as the preferred threshold if out of warranty.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and competitiveness.</t>
+          <t>Minimizes downtime and support costs for SMBs, improving satisfaction and reducing service expenses.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Marketing</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Print engine and firmware capability</t>
+          <t>Requires design for replaceability and service documentation.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Printer achieves required speeds in standardized performance tests.</t>
+          <t>PHA parts are customer-replaceable; MINK service available at centers; validated in service trials.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Serviceability: Maintenance Box</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Design printer with a serviceable maintenance box for easy end-user or service center replacement.</t>
+          <t>Provide SMB2.0 solutions and an Advanced View SMB portal for non-PDL SKUs, supporting Platform-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Improves uptime and reduces repair costs.</t>
+          <t>Addresses specific SMB management needs and enables new business models (PaaS).</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3633,17 +3483,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation</t>
+          <t>Requires software development and integration with hardware.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Box can be replaced in under 10 minutes by trained personnel or end users.</t>
+          <t>SMB2.0 and Advanced View portal are functional and available at launch for non-PDL SKUs.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3651,123 +3501,123 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SMB Solution and PaaS Support</t>
+          <t>PDL SKU: Improved Speed and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Support SMB solution features and Printer-as-a-Service (PaaS) business models.</t>
+          <t>PDL SKUs must support improved print speeds (25/20 ppm) and meet Blue Angel environmental standards.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Expands addressable market and supports new revenue streams.</t>
+          <t>Meets market expectations for performance and sustainability in higher-end SKUs.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Business Development, SMB Customers, IT</t>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Solution software, service integration</t>
+          <t>Requires hardware and firmware optimization, compliance testing.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Printer integrates with SMB solution and PaaS platforms as required by business model.</t>
+          <t>PDL SKU achieves 25/20 ppm and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K</t>
+          <t>Perfect Print and Perfect Scan Features</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Support hosting of 12K-CMYK and trade page yield of 6K as flexible business requirements.</t>
+          <t>Deliver advanced print and scan quality features, leveraging AI to ensure optimal output with minimal user intervention.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Provides flexibility for different market segments and promotions.</t>
+          <t>Addresses SMB need for professional-quality documents without expert setup.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Product Management, Marketing</t>
+          <t>['Marketing', 'GXD', 'Quality']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yield validation, SKU management</t>
+          <t>Requires AI software and sensor integration.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Printer supports 12K-CMYK and 6K trade page configurations as validated in market trials.</t>
+          <t>Print and scan quality meets or exceeds defined benchmarks in SMB use cases.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Solution and Services Integration: Scan, Manageability, Enterprise Support</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Integrate scan solutions, SMB manageability, and enterprise support including WJA (Web Jetadmin), HPSM, JAM.</t>
+          <t>Design the product using at least 60% recycled content plastic, surpassing competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Meets enterprise and SMB customer requirements for fleet management and workflow.</t>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3777,73 +3627,217 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Enterprise IT, SMB Customers, Product Management</t>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Software integration, platform compatibility</t>
+          <t>Requires sourcing and manufacturing process changes.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>All solution features are functional and validated in enterprise and SMB pilot deployments.</t>
+          <t>Third-party audit confirms at least 60% RCP in product materials.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Enable seamless mobile printing and device management via the HP App, supporting common SMB workflows.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Maximizes compatibility and ease of use for customers across segments.</t>
+          <t>SMBs increasingly rely on mobile devices for business operations; app integration is a user expectation.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['GXD', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Requires app development and printer firmware support.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Mobile print and management features available in HP App and validated with SMB users.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>13</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PaaS Enablement</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Support Platform-as-a-Service (PaaS) models to allow flexible, usage-based billing and management for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Enables new business models and recurring revenue streams for HP, aligning with market trends.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['Marketing', 'BA']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Requires integration with HP’s PaaS infrastructure.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PaaS features available and functional for eligible SKUs at launch.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>14</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Implement telemetry capabilities to collect device usage, performance, and health data for proactive support and analytics.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Enables HP and SMBs to monitor device health, optimize usage, and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Requires secure data collection and privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, transmitted securely, and accessible via portal; meets privacy standards.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>15</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Advanced Security and Compliance</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ensure the product meets enterprise-grade security and regulatory compliance requirements relevant for SMBs.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Protects SMB customers from security threats and ensures compliance with local regulations.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>End Users, IT, Support</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Driver and client software updates</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>All listed clients and drivers are supported and pass compatibility tests.</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Requires security features and regulatory review.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Product passes security and compliance audits for target markets.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, inferred from multiple sections</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,160 +418,160 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Department_Requestor</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -1306,57 +1294,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -1290,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,45 +1646,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
+          <t>Provide NOA-F as service parts for warranty support, ensuring availability during the warranty period.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
+          <t>Improves serviceability and supports contractual service obligations.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Quality Assurance</t>
+          <t>Service, Support, Supply Chain</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dependent on Acumen 6 technology readiness.</t>
+          <t>NOA-F design finalization and supply chain planning.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
+          <t>NOA-F parts are available for all warranty claims within service SLAs.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1695,45 +1695,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Modify Existing SA 14 Line for NOA-F</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
+          <t>Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enables efficient manufacturing and quality control for new components.</t>
+          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>R&amp;D, Security, Quality Assurance</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Final NOA-F design, factory retooling schedule.</t>
+          <t>Dependent on Acumen 6 technology readiness.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
+          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1744,45 +1744,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
+          <t>Modify Existing SA 14 Line for NOA-F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
+          <t>Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Supports production of new ink system and traceability.</t>
+          <t>Enables efficient manufacturing and quality control for new components.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, Supply Chain</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orcus 5 readiness, tool procurement.</t>
+          <t>Final NOA-F design, factory retooling schedule.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
+          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1793,45 +1793,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
+          <t>Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reduces service costs and increases customer satisfaction.</t>
+          <t>Supports production of new ink system and traceability.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Manufacturing, Operations, Supply Chain</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Requires robust design for user handling.</t>
+          <t>Orcus 5 readiness, tool procurement.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
+          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1842,21 +1842,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Support New Warranty Page Life Goal of 80k Pages</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure system reliability and consumable capacity to support a warranty page life goal of 80,000 pages.</t>
+          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
+          <t>Reduces service costs and increases customer satisfaction.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1866,17 +1866,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>All system components must meet durability targets.</t>
+          <t>Requires robust design for user handling.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>System passes accelerated life testing to 80,000 pages with no critical failures.</t>
+          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1891,21 +1891,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>Support New Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+          <t>Ensure system reliability and consumable capacity to support a warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Enables sales in regulated markets and supports sustainability goals.</t>
+          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1915,21 +1915,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Product design and documentation updates.</t>
+          <t>All system components must meet durability targets.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Product achieves certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+          <t>System passes accelerated life testing to 80,000 pages with no critical failures.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>Product Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Adopt Reddington industrial design (ID) with modifications for increased tank size; maintain Marconi-HI ADF and EPS foam packaging.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ensures physical compatibility and maintains compact product footprint.</t>
+          <t>Accommodates higher capacity while leveraging existing design elements.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Design, Manufacturing, R&amp;D</t>
+          <t>Design, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tank size and chassis design.</t>
+          <t>Tank and chassis design, packaging updates.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Trays operate without interference, and overall product dimensions meet target specifications.</t>
+          <t>Product passes design review and packaging tests with new tank size and EPS foam.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1989,41 +1989,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) for user interface.</t>
+          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Improves usability and aligns with market expectations for modern printers.</t>
+          <t>Enables sales in regulated markets and supports sustainability goals.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>End Users, Product Management, UX Design</t>
+          <t>Regulatory, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Display sourcing, UI software.</t>
+          <t>Product design and documentation updates.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Display is functional and passes user experience testing.</t>
+          <t>Product achieves certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2038,21 +2038,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Utilize Sayan Sibstar tubes and implement new tube routing and integration for the ink delivery system.</t>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Improves reliability and supports new tank configuration.</t>
+          <t>Ensures physical compatibility and maintains compact product footprint.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2062,17 +2062,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Design, Manufacturing, R&amp;D</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tube design finalization, chassis integration.</t>
+          <t>Tank size and chassis design.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tubes are installed without leaks or flow issues in 100 test units.</t>
+          <t>Trays operate without interference, and overall product dimensions meet target specifications.</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -2087,21 +2087,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with New Tubes and Weights</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Develop new dynamic and force models for the carriage, accounting for new tube routing and increased weights.</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) for user interface.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ensures print quality and mechanical reliability.</t>
+          <t>Improves usability and aligns with market expectations for modern printers.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2111,21 +2111,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>End Users, Product Management, UX Design</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Final tube and tank design.</t>
+          <t>Display sourcing, UI software.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Carriage operates within force and acceleration limits in simulation and physical testing.</t>
+          <t>Display is functional and passes user experience testing.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2136,45 +2136,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased duty cycle and page life up to 80k pages.</t>
+          <t>Utilize Sayan Sibstar tubes and implement new tube routing and integration for the ink delivery system.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ensures consistent reliability and performance over extended use.</t>
+          <t>Improves reliability and supports new tank configuration.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chassis and component durability.</t>
+          <t>Tube design finalization, chassis integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paper path components pass 80k page accelerated life test.</t>
+          <t>Tubes are installed without leaks or flow issues in 100 test units.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>Service Station Aerosol Management with Tank Changes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable at service centers after 80k page life is reached.</t>
+          <t>Update service station for aerosol management, accounting for changes due to new tank design.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Facilitates extended product life and supports service contracts.</t>
+          <t>Prevents contamination and ensures long-term reliability.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2209,21 +2209,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Service, Support, End Users</t>
+          <t>R&amp;D, Quality Assurance, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service center readiness, part design.</t>
+          <t>Service station and tank design.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts in &lt;30 minutes with standard tools.</t>
+          <t>Aerosol levels remain within safe limits in endurance testing.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>140ml Black and New CMY Bottles</t>
+          <t>Carriage Dynamic and Force Model with New Tubes and Weights</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Introduce 140ml black bottles and new capacity CMY bottles for Magellan platform.</t>
+          <t>Develop new dynamic and force models for the carriage, accounting for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Supports higher page yields and reduces refill frequency.</t>
+          <t>Ensures print quality and mechanical reliability.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2258,21 +2258,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Consumables Team, R&amp;D, Product Management</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bottle and tank design.</t>
+          <t>Final tube and tank design.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bottles meet capacity and compatibility requirements in production units.</t>
+          <t>Carriage operates within force and acceleration limits in simulation and physical testing.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2283,45 +2283,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
+          <t>Redesign paper path to support increased duty cycle and page life up to 80k pages.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Improves reliability and serviceability of ink connections.</t>
+          <t>Ensures consistent reliability and performance over extended use.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IDS and tank design.</t>
+          <t>Chassis and component durability.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
+          <t>Paper path components pass 80k page accelerated life test.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adopt LEBI ink-tank design with increased size, unique keying, and LOI (Level of Integration) One SHAID for security and compatibility.</t>
+          <t>Design ink maintenance components to be serviceable at service centers after 80k page life is reached.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Prevents cross-contamination and supports secure supply chain.</t>
+          <t>Facilitates extended product life and supports service contracts.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Supply Chain</t>
+          <t>Service, Support, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tank and bottle design, SHAID technology.</t>
+          <t>Service center readiness, part design.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
+          <t>Service centers can replace ink maintenance parts in &lt;30 minutes with standard tools.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2381,21 +2381,21 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>New IDS Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
+          <t>Improves reliability and serviceability of ink connections.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
+          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -2430,21 +2430,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
+          <t>Adopt LEBI ink-tank design with increased size, unique keying, and LOI (Level of Integration) One SHAID for security and compatibility.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Improves system uptime and reduces service calls.</t>
+          <t>Prevents cross-contamination and supports secure supply chain.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2454,21 +2454,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Security, Supply Chain</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IDS, firmware development.</t>
+          <t>Tank and bottle design, SHAID technology.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
+          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New PQ Goals and Depletion Definition</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
+          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ensures consistent output and clear customer communication on ink usage.</t>
+          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2503,21 +2503,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Marketing</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Page yield testing, IDS design.</t>
+          <t>IDS and tank design.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
+          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2528,45 +2528,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
+          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven, reliable components.</t>
+          <t>Improves system uptime and reduces service calls.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Compatibility with new system design.</t>
+          <t>IDS, firmware development.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Components pass integration and system validation tests in Magellan units.</t>
+          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>New PQ Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
+          <t>Ensures consistent output and clear customer communication on ink usage.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2601,21 +2601,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>Product Management, R&amp;D, Marketing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration.</t>
+          <t>Page yield testing, IDS design.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware features pass functional and security testing.</t>
+          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ensures compliance with security standards and protects against threats.</t>
+          <t>Reduces development cost and leverages proven, reliable components.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2650,21 +2650,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HW/FW development, certification.</t>
+          <t>Compatibility with new system design.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
+          <t>Components pass integration and system validation tests in Magellan units.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2675,45 +2675,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Expands market reach and supports diverse customer requirements.</t>
+          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Service and solution development.</t>
+          <t>Module sourcing, firmware integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
+          <t>Wi-Fi and firmware features pass functional and security testing.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2724,45 +2724,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
+          <t>Ensures compliance with security standards and protects against threats.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT, Product Management</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Software development and integration.</t>
+          <t>HW/FW development, certification.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
+          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2773,45 +2773,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Support for Multiple Clients and Drivers</t>
+          <t>Support for Consumer, SMB, and Enterprise Segments</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
+          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
+          <t>Expands market reach and supports diverse customer requirements.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>IT, End Users, Product Management</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Driver and client software development.</t>
+          <t>Service and solution development.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
+          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2822,119 +2822,119 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
+          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Critical for product reliability and competitive positioning.</t>
+          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PHA design and validation.</t>
+          <t>Software development and integration.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
+          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or 80k Pages</t>
+          <t>Support for Multiple Clients and Drivers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aligns with customer expectations and competitive offerings.</t>
+          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>IT, End Users, Product Management</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>System reliability, consumable capacity.</t>
+          <t>Driver and client software development.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
+          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
+          <t>SuperAmp PHA Life at 65K Pages</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
+          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Meets market performance benchmarks and customer needs.</t>
+          <t>Critical for product reliability and competitive positioning.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2944,70 +2944,70 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>R&amp;D, Service, Product Management</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Engine design, firmware optimization.</t>
+          <t>PHA design and validation.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Printer achieves specified throughput in ISO test conditions.</t>
+          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>Warranty Life of 2 Years or 80k Pages</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
+          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs.</t>
+          <t>Aligns with customer expectations and competitive offerings.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Maintenance box design.</t>
+          <t>System reliability, consumable capacity.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
+          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3018,166 +3018,166 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>36</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Meets market performance benchmarks and customer needs.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, End Users</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Engine design, firmware optimization.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Printer achieves specified throughput in ISO test conditions.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>37</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Serviceability of Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Maintenance box design.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>38</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Allows adaptation to changing market and business needs.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Product Management, Business</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>System design flexibility.</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Configurations are validated and available as business needs arise.</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I38" t="n">
         <v>0.7</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>AI Productivity and Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Requires integration with SMB portal and AI solution development.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Lowest Business TCO for SMB Segment</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Marketing, BA, Quality, Supplies Quality</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>2</v>
-      </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
+          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3187,46 +3187,46 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Requires hardware and packaging design for easy replacement.</t>
+          <t>Requires integration with SMB portal and AI solution development.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
+          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Lowest Business TCO for SMB Segment</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
+          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Prevents user error and potential damage, reducing support incidents.</t>
+          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3236,46 +3236,46 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA, Tech Reg</t>
+          <t>Marketing, BA, Quality, Supplies Quality</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires bottle and tank redesign.</t>
+          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
+          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, Page 11</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
+          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3285,70 +3285,70 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+          <t>Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
+          <t>Requires hardware and packaging design for easy replacement.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
+          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+          <t>Prevents user error and potential damage, reducing support incidents.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marketing, GXD, DVAR, BA</t>
+          <t>Quality, Supplies Quality, BA, Tech Reg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires integration with HP cloud and service platforms.</t>
+          <t>Requires bottle and tank redesign.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3356,24 +3356,24 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PDL SKU Performance and Compatibility</t>
+          <t>SMB Portal for Printer Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
+          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ensures competitive performance and compliance for managed office environments.</t>
+          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marketing, Tech Reg, Quality, DVAR</t>
+          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
+          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
+          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3401,77 +3401,77 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, Page 10</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
+          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+          <t>Marketing, GXD, DVAR, BA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires AI software development and hardware compatibility.</t>
+          <t>Requires integration with HP cloud and service platforms.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
+          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>PDL SKU Performance and Compatibility</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
+          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+          <t>Ensures competitive performance and compliance for managed office environments.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3481,95 +3481,95 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Tech Reg</t>
+          <t>Marketing, Tech Reg, Quality, DVAR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Requires sourcing and validation of recycled materials.</t>
+          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
+          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Minimal Maintenance Design</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Reduces operational costs and downtime for SMBs.</t>
+          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pending investigation and design validation.</t>
+          <t>Requires AI software development and hardware compatibility.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 7, Page 11</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Comprehensive Telemetry Support</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
+          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3579,77 +3579,175 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
+          <t>Prod Steward, Marketing, Tech Reg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Requires firmware and cloud integration.</t>
+          <t>Requires sourcing and validation of recycled materials.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
+          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
+          <t>Minimal Maintenance Design</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Reduces operational costs and downtime for SMBs.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pending investigation and design validation.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Comprehensive Telemetry Support</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Requires firmware and cloud integration.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, Page 12</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Supports modern SMB workflows and BYOD environments.</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>GXD, Marketing, BA</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Requires app and firmware compatibility.</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I50" t="n">
         <v>0.9</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Magellan MRD, Page 9, Page 10</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="K50" t="n">
         <v>12</v>
       </c>
     </row>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -1290,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,45 +1646,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts for warranty support, ensuring availability during the warranty period.</t>
+          <t>Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves serviceability and supports contractual service obligations.</t>
+          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Support, Supply Chain</t>
+          <t>R&amp;D, Security, Quality Assurance</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NOA-F design finalization and supply chain planning.</t>
+          <t>Dependent on Acumen 6 technology readiness.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F parts are available for all warranty claims within service SLAs.</t>
+          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1695,45 +1695,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Modify Existing SA 14 Line for NOA-F</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
+          <t>Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
+          <t>Enables efficient manufacturing and quality control for new components.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Quality Assurance</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dependent on Acumen 6 technology readiness.</t>
+          <t>Final NOA-F design, factory retooling schedule.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
+          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1744,45 +1744,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Modify Existing SA 14 Line for NOA-F</t>
+          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
+          <t>Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Enables efficient manufacturing and quality control for new components.</t>
+          <t>Supports production of new ink system and traceability.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Manufacturing, Operations, Supply Chain</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Final NOA-F design, factory retooling schedule.</t>
+          <t>Orcus 5 readiness, tool procurement.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
+          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1793,45 +1793,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
+          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Supports production of new ink system and traceability.</t>
+          <t>Reduces service costs and increases customer satisfaction.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, Supply Chain</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orcus 5 readiness, tool procurement.</t>
+          <t>Requires robust design for user handling.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
+          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1842,21 +1842,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Support New Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
+          <t>Ensure system reliability and consumable capacity to support a warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reduces service costs and increases customer satisfaction.</t>
+          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1866,17 +1866,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires robust design for user handling.</t>
+          <t>All system components must meet durability targets.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
+          <t>System passes accelerated life testing to 80,000 pages with no critical failures.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1891,21 +1891,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Support New Warranty Page Life Goal of 80k Pages</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure system reliability and consumable capacity to support a warranty page life goal of 80,000 pages.</t>
+          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
+          <t>Enables sales in regulated markets and supports sustainability goals.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1915,21 +1915,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Regulatory, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>All system components must meet durability targets.</t>
+          <t>Product design and documentation updates.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>System passes accelerated life testing to 80,000 pages with no critical failures.</t>
+          <t>Product achieves certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Product Reddington ID with Increased Tank Size</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adopt Reddington industrial design (ID) with modifications for increased tank size; maintain Marconi-HI ADF and EPS foam packaging.</t>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Accommodates higher capacity while leveraging existing design elements.</t>
+          <t>Ensures physical compatibility and maintains compact product footprint.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Design, Product Management, Manufacturing</t>
+          <t>Design, Manufacturing, R&amp;D</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tank and chassis design, packaging updates.</t>
+          <t>Tank size and chassis design.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Product passes design review and packaging tests with new tank size and EPS foam.</t>
+          <t>Trays operate without interference, and overall product dimensions meet target specifications.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1989,41 +1989,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) for user interface.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enables sales in regulated markets and supports sustainability goals.</t>
+          <t>Improves usability and aligns with market expectations for modern printers.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>End Users, Product Management, UX Design</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Product design and documentation updates.</t>
+          <t>Display sourcing, UI software.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product achieves certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+          <t>Display is functional and passes user experience testing.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2038,21 +2038,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Utilize Sayan Sibstar tubes and implement new tube routing and integration for the ink delivery system.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures physical compatibility and maintains compact product footprint.</t>
+          <t>Improves reliability and supports new tank configuration.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2062,17 +2062,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Design, Manufacturing, R&amp;D</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tank size and chassis design.</t>
+          <t>Tube design finalization, chassis integration.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Trays operate without interference, and overall product dimensions meet target specifications.</t>
+          <t>Tubes are installed without leaks or flow issues in 100 test units.</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -2087,21 +2087,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Carriage Dynamic and Force Model with New Tubes and Weights</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) for user interface.</t>
+          <t>Develop new dynamic and force models for the carriage, accounting for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Improves usability and aligns with market expectations for modern printers.</t>
+          <t>Ensures print quality and mechanical reliability.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2111,21 +2111,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, Product Management, UX Design</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Display sourcing, UI software.</t>
+          <t>Final tube and tank design.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Display is functional and passes user experience testing.</t>
+          <t>Carriage operates within force and acceleration limits in simulation and physical testing.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2136,45 +2136,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Utilize Sayan Sibstar tubes and implement new tube routing and integration for the ink delivery system.</t>
+          <t>Redesign paper path to support increased duty cycle and page life up to 80k pages.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Improves reliability and supports new tank configuration.</t>
+          <t>Ensures consistent reliability and performance over extended use.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tube design finalization, chassis integration.</t>
+          <t>Chassis and component durability.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tubes are installed without leaks or flow issues in 100 test units.</t>
+          <t>Paper path components pass 80k page accelerated life test.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management with Tank Changes</t>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Update service station for aerosol management, accounting for changes due to new tank design.</t>
+          <t>Design ink maintenance components to be serviceable at service centers after 80k page life is reached.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Prevents contamination and ensures long-term reliability.</t>
+          <t>Facilitates extended product life and supports service contracts.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2209,21 +2209,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Manufacturing</t>
+          <t>Service, Support, End Users</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service station and tank design.</t>
+          <t>Service center readiness, part design.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Aerosol levels remain within safe limits in endurance testing.</t>
+          <t>Service centers can replace ink maintenance parts in &lt;30 minutes with standard tools.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with New Tubes and Weights</t>
+          <t>140ml Black and New CMY Bottles</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Develop new dynamic and force models for the carriage, accounting for new tube routing and increased weights.</t>
+          <t>Introduce 140ml black bottles and new capacity CMY bottles for Magellan platform.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures print quality and mechanical reliability.</t>
+          <t>Supports higher page yields and reduces refill frequency.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2258,21 +2258,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>Consumables Team, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Final tube and tank design.</t>
+          <t>Bottle and tank design.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carriage operates within force and acceleration limits in simulation and physical testing.</t>
+          <t>Bottles meet capacity and compatibility requirements in production units.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2283,45 +2283,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>New IDS Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased duty cycle and page life up to 80k pages.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures consistent reliability and performance over extended use.</t>
+          <t>Improves reliability and serviceability of ink connections.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chassis and component durability.</t>
+          <t>IDS and tank design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paper path components pass 80k page accelerated life test.</t>
+          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable at service centers after 80k page life is reached.</t>
+          <t>Adopt LEBI ink-tank design with increased size, unique keying, and LOI (Level of Integration) One SHAID for security and compatibility.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Facilitates extended product life and supports service contracts.</t>
+          <t>Prevents cross-contamination and supports secure supply chain.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, Support, End Users</t>
+          <t>R&amp;D, Security, Supply Chain</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Service center readiness, part design.</t>
+          <t>Tank and bottle design, SHAID technology.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts in &lt;30 minutes with standard tools.</t>
+          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2381,21 +2381,21 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
+          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Improves reliability and serviceability of ink connections.</t>
+          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
+          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -2430,21 +2430,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Adopt LEBI ink-tank design with increased size, unique keying, and LOI (Level of Integration) One SHAID for security and compatibility.</t>
+          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Prevents cross-contamination and supports secure supply chain.</t>
+          <t>Improves system uptime and reduces service calls.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2454,21 +2454,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Supply Chain</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tank and bottle design, SHAID technology.</t>
+          <t>IDS, firmware development.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
+          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>New PQ Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
+          <t>Ensures consistent output and clear customer communication on ink usage.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2503,21 +2503,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Product Management, R&amp;D, Marketing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IDS and tank design.</t>
+          <t>Page yield testing, IDS design.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
+          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2528,45 +2528,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Improves system uptime and reduces service calls.</t>
+          <t>Reduces development cost and leverages proven, reliable components.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IDS, firmware development.</t>
+          <t>Compatibility with new system design.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
+          <t>Components pass integration and system validation tests in Magellan units.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2577,21 +2577,21 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New PQ Goals and Depletion Definition</t>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ensures consistent output and clear customer communication on ink usage.</t>
+          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2601,21 +2601,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Marketing</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Page yield testing, IDS design.</t>
+          <t>Module sourcing, firmware integration.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
+          <t>Wi-Fi and firmware features pass functional and security testing.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven, reliable components.</t>
+          <t>Ensures compliance with security standards and protects against threats.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2650,21 +2650,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Compatibility with new system design.</t>
+          <t>HW/FW development, certification.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Components pass integration and system validation tests in Magellan units.</t>
+          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2675,45 +2675,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>Support for Consumer, SMB, and Enterprise Segments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
+          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
+          <t>Expands market reach and supports diverse customer requirements.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration.</t>
+          <t>Service and solution development.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware features pass functional and security testing.</t>
+          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2724,45 +2724,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ensures compliance with security standards and protects against threats.</t>
+          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HW/FW development, certification.</t>
+          <t>Software development and integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
+          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2773,45 +2773,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+          <t>Support for Multiple Clients and Drivers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Expands market reach and supports diverse customer requirements.</t>
+          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>IT, End Users, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Service and solution development.</t>
+          <t>Driver and client software development.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
+          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2822,119 +2822,119 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
+          <t>SuperAmp PHA Life at 65K Pages</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
+          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
+          <t>Critical for product reliability and competitive positioning.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT, Product Management</t>
+          <t>R&amp;D, Service, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Software development and integration.</t>
+          <t>PHA design and validation.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
+          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Support for Multiple Clients and Drivers</t>
+          <t>Warranty Life of 2 Years or 80k Pages</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
+          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
+          <t>Aligns with customer expectations and competitive offerings.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IT, End Users, Product Management</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Driver and client software development.</t>
+          <t>System reliability, consumable capacity.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
+          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
+          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Critical for product reliability and competitive positioning.</t>
+          <t>Meets market performance benchmarks and customer needs.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2944,70 +2944,70 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PHA design and validation.</t>
+          <t>Engine design, firmware optimization.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
+          <t>Printer achieves specified throughput in ISO test conditions.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or 80k Pages</t>
+          <t>Serviceability of Maintenance Box</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aligns with customer expectations and competitive offerings.</t>
+          <t>Reduces downtime and service costs.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>System reliability, consumable capacity.</t>
+          <t>Maintenance box design.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
+          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3018,166 +3018,166 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
+          <t>Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Meets market performance benchmarks and customer needs.</t>
+          <t>Allows adaptation to changing market and business needs.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Product Management, Business</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>System design flexibility.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Configurations are validated and available as business needs arise.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Product Management, R&amp;D, End Users</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Engine design, firmware optimization.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Printer achieves specified throughput in ISO test conditions.</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>37</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Serviceability of Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Reduces downtime and service costs.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Maintenance box design.</t>
+          <t>Requires integration with SMB portal and AI solution development.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
+          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>38</v>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
+          <t>Lowest Business TCO for SMB Segment</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
+          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Allows adaptation to changing market and business needs.</t>
+          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Product Management, Business</t>
+          <t>Marketing, BA, Quality, Supplies Quality</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>System design flexibility.</t>
+          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Configurations are validated and available as business needs arise.</t>
+          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, Page 11</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
+          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
+          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3187,46 +3187,46 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solution development.</t>
+          <t>Requires hardware and packaging design for easy replacement.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
+          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lowest Business TCO for SMB Segment</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
+          <t>Prevents user error and potential damage, reducing support incidents.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3236,46 +3236,46 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Marketing, BA, Quality, Supplies Quality</t>
+          <t>Quality, Supplies Quality, BA, Tech Reg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
+          <t>Requires bottle and tank redesign.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
+          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>SMB Portal for Printer Management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
+          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3285,70 +3285,70 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires hardware and packaging design for easy replacement.</t>
+          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
+          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, Page 10</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
+          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Prevents user error and potential damage, reducing support incidents.</t>
+          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA, Tech Reg</t>
+          <t>Marketing, GXD, DVAR, BA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires bottle and tank redesign.</t>
+          <t>Requires integration with HP cloud and service platforms.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
+          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3356,24 +3356,24 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>PDL SKU Performance and Compatibility</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
+          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+          <t>Ensures competitive performance and compliance for managed office environments.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+          <t>Marketing, Tech Reg, Quality, DVAR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
+          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
+          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3401,77 +3401,77 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
+          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marketing, GXD, DVAR, BA</t>
+          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires integration with HP cloud and service platforms.</t>
+          <t>Requires AI software development and hardware compatibility.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, Page 11</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PDL SKU Performance and Compatibility</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
+          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ensures competitive performance and compliance for managed office environments.</t>
+          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3481,95 +3481,95 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marketing, Tech Reg, Quality, DVAR</t>
+          <t>Prod Steward, Marketing, Tech Reg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
+          <t>Requires sourcing and validation of recycled materials.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
+          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Minimal Maintenance Design</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
+          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+          <t>Reduces operational costs and downtime for SMBs.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+          <t>Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Requires AI software development and hardware compatibility.</t>
+          <t>Pending investigation and design validation.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
+          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 11</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Comprehensive Telemetry Support</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
+          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3579,175 +3579,77 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Tech Reg</t>
+          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Requires sourcing and validation of recycled materials.</t>
+          <t>Requires firmware and cloud integration.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
+          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 3, Page 12</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Minimal Maintenance Design</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+          <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Reduces operational costs and downtime for SMBs.</t>
+          <t>Supports modern SMB workflows and BYOD environments.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>GXD, Marketing, BA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pending investigation and design validation.</t>
+          <t>Requires app and firmware compatibility.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 9, Page 10</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Comprehensive Telemetry Support</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Requires firmware and cloud integration.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Mobile Printing and HP App Integration</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Supports modern SMB workflows and BYOD environments.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>GXD, Marketing, BA</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Requires app and firmware compatibility.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, Page 10</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
         <v>12</v>
       </c>
     </row>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -1290,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2332,21 +2332,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adopt LEBI ink-tank design with increased size, unique keying, and LOI (Level of Integration) One SHAID for security and compatibility.</t>
+          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Prevents cross-contamination and supports secure supply chain.</t>
+          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2356,21 +2356,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Supply Chain</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tank and bottle design, SHAID technology.</t>
+          <t>IDS and tank design.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No incorrect bottle insertions in 100 user tests; SHAID passes security audit.</t>
+          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
+          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
+          <t>Improves system uptime and reduces service calls.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>IDS and tank design.</t>
+          <t>IDS, firmware development.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
+          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -2430,21 +2430,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>New PQ Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Improves system uptime and reduces service calls.</t>
+          <t>Ensures consistent output and clear customer communication on ink usage.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2454,21 +2454,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Product Management, R&amp;D, Marketing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IDS, firmware development.</t>
+          <t>Page yield testing, IDS design.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
+          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2479,45 +2479,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New PQ Goals and Depletion Definition</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ensures consistent output and clear customer communication on ink usage.</t>
+          <t>Reduces development cost and leverages proven, reliable components.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Marketing</t>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Page yield testing, IDS design.</t>
+          <t>Compatibility with new system design.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
+          <t>Components pass integration and system validation tests in Magellan units.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2528,45 +2528,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven, reliable components.</t>
+          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Compatibility with new system design.</t>
+          <t>Module sourcing, firmware integration.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Components pass integration and system validation tests in Magellan units.</t>
+          <t>Wi-Fi and firmware features pass functional and security testing.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2577,45 +2577,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
+          <t>Ensures compliance with security standards and protects against threats.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration.</t>
+          <t>HW/FW development, certification.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware features pass functional and security testing.</t>
+          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Support for Consumer, SMB, and Enterprise Segments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ensures compliance with security standards and protects against threats.</t>
+          <t>Expands market reach and supports diverse customer requirements.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HW/FW development, certification.</t>
+          <t>Service and solution development.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
+          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2675,45 +2675,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
+          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Expands market reach and supports diverse customer requirements.</t>
+          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Service and solution development.</t>
+          <t>Software development and integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
+          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2724,21 +2724,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
+          <t>Support for Multiple Clients and Drivers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
+          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT, Product Management</t>
+          <t>IT, End Users, Product Management</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Software development and integration.</t>
+          <t>Driver and client software development.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
+          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2773,70 +2773,70 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Support for Multiple Clients and Drivers</t>
+          <t>SuperAmp PHA Life at 65K Pages</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
+          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
+          <t>Critical for product reliability and competitive positioning.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>IT, End Users, Product Management</t>
+          <t>R&amp;D, Service, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Driver and client software development.</t>
+          <t>PHA design and validation.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
+          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>Warranty Life of 2 Years or 80k Pages</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
+          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Critical for product reliability and competitive positioning.</t>
+          <t>Aligns with customer expectations and competitive offerings.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PHA design and validation.</t>
+          <t>System reliability, consumable capacity.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
+          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2871,21 +2871,21 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or 80k Pages</t>
+          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aligns with customer expectations and competitive offerings.</t>
+          <t>Meets market performance benchmarks and customer needs.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2895,119 +2895,119 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>System reliability, consumable capacity.</t>
+          <t>Engine design, firmware optimization.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
+          <t>Printer achieves specified throughput in ISO test conditions.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
+          <t>Serviceability of Maintenance Box</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
+          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Meets market performance benchmarks and customer needs.</t>
+          <t>Reduces downtime and service costs.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Engine design, firmware optimization.</t>
+          <t>Maintenance box design.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Printer achieves specified throughput in ISO test conditions.</t>
+          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
+          <t>Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs.</t>
+          <t>Allows adaptation to changing market and business needs.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Product Management, Business</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Maintenance box design.</t>
+          <t>System design flexibility.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
+          <t>Configurations are validated and available as business needs arise.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3017,69 +3017,69 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>38</v>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
+          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Allows adaptation to changing market and business needs.</t>
+          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Product Management, Business</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>System design flexibility.</t>
+          <t>Requires integration with SMB portal and AI solution development.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Configurations are validated and available as business needs arise.</t>
+          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Lowest Business TCO for SMB Segment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
+          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
+          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3089,46 +3089,46 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>Marketing, BA, Quality, Supplies Quality</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solution development.</t>
+          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
+          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
+          <t>Magellan MRD, Page 4, Page 11</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lowest Business TCO for SMB Segment</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
+          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
+          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3138,46 +3138,46 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Marketing, BA, Quality, Supplies Quality</t>
+          <t>Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
+          <t>Requires hardware and packaging design for easy replacement.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
+          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+          <t>Prevents user error and potential damage, reducing support incidents.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3187,21 +3187,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>Quality, Supplies Quality, BA, Tech Reg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Requires hardware and packaging design for easy replacement.</t>
+          <t>Requires bottle and tank redesign.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
+          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3209,24 +3209,24 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>SMB Portal for Printer Management</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
+          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Prevents user error and potential damage, reducing support incidents.</t>
+          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3236,119 +3236,119 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA, Tech Reg</t>
+          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires bottle and tank redesign.</t>
+          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
+          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, Page 10</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
+          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+          <t>Marketing, GXD, DVAR, BA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
+          <t>Requires integration with HP cloud and service platforms.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
+          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
+          <t>PDL SKU Performance and Compatibility</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
+          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+          <t>Ensures competitive performance and compliance for managed office environments.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marketing, GXD, DVAR, BA</t>
+          <t>Marketing, Tech Reg, Quality, DVAR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires integration with HP cloud and service platforms.</t>
+          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3356,24 +3356,24 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PDL SKU Performance and Compatibility</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
+          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ensures competitive performance and compliance for managed office environments.</t>
+          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marketing, Tech Reg, Quality, DVAR</t>
+          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
+          <t>Requires AI software development and hardware compatibility.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
+          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3401,28 +3401,28 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, Page 11</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
+          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3432,70 +3432,70 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+          <t>Prod Steward, Marketing, Tech Reg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires AI software development and hardware compatibility.</t>
+          <t>Requires sourcing and validation of recycled materials.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
+          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 11</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Minimal Maintenance Design</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
+          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+          <t>Reduces operational costs and downtime for SMBs.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Tech Reg</t>
+          <t>Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Requires sourcing and validation of recycled materials.</t>
+          <t>Pending investigation and design validation.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
+          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3503,73 +3503,73 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Minimal Maintenance Design</t>
+          <t>Comprehensive Telemetry Support</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Reduces operational costs and downtime for SMBs.</t>
+          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pending investigation and design validation.</t>
+          <t>Requires firmware and cloud integration.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 3, Page 12</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Comprehensive Telemetry Support</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
+          <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+          <t>Supports modern SMB workflows and BYOD environments.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
+          <t>GXD, Marketing, BA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Requires firmware and cloud integration.</t>
+          <t>Requires app and firmware compatibility.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
+          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3597,59 +3597,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
+          <t>Magellan MRD, Page 9, Page 10</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Mobile Printing and HP App Integration</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Supports modern SMB workflows and BYOD environments.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>GXD, Marketing, BA</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Requires app and firmware compatibility.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, Page 10</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
         <v>12</v>
       </c>
     </row>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,160 +430,160 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Department_Requestor</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -710,7 +722,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>The Out-of-Box Experience (OOBE) at 123.hp.com should present only one consistent printer reference name to the customer for HP OfficeJet Pro 9010 series, reducing the current four references to just one.</t>
+          <t>Ensure that only one name/reference is presented to customers for the HP OfficeJet Pro 9010 series on 123.hp.com, to reduce user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -844,7 +856,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and media types for each market segment, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
+          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -978,7 +990,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>The product must operate correctly when placed on uneven surfaces such as sofas, table cloths, or carpets, without input tray sensor flag breakage or similar failures.</t>
+          <t>The printer must operate without functional issues when placed on uneven surfaces such as sofas, tablecloths, or carpets, and must not experience input tray sensor flag breakage under these conditions.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1121,7 +1133,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>The printer must be able to function without failure if tilted left or right up to 20 degrees during printing.</t>
+          <t>Assess functional performance and failure risks if the printer is tilted left or right by 20 degrees during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1267,7 +1279,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>The printer must maintain print quality and function correctly when placed on a moving trolley during operation.</t>
+          <t>The printer must maintain print quality and functionality when printing while placed on a moving or stationary trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1290,61 +1302,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1356,17 +1368,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with 6K Black and 6K CMY Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles capable of delivering 6,000 pages for both black and CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield. CMY bottle size should support &gt;8K yield.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Supports high page yield and efficiency for customers, addressing market demand for higher capacity consumables.</t>
+          <t>Higher yield bottles reduce user intervention and support high-volume printing requirements.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1376,21 +1388,21 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Consumables Team, Product Management</t>
+          <t>R&amp;D, Supply Chain, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with NOA-F, IDS, and existing ink systems.</t>
+          <t>Requires bottle design, compatibility with NOA-F and IDS, and supply chain adjustments.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles must pass page yield testing with at least 6,000 pages for black and CMY, and CMY bottle size must support &gt;8,000 pages under ISO standards.</t>
+          <t>New bottles must pass yield tests demonstrating 6K Black and &gt;8K CMY page output under standard conditions.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1410,12 +1422,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure ink bottles and bottle-to-tank interface are designed for spill-free operation during user installation and replacement.</t>
+          <t>Ensure the new NGB keyed bottles are designed for spill-free reliability during user handling and refilling.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reduces mess and improves user experience, key for customer satisfaction and warranty claims reduction.</t>
+          <t>Prevents ink spills, reducing mess and potential product damage, enhancing user experience.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1425,21 +1437,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Service</t>
+          <t>R&amp;D, End Users, Customer Support</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Linked to bottle design, NOA-F interface, and IDS system.</t>
+          <t>Bottle design and IDS compatibility.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spills during 100 consecutive bottle replacements in lab and field tests.</t>
+          <t>Bottles must pass spill simulation tests with zero leakage in at least 99% of test cases.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1459,12 +1471,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F (New On-demand Air-Filter) with a metal foiled labyrinth design and a lid label, maintaining current push-push and TDF features.</t>
+          <t>Integrate a metal foiled labyrinth and lid label into the NOA-F, with no change to the click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances air management, reliability, and product differentiation.</t>
+          <t>Improves reliability and security of the ink delivery system.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1474,17 +1486,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Consumables Team</t>
+          <t>R&amp;D, Manufacturing, QA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bottle design, IDS, printer assembly process.</t>
+          <t>NOA-F component design, assembly process.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F must pass air flow and reliability tests, and be compatible with existing push-push and TDF mechanisms.</t>
+          <t>NOA-F units must be produced with metal foiled labyrinth and lid label, verified by QA inspection.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1503,17 +1515,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse of Superamp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation for the Magellan platform.</t>
+          <t>Reuse the existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D cost and time to market by reusing proven components.</t>
+          <t>Reduces development time and leverages proven components for reliability.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1523,17 +1535,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and tank systems.</t>
+          <t>Compatibility with new bottle and tank designs.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan units.</t>
+          <t>All new units must function with current Superamp Si PHA and Magi/Nessie inks without performance degradation.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1552,17 +1564,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and IDS Characterization &amp; Modeling</t>
+          <t>Reliability and Performance Characterization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Model and characterize system reliability, including Water Vapor Transmission Rate (WVTR), air gain, flow rate, IDS (Ink Delivery System) performance, startup, and NOA-F End of Life (EOL).</t>
+          <t>Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures robust system design and high product reliability throughout lifecycle.</t>
+          <t>Ensures long-term product reliability and performance.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1572,17 +1584,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires finalized IDS and NOA-F design.</t>
+          <t>Testing infrastructure, finalized designs.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Completion of reliability and IDS models, with all parameters within defined engineering tolerances.</t>
+          <t>Comprehensive test reports for all parameters, with results meeting predefined reliability thresholds.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1606,12 +1618,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and assess impact on print quality (PQ) over time.</t>
+          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prevents degradation of print quality and supports warranty claims.</t>
+          <t>Prevents ink degradation and maintains consistent print quality.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1621,17 +1633,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dependent on ink formulation and tank design.</t>
+          <t>Access to tank samples, ink formulations.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ink remains stable for the duration of warranty period, with no PQ defects observed in accelerated aging tests.</t>
+          <t>Modeling results demonstrate ink stability over the product’s intended lifecycle with no significant PQ impact.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1646,45 +1658,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (likely a tracking or authentication feature) onto the lid of the bottle or tank system.</t>
+          <t>Make NOA-F available as service parts for in-warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enhances traceability, anti-counterfeit, and quality assurance.</t>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Quality Assurance</t>
+          <t>Customer Support, Service Centers, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dependent on Acumen 6 technology readiness.</t>
+          <t>Parts supply chain, service documentation.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Acumen 6 feature is present and functional on all production lids, passing security validation.</t>
+          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1695,45 +1707,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Modify Existing SA 14 Line for NOA-F</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Update the existing SA 14 factory line to support assembly and testing of NOA-F components.</t>
+          <t>Integrate Acumen 6 technology into the lid component.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enables efficient manufacturing and quality control for new components.</t>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>R&amp;D, Security, QA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Final NOA-F design, factory retooling schedule.</t>
+          <t>Lid component design.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SA 14 line is operational for NOA-F production, meeting yield and quality targets.</t>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1744,45 +1756,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Install Magi ink cartridge assembly and labelling tools in Orcus 5 production line.</t>
+          <t>Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Supports production of new ink system and traceability.</t>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, Supply Chain</t>
+          <t>Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orcus 5 readiness, tool procurement.</t>
+          <t>Line modification schedules, tool procurement.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Magi ink cart and labelling tool are installed and validated in Orcus 5 line.</t>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1793,7 +1805,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1802,12 +1814,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable, minimizing service intervention.</t>
+          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reduces service costs and increases customer satisfaction.</t>
+          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1817,21 +1829,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>End Users, Service Centers, Customer Support</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Requires robust design for user handling.</t>
+          <t>Component design, user documentation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions, with &lt;2% error rate in pilot tests.</t>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1842,21 +1854,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Support New Warranty Page Life Goal of 80k Pages</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure system reliability and consumable capacity to support a warranty page life goal of 80,000 pages.</t>
+          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Competitive differentiation and reduced total cost of ownership for customers.</t>
+          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1866,21 +1878,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>End Users, Marketing, Service</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>All system components must meet durability targets.</t>
+          <t>Component durability, consumables yield.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>System passes accelerated life testing to 80,000 pages with no critical failures.</t>
+          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1891,21 +1903,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>Support for 25/20ppm Print Speed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel environmental standards for the PDL SKU.</t>
+          <t>Product must support print speeds of 25ppm (pages per minute) for PDL and 20ppm for standard mode.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Enables sales in regulated markets and supports sustainability goals.</t>
+          <t>Competitive print speeds are required to meet market demands.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1915,21 +1927,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>End Users, Marketing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Product design and documentation updates.</t>
+          <t>Print engine design, firmware.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Product achieves certifications for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+          <t>Printers demonstrate 25ppm (PDL) and 20ppm (standard) speeds in benchmark tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1940,21 +1952,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Use EPS foam packaging for the product.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ensures physical compatibility and maintains compact product footprint.</t>
+          <t>Provides protection during shipping and handling.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1964,21 +1976,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Design, Manufacturing, R&amp;D</t>
+          <t>Manufacturing, Logistics, QA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tank size and chassis design.</t>
+          <t>Packaging design, supplier availability.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Trays operate without interference, and overall product dimensions meet target specifications.</t>
+          <t>Packaging passes drop and vibration tests as per HP standards.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1989,45 +2001,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) for user interface.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Improves usability and aligns with market expectations for modern printers.</t>
+          <t>Meets environmental and regulatory standards, enabling market access.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>End Users, Product Management, UX Design</t>
+          <t>Regulatory, Marketing, QA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Display sourcing, UI software.</t>
+          <t>Product design, documentation.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Display is functional and passes user experience testing.</t>
+          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -2038,21 +2050,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
+          <t>Input and Output Tray Adjustments for Tank Protrusion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Utilize Sayan Sibstar tubes and implement new tube routing and integration for the ink delivery system.</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Improves reliability and supports new tank configuration.</t>
+          <t>Ensures usability and compactness despite larger tank size.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2062,21 +2074,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tube design finalization, chassis integration.</t>
+          <t>Tank design finalization.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tubes are installed without leaks or flow issues in 100 test units.</t>
+          <t>Trays fit seamlessly with tank and pass usability tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2087,21 +2099,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with New Tubes and Weights</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Develop new dynamic and force models for the carriage, accounting for new tube routing and increased weights.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ensures print quality and mechanical reliability.</t>
+          <t>Improves user interface and accessibility.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2111,21 +2123,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Final tube and tank design.</t>
+          <t>UI design, hardware integration.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Carriage operates within force and acceleration limits in simulation and physical testing.</t>
+          <t>Display is functional and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2136,21 +2148,21 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>4-Tube Ink Delivery Platform</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased duty cycle and page life up to 80k pages.</t>
+          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for a 4-tube platform.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ensures consistent reliability and performance over extended use.</t>
+          <t>Supports reliable ink delivery and accommodates new tank configuration.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2160,21 +2172,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chassis and component durability.</t>
+          <t>Tube sourcing, design integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paper path components pass 80k page accelerated life test.</t>
+          <t>Ink delivery system passes flow and reliability tests under all operating conditions.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2185,21 +2197,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable at service centers after 80k page life is reached.</t>
+          <t>Modify the service station for improved aerosol management due to tank changes.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Facilitates extended product life and supports service contracts.</t>
+          <t>Prevents ink mist and maintains print quality and internal cleanliness.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2209,21 +2221,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Service, Support, End Users</t>
+          <t>R&amp;D, QA, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service center readiness, part design.</t>
+          <t>Service station redesign.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts in &lt;30 minutes with standard tools.</t>
+          <t>Aerosol levels remain within safe limits in all operating conditions.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2234,21 +2246,21 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>140ml Black and New CMY Bottles</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Introduce 140ml black bottles and new capacity CMY bottles for Magellan platform.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Supports higher page yields and reduces refill frequency.</t>
+          <t>Ensures mechanical reliability and print quality.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2258,21 +2270,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Consumables Team, R&amp;D, Product Management</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bottle and tank design.</t>
+          <t>Tube and tank design finalization.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bottles meet capacity and compatibility requirements in production units.</t>
+          <t>Carriage system passes stress and dynamic motion tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2283,45 +2295,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
+          <t>Redesign paper path to support increased page life up to 80K pages.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Improves reliability and serviceability of ink connections.</t>
+          <t>Ensures consistent operation and reliability over extended use.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IDS and tank design.</t>
+          <t>Paper path component design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Connections pass leak and durability tests over 5,000 cycles.</t>
+          <t>Paper path passes durability tests for 80K page cycles.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2332,21 +2344,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Ink Maintenance as Serviceable Part</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system to support new tank and ink delivery configuration.</t>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures reliable startup and prevents airlocks in the ink system.</t>
+          <t>Reduces TCO and supports extended product lifecycle.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2356,21 +2368,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Service Centers, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IDS and tank design.</t>
+          <t>Component design, service documentation.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Startup algorithm enables successful priming and no airlocks in 100 consecutive startups.</t>
+          <t>Maintenance part replacement process is validated at service centers.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2381,45 +2393,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithm for Magellan platform, optimizing for reliability and user experience.</t>
+          <t>Develop new startup algorithm and air management for IDS to ensure optimal operation.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Improves system uptime and reduces service calls.</t>
+          <t>Prevents air entrapment and startup failures, enhancing reliability.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>IDS, firmware development.</t>
+          <t>Firmware, IDS hardware.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Algorithm passes field validation with &lt;2% service call rate due to startup issues.</t>
+          <t>Startup algorithm passes reliability tests with zero startup failures in 99% of cases.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2430,21 +2442,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New PQ Goals and Depletion Definition</t>
+          <t>New Print Quality Goals and Depletion Definitions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and ink depletion definitions to align with updated page yield targets.</t>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with increased page yield targets.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures consistent output and clear customer communication on ink usage.</t>
+          <t>Ensures customer satisfaction and accurate yield claims.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2454,21 +2466,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Marketing</t>
+          <t>R&amp;D, Marketing, QA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Page yield testing, IDS design.</t>
+          <t>Yield testing, PQ benchmarking.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PQ goals are met in 95% of test prints; depletion alerts align with actual ink usage in 90% of cases.</t>
+          <t>PQ and depletion metrics are defined and documented; product passes PQ tests at yield endpoints.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2479,41 +2491,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for electronics and power supply.</t>
+          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven, reliable components.</t>
+          <t>Reduces development costs and leverages proven electronics.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Compatibility with new system design.</t>
+          <t>Component compatibility.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Components pass integration and system validation tests in Magellan units.</t>
+          <t>Product passes functional and reliability tests with reused components.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2528,21 +2540,21 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Supports modern connectivity requirements and up-to-date firmware platform.</t>
+          <t>Provides modern wireless networking capabilities.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2552,21 +2564,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>End Users, IT, QA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration.</t>
+          <t>Firmware, hardware integration.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware features pass functional and security testing.</t>
+          <t>Wi-Fi passes connectivity and throughput benchmarks.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2577,41 +2589,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Firmware Dune Integration</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Use Dune firmware in the product.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ensures compliance with security standards and protects against threats.</t>
+          <t>Standardizes software stack and leverages existing capabilities.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HW/FW development, certification.</t>
+          <t>Firmware compatibility.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Product passes internal and external security audits to Gauss4.xx standard.</t>
+          <t>Product passes all functional and regression firmware tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2626,21 +2638,21 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Segments</t>
+          <t>Gauss4.xx Security for HW &amp; FW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ensure the product line and services are tailored to the needs of consumer, SMB, and enterprise segments, including PaaS (Printing as a Service) and flexible onboarding paths.</t>
+          <t>Implement Gauss4.xx security in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Expands market reach and supports diverse customer requirements.</t>
+          <t>Enhances product security and protects against unauthorized access.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2650,21 +2662,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>Security, R&amp;D, QA, End Users</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Service and solution development.</t>
+          <t>HW and FW integration.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Product SKUs and onboarding paths are available and validated for all segments.</t>
+          <t>Security features pass penetration and vulnerability tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2675,21 +2687,21 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Scan Solution and Enterprise Support (WJA, HPSM, JAM)</t>
+          <t>SMB and Enterprise Solution Integration</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate scan solution and enterprise support tools (Web JetAdmin, HP Smart Management, JAM) for manageability.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Essential for SMB and enterprise customers requiring fleet management and advanced features.</t>
+          <t>Expands product applicability to business and enterprise segments.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2699,21 +2711,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT, Product Management</t>
+          <t>SMB and Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Software development and integration.</t>
+          <t>Software and hardware integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Scan and enterprise management features are functional and validated in enterprise deployments.</t>
+          <t>All solutions are functional and pass customer acceptance tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2724,21 +2736,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Support for Multiple Clients and Drivers</t>
+          <t>Clients &amp; Drivers Support</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and clients.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ensures seamless integration in diverse IT environments and simplifies deployment.</t>
+          <t>Maximizes customer compatibility and ease of onboarding.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2748,21 +2760,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IT, End Users, Product Management</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Driver and client software development.</t>
+          <t>Firmware, driver development.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Drivers are available and pass compatibility testing on all supported platforms.</t>
+          <t>All listed drivers and clients are tested and certified for compatibility.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2773,119 +2785,119 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>Business Model Flexibility (Consumer, SMB, Enterprise)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
+          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Critical for product reliability and competitive positioning.</t>
+          <t>Increases market reach and adapts to evolving customer needs.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>Business Development, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PHA design and validation.</t>
+          <t>Solution and service integration.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing to at least 65,000 pages without failure.</t>
+          <t>Product and services are available and functional for all targeted business models.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or 80k Pages</t>
+          <t>Onboarding and S&amp;O Path Support</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Offer a warranty covering either 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Support onboarding through Consumer/HPX path, HP One path, SMB Portal path, and ECP path.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aligns with customer expectations and competitive offerings.</t>
+          <t>Streamlines customer onboarding and setup.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>System reliability, consumable capacity.</t>
+          <t>Software integration.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Product supports warranty claims for 2 years or 80k pages without major issues.</t>
+          <t>All onboarding paths are tested and documented for smooth user experience.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 PPM (PDL: 25/19 PPM)</t>
+          <t>SuperAmp PHA Life at 65K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Achieve print throughput of 25/20 pages per minute (PPM), with PDL SKUs reaching 25/19 PPM.</t>
+          <t>SuperAmp PHA must achieve a life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Meets market performance benchmarks and customer needs.</t>
+          <t>Ensures key component reliability and aligns with warranty/service intervals.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2895,70 +2907,70 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>R&amp;D, QA, Service</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Engine design, firmware optimization.</t>
+          <t>Component durability testing.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Printer achieves specified throughput in ISO test conditions.</t>
+          <t>SuperAmp PHA passes life testing to 65K pages without failure.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>Warranty Life of 2 Years</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ensure maintenance box is easily serviceable for users or service technicians.</t>
+          <t>Product must support a warranty life of 2 years.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs.</t>
+          <t>Meets standard industry warranty expectations.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Marketing, End Users, Service</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Maintenance box design.</t>
+          <t>Component reliability, service support.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in &lt;10 minutes with no special tools.</t>
+          <t>Product warranty is validated for 2 years under normal use conditions.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2969,117 +2981,117 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Serviceability (Maintenance Box)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Design the maintenance box for easy serviceability.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Reduces service time and cost.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Service Centers, End Users</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Maintenance box design.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced or serviced in under 5 minutes by a trained technician.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>36</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Design flexibility to support host 12K-CMYK and trade page 6K configurations, subject to business priorities.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Allows adaptation to changing market and business needs.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Host support for 12K-CMYK and trade page 6K as flexible requirements.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Allows future scalability and market adaptation.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Product Management, Business</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>System design flexibility.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Configurations are validated and available as business needs arise.</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Platform capability.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Product can be configured to support 12K-CMYK and trade page 6K if required.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>0.7</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>AI Productivity and Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify management for SMBs, both today and in the future.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SMBs need easy-to-use, efficient solutions to manage their printers without dedicated IT resources.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Requires integration with SMB portal and AI solution development.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>AI features are available for productivity, scan workflow, and device management; tested with SMB user group and validated to reduce management time by at least 30%.</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lowest Business TCO for SMB Segment</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Magellan must deliver the lowest total cost of ownership (TCO) for SMBs compared to other HP business printers, with minimal intervention required.</t>
+          <t>Integrate advanced AI-based productivity and manageability solutions, including Perfect Print and Perfect Scan, to streamline workflows and device management for SMBs.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cost-efficiency is a top priority for SMBs, and minimizing intervention reduces downtime and support needs.</t>
+          <t>SMBs need efficient, easy-to-manage solutions without dedicated IT teams. AI features differentiate Magellan from competitors and address key customer needs for ROI and efficiency.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3089,46 +3101,46 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Marketing, BA, Quality, Supplies Quality</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires supply chain optimization, efficient ink tank design, and robust hardware.</t>
+          <t>Requires AI software integration, compatible hardware, and SMB portal development.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Independent TCO analysis demonstrates Magellan has the lowest TCO in its class; maintenance intervals are at least 20% longer than previous models.</t>
+          <t>AI-based Perfect Print and Perfect Scan functionalities are available and improve workflow efficiency by at least 20% over standard solutions. Usability validated with non-IT users in SMBs.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Design the maintenance box to be easily replaceable by customers (PHA), with a fallback to service center replacement (MINK) if out of warranty.</t>
+          <t>Design Magellan as HP’s most cost-efficient color printing solution for SMBs, ensuring lowest TCO through high-yield tanks, minimal intervention, and reduced maintenance.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime for SMB customers without IT staff.</t>
+          <t>Cost efficiency is a top priority for SMBs. Lowest TCO is a key differentiator and core value proposition for Magellan.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3138,46 +3150,46 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires hardware and packaging design for easy replacement.</t>
+          <t>Requires high-yield ink tank system, optimized consumables, and robust hardware.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>80% of maintenance box replacements can be performed by end-users without assistance; instructions provided and validated in user testing.</t>
+          <t>TCO for Magellan is demonstrably lower than comparable SMB printers (by at least 10%) in independent testing.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Serviceability – Customer Replaceable Parts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure correct color placement.</t>
+          <t>Enable customer replaceable parts (e.g., maintenance box) and ensure ease of service with PHA (customer replaceable) and MINK (service center, if out of warranty) thresholds.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Prevents user error and potential damage, reducing support incidents.</t>
+          <t>SMBs lack dedicated IT support and require simple, low-cost servicing options to minimize downtime.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3187,21 +3199,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA, Tech Reg</t>
+          <t>['Quality', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Requires bottle and tank redesign.</t>
+          <t>Design for serviceability, documentation, and part supply chain.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>100% of test users are unable to insert the wrong bottle in the wrong tank; passes HP QA and regulatory testing.</t>
+          <t>80%+ of common service events can be handled by customers without professional intervention. User documentation provided.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3209,122 +3221,122 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for managing multiple printers and devices, tailored for unmanaged/lightly managed SMB environments.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SMBs with limited IT support need a simple, centralized management tool.</t>
+          <t>Reduces user error and service calls, improving user experience and reducing support costs.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, DVAR</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires backend integration, UI/UX design, and device telemetry.</t>
+          <t>Requires unique bottle design and printer detection mechanism.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Portal supports management of at least 15 devices, provides actionable alerts, and is validated by SMB user group for usability.</t>
+          <t>Keyed bottles are physically incompatible with incorrect tanks; 100% prevention rate in usability tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
+          <t>Non-PDL SKU – SMB Portal and PaaS Support</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs must support HP's SMB2.0 Solutions, Advanced View SMB portal, and Platform as a Service (PaaS) offerings.</t>
+          <t>For Non-PDL SKUs, integrate SMB2.0 Solutions and Advanced View SMB portal, and ensure support for Printing-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aligns with HP's strategy to accelerate PaaS adoption and value-added solutions for SMBs.</t>
+          <t>SMB customers require centralized, simple management and flexible service models.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marketing, GXD, DVAR, BA</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires integration with HP cloud and service platforms.</t>
+          <t>Portal development, PaaS infrastructure, and integration with printer firmware.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Non-PDL SKU passes solution certification for SMB2.0, Advanced View, and PaaS support.</t>
+          <t>Non-PDL SKUs support SMB portal and PaaS; validated in controlled SMB pilot.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PDL SKU Performance and Compatibility</t>
+          <t>PDL SKU – Enhanced Speed and PDL/PS Support</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PDL SKU must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and meet Blue Angel certification.</t>
+          <t>For PDL SKUs, provide improved print speed (25/20 ppm target) and support for PDL/PS (Page Description Language/PostScript).</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ensures competitive performance and compliance for managed office environments.</t>
+          <t>Higher speed and PDL/PS support are critical for advanced SMB workflows and compatibility.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3334,17 +3346,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marketing, Tech Reg, Quality, DVAR</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware optimization, Blue Angel certification process.</t>
+          <t>Hardware and firmware capable of target speeds and PDL/PS support.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PDL SKU achieves required print speeds, passes PDL/PS compatibility tests, and receives Blue Angel certification.</t>
+          <t>PDL SKUs achieve 25/20 ppm and pass compatibility tests with PDL/PS applications.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3356,73 +3368,73 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Integrate AI-driven 'Perfect Print' and 'Perfect Scan' features for superior output quality and ease of use.</t>
+          <t>Ensure Magellan meets Blue Angel environmental certification requirements for relevant SKUs.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Differentiates Magellan with advanced, user-friendly print and scan experiences.</t>
+          <t>Sustainability is a key differentiator and increasingly required in many markets.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Requires AI software development and hardware compatibility.</t>
+          <t>Design, materials, and manufacturing processes must comply with Blue Angel standards.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>AI features are available in product UI; user testing shows at least 20% improvement in output quality and ease of use over previous models.</t>
+          <t>Blue Angel certification is obtained for designated SKUs before launch.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic content is made from recycled materials, exceeding key competitors.</t>
+          <t>Introduce a replaceable maintenance box as a new feature for Magellan, enabling users to easily maintain printer health.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Addresses increasing demand for sustainable products and differentiates from competitors (Epson 30%, Canon TBC).</t>
+          <t>Addresses new use-cases and pain points for SMBs, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3432,95 +3444,95 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Tech Reg</t>
+          <t>['Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Requires sourcing and validation of recycled materials.</t>
+          <t>Design for user replacement, supply chain for maintenance boxes.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party audit confirm at least 60% RCP; sustainability claim validated by HP and external certifiers.</t>
+          <t>Maintenance box can be replaced by users in under 5 minutes with provided instructions; success rate &gt;95% in testing.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minimal Maintenance Design</t>
+          <t>Consolidated Device Management Portal (SMB Portal)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Design the printer for minimal maintenance, with fewer parts to replace over its lifecycle (subject to ongoing investigation).</t>
+          <t>Develop a consolidated portal for device management, targeting unmanaged and lightly managed SMBs for easy printer monitoring, configuration, and support.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Reduces operational costs and downtime for SMBs.</t>
+          <t>Office managers/generalist IT need simple, centralized management tools to handle multiple printers efficiently.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, BA</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pending investigation and design validation.</t>
+          <t>Portal software development, printer integration, security compliance.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Field data shows at least 15% reduction in maintenance events compared to previous HP SMB printers.</t>
+          <t>Portal allows management of at least 15 printers, with positive usability feedback from SMB pilot users.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Comprehensive Telemetry Support</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Implement robust telemetry to support remote diagnostics, predictive maintenance, and usage analytics for SMBs.</t>
+          <t>Enable seamless mobile printing and integration with the HP App for Magellan printers.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Enables proactive support and enhances device manageability for customers with limited IT resources.</t>
+          <t>Mobile printing is a core SMB use case and a top customer priority.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3530,17 +3542,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, GXD, Quality, DVAR</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Requires firmware and cloud integration.</t>
+          <t>HP App compatibility and printer firmware support.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Telemetry data is accessible via SMB portal and HP support tools; validated in pilot deployments.</t>
+          <t>Users can print from mobile devices via HP App with &gt;98% success rate in user testing.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3548,60 +3560,158 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, Page 12</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>High Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and integration with the HP App for easy setup, printing, and device management.</t>
+          <t>Use at least 60% recycled content plastic (RCP) in Magellan’s construction to exceed competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Supports modern SMB workflows and BYOD environments.</t>
+          <t>Sustainability is a key differentiator and aligns with HP’s environmental goals.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Supply chain sourcing, manufacturing process adaptation.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Material composition verified by third-party audit; 60%+ RCP in all applicable parts.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Warranty – 80,000 Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Provides assurance to SMBs about durability and reliability, supporting purchase decision.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>GXD, Marketing, BA</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Requires app and firmware compatibility.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Printer is discoverable and manageable via HP App; passes mobile printing certification tests.</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hardware reliability and warranty support infrastructure.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Warranty terms are clearly documented and implemented in all regions at launch.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
         <v>0.9</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, Page 10</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Telemetry and Advanced Analytics</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Implement robust telemetry features to collect device usage, health, and performance data for proactive support and insights.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Enables advanced support, predictive maintenance, and continuous improvement for SMB customers.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Telemetry module integration, data privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, anonymized, and accessible in the SMB portal; compliance with privacy regulations demonstrated.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,160 +418,160 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -1306,57 +1294,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,160 +430,160 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -1294,57 +1306,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,160 +418,160 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -1302,61 +1290,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1658,45 +1646,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Make NOA-F available as service parts for in-warranty support.</t>
+          <t>Integrate Acumen 6 technology into the lid component.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enables efficient field service and reduces downtime for customers.</t>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Customer Support, Service Centers, End Users</t>
+          <t>R&amp;D, Security, QA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parts supply chain, service documentation.</t>
+          <t>Lid component design.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1707,45 +1695,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology into the lid component.</t>
+          <t>Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, QA</t>
+          <t>Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lid component design.</t>
+          <t>Line modification schedules, tool procurement.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1756,21 +1744,21 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
+          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ensures manufacturing capability for new components and configurations.</t>
+          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1780,21 +1768,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain</t>
+          <t>End Users, Service Centers, Customer Support</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Line modification schedules, tool procurement.</t>
+          <t>Component design, user documentation.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1805,21 +1793,21 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
+          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces service costs.</t>
+          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1829,17 +1817,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service Centers, Customer Support</t>
+          <t>End Users, Marketing, Service</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design, user documentation.</t>
+          <t>Component durability, consumables yield.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1854,21 +1842,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>Support for 25/20ppm Print Speed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
+          <t>Product must support print speeds of 25ppm (pages per minute) for PDL and 20ppm for standard mode.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
+          <t>Competitive print speeds are required to meet market demands.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1878,21 +1866,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Marketing, Service</t>
+          <t>End Users, Marketing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Component durability, consumables yield.</t>
+          <t>Print engine design, firmware.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
+          <t>Printers demonstrate 25ppm (PDL) and 20ppm (standard) speeds in benchmark tests.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1903,21 +1891,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Support for 25/20ppm Print Speed</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Product must support print speeds of 25ppm (pages per minute) for PDL and 20ppm for standard mode.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Competitive print speeds are required to meet market demands.</t>
+          <t>Meets environmental and regulatory standards, enabling market access.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1927,17 +1915,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>End Users, Marketing</t>
+          <t>Regulatory, Marketing, QA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Print engine design, firmware.</t>
+          <t>Product design, documentation.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Printers demonstrate 25ppm (PDL) and 20ppm (standard) speeds in benchmark tests.</t>
+          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1952,21 +1940,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Input and Output Tray Adjustments for Tank Protrusion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for the product.</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Provides protection during shipping and handling.</t>
+          <t>Ensures usability and compactness despite larger tank size.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1976,17 +1964,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics, QA</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Packaging design, supplier availability.</t>
+          <t>Tank design finalization.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Packaging passes drop and vibration tests as per HP standards.</t>
+          <t>Trays fit seamlessly with tank and pass usability tests.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -2001,41 +1989,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Meets environmental and regulatory standards, enabling market access.</t>
+          <t>Improves user interface and accessibility.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Regulatory, Marketing, QA</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Product design, documentation.</t>
+          <t>UI design, hardware integration.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications.</t>
+          <t>Display is functional and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2050,45 +2038,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Input and Output Tray Adjustments for Tank Protrusion</t>
+          <t>4-Tube Ink Delivery Platform</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for a 4-tube platform.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures usability and compactness despite larger tank size.</t>
+          <t>Supports reliable ink delivery and accommodates new tank configuration.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Industrial Design, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tank design finalization.</t>
+          <t>Tube sourcing, design integration.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Trays fit seamlessly with tank and pass usability tests.</t>
+          <t>Ink delivery system passes flow and reliability tests under all operating conditions.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2099,21 +2087,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Improves user interface and accessibility.</t>
+          <t>Ensures mechanical reliability and print quality.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2123,21 +2111,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UI design, hardware integration.</t>
+          <t>Tube and tank design finalization.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Display is functional and passes usability and reliability tests.</t>
+          <t>Carriage system passes stress and dynamic motion tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2148,21 +2136,21 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4-Tube Ink Delivery Platform</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for a 4-tube platform.</t>
+          <t>Redesign paper path to support increased page life up to 80K pages.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Supports reliable ink delivery and accommodates new tank configuration.</t>
+          <t>Ensures consistent operation and reliability over extended use.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2172,17 +2160,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tube sourcing, design integration.</t>
+          <t>Paper path component design.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ink delivery system passes flow and reliability tests under all operating conditions.</t>
+          <t>Paper path passes durability tests for 80K page cycles.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2197,21 +2185,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Ink Maintenance as Serviceable Part</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Modify the service station for improved aerosol management due to tank changes.</t>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Prevents ink mist and maintains print quality and internal cleanliness.</t>
+          <t>Reduces TCO and supports extended product lifecycle.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2221,17 +2209,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, QA, Manufacturing</t>
+          <t>Service Centers, End Users</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service station redesign.</t>
+          <t>Component design, service documentation.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Aerosol levels remain within safe limits in all operating conditions.</t>
+          <t>Maintenance part replacement process is validated at service centers.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -2246,45 +2234,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>New Make-Break and FI Connection in IDS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Implement new make-break and FI (Fluidic Interface) connection in the Ink Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality.</t>
+          <t>Improves reliability and security of ink delivery.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>R&amp;D, QA, Manufacturing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tube and tank design finalization.</t>
+          <t>IDS redesign, tank and bottle compatibility.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carriage system passes stress and dynamic motion tests.</t>
+          <t>IDS passes connection reliability and security tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2295,21 +2283,21 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life up to 80K pages.</t>
+          <t>Develop new startup algorithm and air management for IDS to ensure optimal operation.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures consistent operation and reliability over extended use.</t>
+          <t>Prevents air entrapment and startup failures, enhancing reliability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2324,16 +2312,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Paper path component design.</t>
+          <t>Firmware, IDS hardware.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paper path passes durability tests for 80K page cycles.</t>
+          <t>Startup algorithm passes reliability tests with zero startup failures in 99% of cases.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2344,21 +2332,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part</t>
+          <t>New Print Quality Goals and Depletion Definitions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with increased page yield targets.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reduces TCO and supports extended product lifecycle.</t>
+          <t>Ensures customer satisfaction and accurate yield claims.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2368,21 +2356,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service Centers, End Users</t>
+          <t>R&amp;D, Marketing, QA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Component design, service documentation.</t>
+          <t>Yield testing, PQ benchmarking.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maintenance part replacement process is validated at service centers.</t>
+          <t>PQ and depletion metrics are defined and documented; product passes PQ tests at yield endpoints.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2393,45 +2381,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Develop new startup algorithm and air management for IDS to ensure optimal operation.</t>
+          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Prevents air entrapment and startup failures, enhancing reliability.</t>
+          <t>Reduces development costs and leverages proven electronics.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Firmware, IDS hardware.</t>
+          <t>Component compatibility.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Startup algorithm passes reliability tests with zero startup failures in 99% of cases.</t>
+          <t>Product passes functional and reliability tests with reused components.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2442,21 +2430,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definitions</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and ink depletion definitions to align with increased page yield targets.</t>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures customer satisfaction and accurate yield claims.</t>
+          <t>Provides modern wireless networking capabilities.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2466,21 +2454,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Marketing, QA</t>
+          <t>End Users, IT, QA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yield testing, PQ benchmarking.</t>
+          <t>Firmware, hardware integration.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PQ and depletion metrics are defined and documented; product passes PQ tests at yield endpoints.</t>
+          <t>Wi-Fi passes connectivity and throughput benchmarks.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2491,21 +2479,21 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Firmware Dune Integration</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
+          <t>Use Dune firmware in the product.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Reduces development costs and leverages proven electronics.</t>
+          <t>Standardizes software stack and leverages existing capabilities.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2515,21 +2503,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Component compatibility.</t>
+          <t>Firmware compatibility.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Product passes functional and reliability tests with reused components.</t>
+          <t>Product passes all functional and regression firmware tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2540,41 +2528,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Gauss4.xx Security for HW &amp; FW</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Implement Gauss4.xx security in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Provides modern wireless networking capabilities.</t>
+          <t>Enhances product security and protects against unauthorized access.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>End Users, IT, QA</t>
+          <t>Security, R&amp;D, QA, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Firmware, hardware integration.</t>
+          <t>HW and FW integration.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Wi-Fi passes connectivity and throughput benchmarks.</t>
+          <t>Security features pass penetration and vulnerability tests.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2589,21 +2577,21 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Firmware Dune Integration</t>
+          <t>SMB and Enterprise Solution Integration</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Use Dune firmware in the product.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Standardizes software stack and leverages existing capabilities.</t>
+          <t>Expands product applicability to business and enterprise segments.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2613,17 +2601,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>SMB and Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Firmware compatibility.</t>
+          <t>Software and hardware integration.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Product passes all functional and regression firmware tests.</t>
+          <t>All solutions are functional and pass customer acceptance tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2638,41 +2626,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security for HW &amp; FW</t>
+          <t>Clients &amp; Drivers Support</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security in both hardware and firmware.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and clients.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Enhances product security and protects against unauthorized access.</t>
+          <t>Maximizes customer compatibility and ease of onboarding.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, QA, End Users</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HW and FW integration.</t>
+          <t>Firmware, driver development.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Security features pass penetration and vulnerability tests.</t>
+          <t>All listed drivers and clients are tested and certified for compatibility.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2687,21 +2675,21 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Solution Integration</t>
+          <t>Business Model Flexibility (Consumer, SMB, Enterprise)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
+          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Expands product applicability to business and enterprise segments.</t>
+          <t>Increases market reach and adapts to evolving customer needs.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2711,17 +2699,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Customers, IT, Product Management</t>
+          <t>Business Development, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Software and hardware integration.</t>
+          <t>Solution and service integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>All solutions are functional and pass customer acceptance tests.</t>
+          <t>Product and services are available and functional for all targeted business models.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2736,21 +2724,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Clients &amp; Drivers Support</t>
+          <t>Onboarding and S&amp;O Path Support</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and clients.</t>
+          <t>Support onboarding through Consumer/HPX path, HP One path, SMB Portal path, and ECP path.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maximizes customer compatibility and ease of onboarding.</t>
+          <t>Streamlines customer onboarding and setup.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2765,16 +2753,16 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Firmware, driver development.</t>
+          <t>Software integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>All listed drivers and clients are tested and certified for compatibility.</t>
+          <t>All onboarding paths are tested and documented for smooth user experience.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2785,143 +2773,143 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Business Model Flexibility (Consumer, SMB, Enterprise)</t>
+          <t>SuperAmp PHA Life at 65K</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker services.</t>
+          <t>SuperAmp PHA must achieve a life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Increases market reach and adapts to evolving customer needs.</t>
+          <t>Ensures key component reliability and aligns with warranty/service intervals.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Business Development, Product Management</t>
+          <t>R&amp;D, QA, Service</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Solution and service integration.</t>
+          <t>Component durability testing.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Product and services are available and functional for all targeted business models.</t>
+          <t>SuperAmp PHA passes life testing to 65K pages without failure.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Onboarding and S&amp;O Path Support</t>
+          <t>Warranty Life of 2 Years</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Support onboarding through Consumer/HPX path, HP One path, SMB Portal path, and ECP path.</t>
+          <t>Product must support a warranty life of 2 years.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Streamlines customer onboarding and setup.</t>
+          <t>Meets standard industry warranty expectations.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>End Users, IT, Support</t>
+          <t>Marketing, End Users, Service</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Software integration.</t>
+          <t>Component reliability, service support.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>All onboarding paths are tested and documented for smooth user experience.</t>
+          <t>Product warranty is validated for 2 years under normal use conditions.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K</t>
+          <t>Serviceability (Maintenance Box)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must achieve a life of 65,000 pages.</t>
+          <t>Design the maintenance box for easy serviceability.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ensures key component reliability and aligns with warranty/service intervals.</t>
+          <t>Reduces service time and cost.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, QA, Service</t>
+          <t>Service Centers, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Component durability testing.</t>
+          <t>Maintenance box design.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing to 65K pages without failure.</t>
+          <t>Maintenance box can be replaced or serviced in under 5 minutes by a trained technician.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2932,166 +2920,166 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years</t>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Product must support a warranty life of 2 years.</t>
+          <t>Host support for 12K-CMYK and trade page 6K as flexible requirements.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Meets standard industry warranty expectations.</t>
+          <t>Allows future scalability and market adaptation.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Platform capability.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Product can be configured to support 12K-CMYK and trade page 6K if required.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-based productivity and manageability solutions, including Perfect Print and Perfect Scan, to streamline workflows and device management for SMBs.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SMBs need efficient, easy-to-manage solutions without dedicated IT teams. AI features differentiate Magellan from competitors and address key customer needs for ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Marketing, End Users, Service</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Component reliability, service support.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Product warranty is validated for 2 years under normal use conditions.</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Requires AI software integration, compatible hardware, and SMB portal development.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AI-based Perfect Print and Perfect Scan functionalities are available and improve workflow efficiency by at least 20% over standard solutions. Usability validated with non-IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.95</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>35</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Serviceability (Maintenance Box)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Design the maintenance box for easy serviceability.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Reduces service time and cost.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Service Centers, End Users</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Maintenance box design.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Maintenance box can be replaced or serviced in under 5 minutes by a trained technician.</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.85</v>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>36</v>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Host support for 12K-CMYK and trade page 6K as flexible requirements.</t>
+          <t>Design Magellan as HP’s most cost-efficient color printing solution for SMBs, ensuring lowest TCO through high-yield tanks, minimal intervention, and reduced maintenance.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Allows future scalability and market adaptation.</t>
+          <t>Cost efficiency is a top priority for SMBs. Lowest TCO is a key differentiator and core value proposition for Magellan.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platform capability.</t>
+          <t>Requires high-yield ink tank system, optimized consumables, and robust hardware.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Product can be configured to support 12K-CMYK and trade page 6K if required.</t>
+          <t>TCO for Magellan is demonstrably lower than comparable SMB printers (by at least 10%) in independent testing.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Serviceability – Customer Replaceable Parts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-based productivity and manageability solutions, including Perfect Print and Perfect Scan, to streamline workflows and device management for SMBs.</t>
+          <t>Enable customer replaceable parts (e.g., maintenance box) and ensure ease of service with PHA (customer replaceable) and MINK (service center, if out of warranty) thresholds.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SMBs need efficient, easy-to-manage solutions without dedicated IT teams. AI features differentiate Magellan from competitors and address key customer needs for ROI and efficiency.</t>
+          <t>SMBs lack dedicated IT support and require simple, low-cost servicing options to minimize downtime.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3101,95 +3089,95 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Quality', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires AI software integration, compatible hardware, and SMB portal development.</t>
+          <t>Design for serviceability, documentation, and part supply chain.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AI-based Perfect Print and Perfect Scan functionalities are available and improve workflow efficiency by at least 20% over standard solutions. Usability validated with non-IT users in SMBs.</t>
+          <t>80%+ of common service events can be handled by customers without professional intervention. User documentation provided.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Design Magellan as HP’s most cost-efficient color printing solution for SMBs, ensuring lowest TCO through high-yield tanks, minimal intervention, and reduced maintenance.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top priority for SMBs. Lowest TCO is a key differentiator and core value proposition for Magellan.</t>
+          <t>Reduces user error and service calls, improving user experience and reducing support costs.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires high-yield ink tank system, optimized consumables, and robust hardware.</t>
+          <t>Requires unique bottle design and printer detection mechanism.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TCO for Magellan is demonstrably lower than comparable SMB printers (by at least 10%) in independent testing.</t>
+          <t>Keyed bottles are physically incompatible with incorrect tanks; 100% prevention rate in usability tests.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Serviceability – Customer Replaceable Parts</t>
+          <t>Non-PDL SKU – SMB Portal and PaaS Support</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Enable customer replaceable parts (e.g., maintenance box) and ensure ease of service with PHA (customer replaceable) and MINK (service center, if out of warranty) thresholds.</t>
+          <t>For Non-PDL SKUs, integrate SMB2.0 Solutions and Advanced View SMB portal, and ensure support for Printing-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT support and require simple, low-cost servicing options to minimize downtime.</t>
+          <t>SMB customers require centralized, simple management and flexible service models.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3199,17 +3187,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Quality', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Design for serviceability, documentation, and part supply chain.</t>
+          <t>Portal development, PaaS infrastructure, and integration with printer firmware.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>80%+ of common service events can be handled by customers without professional intervention. User documentation provided.</t>
+          <t>Non-PDL SKUs support SMB portal and PaaS; validated in controlled SMB pilot.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3217,52 +3205,52 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>PDL SKU – Enhanced Speed and PDL/PS Support</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
+          <t>For PDL SKUs, provide improved print speed (25/20 ppm target) and support for PDL/PS (Page Description Language/PostScript).</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Reduces user error and service calls, improving user experience and reducing support costs.</t>
+          <t>Higher speed and PDL/PS support are critical for advanced SMB workflows and compatibility.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires unique bottle design and printer detection mechanism.</t>
+          <t>Hardware and firmware capable of target speeds and PDL/PS support.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Keyed bottles are physically incompatible with incorrect tanks; 100% prevention rate in usability tests.</t>
+          <t>PDL SKUs achieve 25/20 ppm and pass compatibility tests with PDL/PS applications.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3270,73 +3258,73 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Non-PDL SKU – SMB Portal and PaaS Support</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>For Non-PDL SKUs, integrate SMB2.0 Solutions and Advanced View SMB portal, and ensure support for Printing-as-a-Service (PaaS) models.</t>
+          <t>Ensure Magellan meets Blue Angel environmental certification requirements for relevant SKUs.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SMB customers require centralized, simple management and flexible service models.</t>
+          <t>Sustainability is a key differentiator and increasingly required in many markets.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Portal development, PaaS infrastructure, and integration with printer firmware.</t>
+          <t>Design, materials, and manufacturing processes must comply with Blue Angel standards.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs support SMB portal and PaaS; validated in controlled SMB pilot.</t>
+          <t>Blue Angel certification is obtained for designated SKUs before launch.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PDL SKU – Enhanced Speed and PDL/PS Support</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>For PDL SKUs, provide improved print speed (25/20 ppm target) and support for PDL/PS (Page Description Language/PostScript).</t>
+          <t>Introduce a replaceable maintenance box as a new feature for Magellan, enabling users to easily maintain printer health.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Higher speed and PDL/PS support are critical for advanced SMB workflows and compatibility.</t>
+          <t>Addresses new use-cases and pain points for SMBs, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3346,17 +3334,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
+          <t>['Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hardware and firmware capable of target speeds and PDL/PS support.</t>
+          <t>Design for user replacement, supply chain for maintenance boxes.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PDL SKUs achieve 25/20 ppm and pass compatibility tests with PDL/PS applications.</t>
+          <t>Maintenance box can be replaced by users in under 5 minutes with provided instructions; success rate &gt;95% in testing.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3368,73 +3356,73 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>Consolidated Device Management Portal (SMB Portal)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ensure Magellan meets Blue Angel environmental certification requirements for relevant SKUs.</t>
+          <t>Develop a consolidated portal for device management, targeting unmanaged and lightly managed SMBs for easy printer monitoring, configuration, and support.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and increasingly required in many markets.</t>
+          <t>Office managers/generalist IT need simple, centralized management tools to handle multiple printers efficiently.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Design, materials, and manufacturing processes must comply with Blue Angel standards.</t>
+          <t>Portal software development, printer integration, security compliance.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Blue Angel certification is obtained for designated SKUs before launch.</t>
+          <t>Portal allows management of at least 15 printers, with positive usability feedback from SMB pilot users.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box as a new feature for Magellan, enabling users to easily maintain printer health.</t>
+          <t>Enable seamless mobile printing and integration with the HP App for Magellan printers.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Addresses new use-cases and pain points for SMBs, reducing downtime and service costs.</t>
+          <t>Mobile printing is a core SMB use case and a top customer priority.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3444,17 +3432,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['Quality', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Design for user replacement, supply chain for maintenance boxes.</t>
+          <t>HP App compatibility and printer firmware support.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users in under 5 minutes with provided instructions; success rate &gt;95% in testing.</t>
+          <t>Users can print from mobile devices via HP App with &gt;98% success rate in user testing.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3462,77 +3450,77 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Consolidated Device Management Portal (SMB Portal)</t>
+          <t>High Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal for device management, targeting unmanaged and lightly managed SMBs for easy printer monitoring, configuration, and support.</t>
+          <t>Use at least 60% recycled content plastic (RCP) in Magellan’s construction to exceed competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Office managers/generalist IT need simple, centralized management tools to handle multiple printers efficiently.</t>
+          <t>Sustainability is a key differentiator and aligns with HP’s environmental goals.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Portal software development, printer integration, security compliance.</t>
+          <t>Supply chain sourcing, manufacturing process adaptation.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 15 printers, with positive usability feedback from SMB pilot users.</t>
+          <t>Material composition verified by third-party audit; 60%+ RCP in all applicable parts.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Warranty – 80,000 Pages or 2 Years</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and integration with the HP App for Magellan printers.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mobile printing is a core SMB use case and a top customer priority.</t>
+          <t>Provides assurance to SMBs about durability and reliability, supporting purchase decision.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3542,17 +3530,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HP App compatibility and printer firmware support.</t>
+          <t>Hardware reliability and warranty support infrastructure.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Users can print from mobile devices via HP App with &gt;98% success rate in user testing.</t>
+          <t>Warranty terms are clearly documented and implemented in all regions at launch.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3560,28 +3548,28 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>High Recycled Content Plastic (RCP)</t>
+          <t>Telemetry and Advanced Analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Use at least 60% recycled content plastic (RCP) in Magellan’s construction to exceed competitor benchmarks (Epson 30%, Canon TBC).</t>
+          <t>Implement robust telemetry features to collect device usage, health, and performance data for proactive support and insights.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and aligns with HP’s environmental goals.</t>
+          <t>Enables advanced support, predictive maintenance, and continuous improvement for SMB customers.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3591,17 +3579,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Supply chain sourcing, manufacturing process adaptation.</t>
+          <t>Telemetry module integration, data privacy compliance.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Material composition verified by third-party audit; 60%+ RCP in all applicable parts.</t>
+          <t>Telemetry data is collected, anonymized, and accessible in the SMB portal; compliance with privacy regulations demonstrated.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3609,108 +3597,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Warranty – 80,000 Pages or 2 Years</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Provides assurance to SMBs about durability and reliability, supporting purchase decision.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>['Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Hardware reliability and warranty support infrastructure.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Warranty terms are clearly documented and implemented in all regions at launch.</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Telemetry and Advanced Analytics</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Implement robust telemetry features to collect device usage, health, and performance data for proactive support and insights.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Enables advanced support, predictive maintenance, and continuous improvement for SMB customers.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Telemetry module integration, data privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Telemetry data is collected, anonymized, and accessible in the SMB portal; compliance with privacy regulations demonstrated.</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
         <v>13</v>
       </c>
     </row>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -1290,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,45 +1646,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology into the lid component.</t>
+          <t>Make NOA-F available as service parts for in-warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+          <t>Enables efficient field service and reduces downtime for customers.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, QA</t>
+          <t>Customer Support, Service Centers, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lid component design.</t>
+          <t>Parts supply chain, service documentation.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1695,45 +1695,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
+          <t>Integrate Acumen 6 technology into the lid component.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ensures manufacturing capability for new components and configurations.</t>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Security, QA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Line modification schedules, tool procurement.</t>
+          <t>Lid component design.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
+          <t>Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces service costs.</t>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1768,21 +1768,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>End Users, Service Centers, Customer Support</t>
+          <t>Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Component design, user documentation.</t>
+          <t>Line modification schedules, tool procurement.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
+          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
+          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1817,17 +1817,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Marketing, Service</t>
+          <t>End Users, Service Centers, Customer Support</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component durability, consumables yield.</t>
+          <t>Component design, user documentation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1842,21 +1842,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Support for 25/20ppm Print Speed</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Product must support print speeds of 25ppm (pages per minute) for PDL and 20ppm for standard mode.</t>
+          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Competitive print speeds are required to meet market demands.</t>
+          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1866,21 +1866,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Marketing</t>
+          <t>End Users, Marketing, Service</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Print engine design, firmware.</t>
+          <t>Component durability, consumables yield.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printers demonstrate 25ppm (PDL) and 20ppm (standard) speeds in benchmark tests.</t>
+          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1891,21 +1891,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>Support for 25/20ppm Print Speed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
+          <t>Product must support print speeds of 25ppm (pages per minute) for PDL and 20ppm for standard mode.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Meets environmental and regulatory standards, enabling market access.</t>
+          <t>Competitive print speeds are required to meet market demands.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1915,17 +1915,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Regulatory, Marketing, QA</t>
+          <t>End Users, Marketing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Product design, documentation.</t>
+          <t>Print engine design, firmware.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications.</t>
+          <t>Printers demonstrate 25ppm (PDL) and 20ppm (standard) speeds in benchmark tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1940,21 +1940,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Input and Output Tray Adjustments for Tank Protrusion</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Use EPS foam packaging for the product.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ensures usability and compactness despite larger tank size.</t>
+          <t>Provides protection during shipping and handling.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Industrial Design, End Users</t>
+          <t>Manufacturing, Logistics, QA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tank design finalization.</t>
+          <t>Packaging design, supplier availability.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Trays fit seamlessly with tank and pass usability tests.</t>
+          <t>Packaging passes drop and vibration tests as per HP standards.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1989,41 +1989,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Improves user interface and accessibility.</t>
+          <t>Meets environmental and regulatory standards, enabling market access.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>Regulatory, Marketing, QA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UI design, hardware integration.</t>
+          <t>Product design, documentation.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Display is functional and passes usability and reliability tests.</t>
+          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2038,45 +2038,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4-Tube Ink Delivery Platform</t>
+          <t>Input and Output Tray Adjustments for Tank Protrusion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for a 4-tube platform.</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Supports reliable ink delivery and accommodates new tank configuration.</t>
+          <t>Ensures usability and compactness despite larger tank size.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tube sourcing, design integration.</t>
+          <t>Tank design finalization.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Ink delivery system passes flow and reliability tests under all operating conditions.</t>
+          <t>Trays fit seamlessly with tank and pass usability tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2087,21 +2087,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality.</t>
+          <t>Improves user interface and accessibility.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2111,21 +2111,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tube and tank design finalization.</t>
+          <t>UI design, hardware integration.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Carriage system passes stress and dynamic motion tests.</t>
+          <t>Display is functional and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>4-Tube Ink Delivery Platform</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life up to 80K pages.</t>
+          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for a 4-tube platform.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ensures consistent operation and reliability over extended use.</t>
+          <t>Supports reliable ink delivery and accommodates new tank configuration.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2160,17 +2160,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Paper path component design.</t>
+          <t>Tube sourcing, design integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paper path passes durability tests for 80K page cycles.</t>
+          <t>Ink delivery system passes flow and reliability tests under all operating conditions.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2185,21 +2185,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
+          <t>Modify the service station for improved aerosol management due to tank changes.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reduces TCO and supports extended product lifecycle.</t>
+          <t>Prevents ink mist and maintains print quality and internal cleanliness.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Service Centers, End Users</t>
+          <t>R&amp;D, QA, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Component design, service documentation.</t>
+          <t>Service station redesign.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Maintenance part replacement process is validated at service centers.</t>
+          <t>Aerosol levels remain within safe limits in all operating conditions.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -2234,45 +2234,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection in IDS</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Implement new make-break and FI (Fluidic Interface) connection in the Ink Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Improves reliability and security of ink delivery.</t>
+          <t>Ensures mechanical reliability and print quality.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, QA, Manufacturing</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IDS redesign, tank and bottle compatibility.</t>
+          <t>Tube and tank design finalization.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>IDS passes connection reliability and security tests.</t>
+          <t>Carriage system passes stress and dynamic motion tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2283,21 +2283,21 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Develop new startup algorithm and air management for IDS to ensure optimal operation.</t>
+          <t>Redesign paper path to support increased page life up to 80K pages.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Prevents air entrapment and startup failures, enhancing reliability.</t>
+          <t>Ensures consistent operation and reliability over extended use.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2312,16 +2312,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Firmware, IDS hardware.</t>
+          <t>Paper path component design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Startup algorithm passes reliability tests with zero startup failures in 99% of cases.</t>
+          <t>Paper path passes durability tests for 80K page cycles.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definitions</t>
+          <t>Ink Maintenance as Serviceable Part</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and ink depletion definitions to align with increased page yield targets.</t>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures customer satisfaction and accurate yield claims.</t>
+          <t>Reduces TCO and supports extended product lifecycle.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2356,21 +2356,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Marketing, QA</t>
+          <t>Service Centers, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yield testing, PQ benchmarking.</t>
+          <t>Component design, service documentation.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PQ and depletion metrics are defined and documented; product passes PQ tests at yield endpoints.</t>
+          <t>Maintenance part replacement process is validated at service centers.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2381,45 +2381,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
+          <t>Develop new startup algorithm and air management for IDS to ensure optimal operation.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Reduces development costs and leverages proven electronics.</t>
+          <t>Prevents air entrapment and startup failures, enhancing reliability.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Component compatibility.</t>
+          <t>Firmware, IDS hardware.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Product passes functional and reliability tests with reused components.</t>
+          <t>Startup algorithm passes reliability tests with zero startup failures in 99% of cases.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>New Print Quality Goals and Depletion Definitions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with increased page yield targets.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Provides modern wireless networking capabilities.</t>
+          <t>Ensures customer satisfaction and accurate yield claims.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2454,21 +2454,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>End Users, IT, QA</t>
+          <t>R&amp;D, Marketing, QA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Firmware, hardware integration.</t>
+          <t>Yield testing, PQ benchmarking.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Wi-Fi passes connectivity and throughput benchmarks.</t>
+          <t>PQ and depletion metrics are defined and documented; product passes PQ tests at yield endpoints.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Firmware Dune Integration</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Use Dune firmware in the product.</t>
+          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Standardizes software stack and leverages existing capabilities.</t>
+          <t>Reduces development costs and leverages proven electronics.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2503,21 +2503,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Firmware compatibility.</t>
+          <t>Component compatibility.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Product passes all functional and regression firmware tests.</t>
+          <t>Product passes functional and reliability tests with reused components.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2528,41 +2528,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security for HW &amp; FW</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security in both hardware and firmware.</t>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Enhances product security and protects against unauthorized access.</t>
+          <t>Provides modern wireless networking capabilities.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, QA, End Users</t>
+          <t>End Users, IT, QA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HW and FW integration.</t>
+          <t>Firmware, hardware integration.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Security features pass penetration and vulnerability tests.</t>
+          <t>Wi-Fi passes connectivity and throughput benchmarks.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2577,21 +2577,21 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Solution Integration</t>
+          <t>Firmware Dune Integration</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
+          <t>Use Dune firmware in the product.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Expands product applicability to business and enterprise segments.</t>
+          <t>Standardizes software stack and leverages existing capabilities.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Customers, IT, Product Management</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Software and hardware integration.</t>
+          <t>Firmware compatibility.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>All solutions are functional and pass customer acceptance tests.</t>
+          <t>Product passes all functional and regression firmware tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2626,41 +2626,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clients &amp; Drivers Support</t>
+          <t>Gauss4.xx Security for HW &amp; FW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and clients.</t>
+          <t>Implement Gauss4.xx security in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Maximizes customer compatibility and ease of onboarding.</t>
+          <t>Enhances product security and protects against unauthorized access.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>End Users, IT, Support</t>
+          <t>Security, R&amp;D, QA, End Users</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Firmware, driver development.</t>
+          <t>HW and FW integration.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>All listed drivers and clients are tested and certified for compatibility.</t>
+          <t>Security features pass penetration and vulnerability tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2675,21 +2675,21 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Business Model Flexibility (Consumer, SMB, Enterprise)</t>
+          <t>SMB and Enterprise Solution Integration</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker services.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Increases market reach and adapts to evolving customer needs.</t>
+          <t>Expands product applicability to business and enterprise segments.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2699,17 +2699,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Business Development, Product Management</t>
+          <t>SMB and Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Solution and service integration.</t>
+          <t>Software and hardware integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Product and services are available and functional for all targeted business models.</t>
+          <t>All solutions are functional and pass customer acceptance tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2724,21 +2724,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Onboarding and S&amp;O Path Support</t>
+          <t>Clients &amp; Drivers Support</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Support onboarding through Consumer/HPX path, HP One path, SMB Portal path, and ECP path.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and clients.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Streamlines customer onboarding and setup.</t>
+          <t>Maximizes customer compatibility and ease of onboarding.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2753,16 +2753,16 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Software integration.</t>
+          <t>Firmware, driver development.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>All onboarding paths are tested and documented for smooth user experience.</t>
+          <t>All listed drivers and clients are tested and certified for compatibility.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2773,143 +2773,143 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K</t>
+          <t>Business Model Flexibility (Consumer, SMB, Enterprise)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must achieve a life of 65,000 pages.</t>
+          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ensures key component reliability and aligns with warranty/service intervals.</t>
+          <t>Increases market reach and adapts to evolving customer needs.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R&amp;D, QA, Service</t>
+          <t>Business Development, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Component durability testing.</t>
+          <t>Solution and service integration.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing to 65K pages without failure.</t>
+          <t>Product and services are available and functional for all targeted business models.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years</t>
+          <t>Onboarding and S&amp;O Path Support</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Product must support a warranty life of 2 years.</t>
+          <t>Support onboarding through Consumer/HPX path, HP One path, SMB Portal path, and ECP path.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Meets standard industry warranty expectations.</t>
+          <t>Streamlines customer onboarding and setup.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Marketing, End Users, Service</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Component reliability, service support.</t>
+          <t>Software integration.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Product warranty is validated for 2 years under normal use conditions.</t>
+          <t>All onboarding paths are tested and documented for smooth user experience.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Serviceability (Maintenance Box)</t>
+          <t>SuperAmp PHA Life at 65K</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Design the maintenance box for easy serviceability.</t>
+          <t>SuperAmp PHA must achieve a life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Reduces service time and cost.</t>
+          <t>Ensures key component reliability and aligns with warranty/service intervals.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Service Centers, End Users</t>
+          <t>R&amp;D, QA, Service</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Maintenance box design.</t>
+          <t>Component durability testing.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced or serviced in under 5 minutes by a trained technician.</t>
+          <t>SuperAmp PHA passes life testing to 65K pages without failure.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2920,166 +2920,166 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>34</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Product must support a warranty life of 2 years.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Meets standard industry warranty expectations.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Marketing, End Users, Service</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Component reliability, service support.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Product warranty is validated for 2 years under normal use conditions.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>35</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Design the maintenance box for easy serviceability.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Reduces service time and cost.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Service Centers, End Users</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Maintenance box design.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced or serviced in under 5 minutes by a trained technician.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
         <v>36</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Host support for 12K-CMYK and trade page 6K as flexible requirements.</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Allows future scalability and market adaptation.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Product Management, R&amp;D</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Platform capability.</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Product can be configured to support 12K-CMYK and trade page 6K if required.</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I36" t="n">
         <v>0.7</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>AI Productivity and Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Integrate advanced AI-based productivity and manageability solutions, including Perfect Print and Perfect Scan, to streamline workflows and device management for SMBs.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SMBs need efficient, easy-to-manage solutions without dedicated IT teams. AI features differentiate Magellan from competitors and address key customer needs for ROI and efficiency.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Requires AI software integration, compatible hardware, and SMB portal development.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>AI-based Perfect Print and Perfect Scan functionalities are available and improve workflow efficiency by at least 20% over standard solutions. Usability validated with non-IT users in SMBs.</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Design Magellan as HP’s most cost-efficient color printing solution for SMBs, ensuring lowest TCO through high-yield tanks, minimal intervention, and reduced maintenance.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Cost efficiency is a top priority for SMBs. Lowest TCO is a key differentiator and core value proposition for Magellan.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Requires high-yield ink tank system, optimized consumables, and robust hardware.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>TCO for Magellan is demonstrably lower than comparable SMB printers (by at least 10%) in independent testing.</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Serviceability – Customer Replaceable Parts</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Enable customer replaceable parts (e.g., maintenance box) and ensure ease of service with PHA (customer replaceable) and MINK (service center, if out of warranty) thresholds.</t>
+          <t>Integrate advanced AI-based productivity and manageability solutions, including Perfect Print and Perfect Scan, to streamline workflows and device management for SMBs.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT support and require simple, low-cost servicing options to minimize downtime.</t>
+          <t>SMBs need efficient, easy-to-manage solutions without dedicated IT teams. AI features differentiate Magellan from competitors and address key customer needs for ROI and efficiency.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3089,95 +3089,95 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Quality', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Design for serviceability, documentation, and part supply chain.</t>
+          <t>Requires AI software integration, compatible hardware, and SMB portal development.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>80%+ of common service events can be handled by customers without professional intervention. User documentation provided.</t>
+          <t>AI-based Perfect Print and Perfect Scan functionalities are available and improve workflow efficiency by at least 20% over standard solutions. Usability validated with non-IT users in SMBs.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
+          <t>Design Magellan as HP’s most cost-efficient color printing solution for SMBs, ensuring lowest TCO through high-yield tanks, minimal intervention, and reduced maintenance.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Reduces user error and service calls, improving user experience and reducing support costs.</t>
+          <t>Cost efficiency is a top priority for SMBs. Lowest TCO is a key differentiator and core value proposition for Magellan.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires unique bottle design and printer detection mechanism.</t>
+          <t>Requires high-yield ink tank system, optimized consumables, and robust hardware.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Keyed bottles are physically incompatible with incorrect tanks; 100% prevention rate in usability tests.</t>
+          <t>TCO for Magellan is demonstrably lower than comparable SMB printers (by at least 10%) in independent testing.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Non-PDL SKU – SMB Portal and PaaS Support</t>
+          <t>Serviceability – Customer Replaceable Parts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>For Non-PDL SKUs, integrate SMB2.0 Solutions and Advanced View SMB portal, and ensure support for Printing-as-a-Service (PaaS) models.</t>
+          <t>Enable customer replaceable parts (e.g., maintenance box) and ensure ease of service with PHA (customer replaceable) and MINK (service center, if out of warranty) thresholds.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SMB customers require centralized, simple management and flexible service models.</t>
+          <t>SMBs lack dedicated IT support and require simple, low-cost servicing options to minimize downtime.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Quality', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Portal development, PaaS infrastructure, and integration with printer firmware.</t>
+          <t>Design for serviceability, documentation, and part supply chain.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs support SMB portal and PaaS; validated in controlled SMB pilot.</t>
+          <t>80%+ of common service events can be handled by customers without professional intervention. User documentation provided.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3205,52 +3205,52 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PDL SKU – Enhanced Speed and PDL/PS Support</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>For PDL SKUs, provide improved print speed (25/20 ppm target) and support for PDL/PS (Page Description Language/PostScript).</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Higher speed and PDL/PS support are critical for advanced SMB workflows and compatibility.</t>
+          <t>Reduces user error and service calls, improving user experience and reducing support costs.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hardware and firmware capable of target speeds and PDL/PS support.</t>
+          <t>Requires unique bottle design and printer detection mechanism.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PDL SKUs achieve 25/20 ppm and pass compatibility tests with PDL/PS applications.</t>
+          <t>Keyed bottles are physically incompatible with incorrect tanks; 100% prevention rate in usability tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3258,73 +3258,73 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>Non-PDL SKU – SMB Portal and PaaS Support</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ensure Magellan meets Blue Angel environmental certification requirements for relevant SKUs.</t>
+          <t>For Non-PDL SKUs, integrate SMB2.0 Solutions and Advanced View SMB portal, and ensure support for Printing-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and increasingly required in many markets.</t>
+          <t>SMB customers require centralized, simple management and flexible service models.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Design, materials, and manufacturing processes must comply with Blue Angel standards.</t>
+          <t>Portal development, PaaS infrastructure, and integration with printer firmware.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Blue Angel certification is obtained for designated SKUs before launch.</t>
+          <t>Non-PDL SKUs support SMB portal and PaaS; validated in controlled SMB pilot.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>PDL SKU – Enhanced Speed and PDL/PS Support</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box as a new feature for Magellan, enabling users to easily maintain printer health.</t>
+          <t>For PDL SKUs, provide improved print speed (25/20 ppm target) and support for PDL/PS (Page Description Language/PostScript).</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Addresses new use-cases and pain points for SMBs, reducing downtime and service costs.</t>
+          <t>Higher speed and PDL/PS support are critical for advanced SMB workflows and compatibility.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3334,17 +3334,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Quality', 'Prod Steward', 'BA']</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Design for user replacement, supply chain for maintenance boxes.</t>
+          <t>Hardware and firmware capable of target speeds and PDL/PS support.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users in under 5 minutes with provided instructions; success rate &gt;95% in testing.</t>
+          <t>PDL SKUs achieve 25/20 ppm and pass compatibility tests with PDL/PS applications.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3356,73 +3356,73 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Consolidated Device Management Portal (SMB Portal)</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal for device management, targeting unmanaged and lightly managed SMBs for easy printer monitoring, configuration, and support.</t>
+          <t>Ensure Magellan meets Blue Angel environmental certification requirements for relevant SKUs.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Office managers/generalist IT need simple, centralized management tools to handle multiple printers efficiently.</t>
+          <t>Sustainability is a key differentiator and increasingly required in many markets.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Portal software development, printer integration, security compliance.</t>
+          <t>Design, materials, and manufacturing processes must comply with Blue Angel standards.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 15 printers, with positive usability feedback from SMB pilot users.</t>
+          <t>Blue Angel certification is obtained for designated SKUs before launch.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and integration with the HP App for Magellan printers.</t>
+          <t>Introduce a replaceable maintenance box as a new feature for Magellan, enabling users to easily maintain printer health.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mobile printing is a core SMB use case and a top customer priority.</t>
+          <t>Addresses new use-cases and pain points for SMBs, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>['Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HP App compatibility and printer firmware support.</t>
+          <t>Design for user replacement, supply chain for maintenance boxes.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Users can print from mobile devices via HP App with &gt;98% success rate in user testing.</t>
+          <t>Maintenance box can be replaced by users in under 5 minutes with provided instructions; success rate &gt;95% in testing.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3450,77 +3450,77 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>High Recycled Content Plastic (RCP)</t>
+          <t>Consolidated Device Management Portal (SMB Portal)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Use at least 60% recycled content plastic (RCP) in Magellan’s construction to exceed competitor benchmarks (Epson 30%, Canon TBC).</t>
+          <t>Develop a consolidated portal for device management, targeting unmanaged and lightly managed SMBs for easy printer monitoring, configuration, and support.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and aligns with HP’s environmental goals.</t>
+          <t>Office managers/generalist IT need simple, centralized management tools to handle multiple printers efficiently.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Supply chain sourcing, manufacturing process adaptation.</t>
+          <t>Portal software development, printer integration, security compliance.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Material composition verified by third-party audit; 60%+ RCP in all applicable parts.</t>
+          <t>Portal allows management of at least 15 printers, with positive usability feedback from SMB pilot users.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Warranty – 80,000 Pages or 2 Years</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
+          <t>Enable seamless mobile printing and integration with the HP App for Magellan printers.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Provides assurance to SMBs about durability and reliability, supporting purchase decision.</t>
+          <t>Mobile printing is a core SMB use case and a top customer priority.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3530,17 +3530,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hardware reliability and warranty support infrastructure.</t>
+          <t>HP App compatibility and printer firmware support.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Warranty terms are clearly documented and implemented in all regions at launch.</t>
+          <t>Users can print from mobile devices via HP App with &gt;98% success rate in user testing.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3548,28 +3548,28 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Telemetry and Advanced Analytics</t>
+          <t>High Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Implement robust telemetry features to collect device usage, health, and performance data for proactive support and insights.</t>
+          <t>Use at least 60% recycled content plastic (RCP) in Magellan’s construction to exceed competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Enables advanced support, predictive maintenance, and continuous improvement for SMB customers.</t>
+          <t>Sustainability is a key differentiator and aligns with HP’s environmental goals.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Telemetry module integration, data privacy compliance.</t>
+          <t>Supply chain sourcing, manufacturing process adaptation.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Telemetry data is collected, anonymized, and accessible in the SMB portal; compliance with privacy regulations demonstrated.</t>
+          <t>Material composition verified by third-party audit; 60%+ RCP in all applicable parts.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3597,10 +3597,108 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Warranty – 80,000 Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Provides assurance to SMBs about durability and reliability, supporting purchase decision.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hardware reliability and warranty support infrastructure.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Warranty terms are clearly documented and implemented in all regions at launch.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Telemetry and Advanced Analytics</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Implement robust telemetry features to collect device usage, health, and performance data for proactive support and insights.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Enables advanced support, predictive maintenance, and continuous improvement for SMB customers.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Telemetry module integration, data privacy compliance.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, anonymized, and accessible in the SMB portal; compliance with privacy regulations demonstrated.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="K49" t="n">
         <v>13</v>
       </c>
     </row>

--- a/consolidation/output/duplicates.xlsx
+++ b/consolidation/output/duplicates.xlsx
@@ -1290,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,45 +1646,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Make NOA-F available as service parts for in-warranty support.</t>
+          <t>Integrate Acumen 6 technology into the lid component.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enables efficient field service and reduces downtime for customers.</t>
+          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Customer Support, Service Centers, End Users</t>
+          <t>R&amp;D, Security, QA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parts supply chain, service documentation.</t>
+          <t>Lid component design.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F parts are listed in service catalogs and available for warranty claims.</t>
+          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1695,45 +1695,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology into the lid component.</t>
+          <t>Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enhances product security, authentication, or performance (context-specific, assumed security/authentication).</t>
+          <t>Ensures manufacturing capability for new components and configurations.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, QA</t>
+          <t>Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lid component design.</t>
+          <t>Line modification schedules, tool procurement.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lid passes Acumen 6 functionality tests as specified in technical documentation.</t>
+          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify SA 14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provision molds for 1 to 4 new keyed caps.</t>
+          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ensures manufacturing capability for new components and configurations.</t>
+          <t>Improves serviceability and reduces service costs.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1768,21 +1768,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Supply Chain</t>
+          <t>End Users, Service Centers, Customer Support</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Line modification schedules, tool procurement.</t>
+          <t>Component design, user documentation.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Production lines are updated and validated for new parts with successful pilot runs.</t>
+          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer replaceable.</t>
+          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces service costs.</t>
+          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1817,17 +1817,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service Centers, Customer Support</t>
+          <t>End Users, Marketing, Service</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design, user documentation.</t>
+          <t>Component durability, consumables yield.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F following provided instructions without tools.</t>
+          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1842,21 +1842,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>Support for 25/20ppm Print Speed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
+          <t>Product must support print speeds of 25ppm (pages per minute) for PDL and 20ppm for standard mode.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Meets market expectations for durability and reduces TCO (Total Cost of Ownership) for customers.</t>
+          <t>Competitive print speeds are required to meet market demands.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1866,21 +1866,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Marketing, Service</t>
+          <t>End Users, Marketing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Component durability, consumables yield.</t>
+          <t>Print engine design, firmware.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printers must pass accelerated life testing to 80K pages with no critical failures.</t>
+          <t>Printers demonstrate 25ppm (PDL) and 20ppm (standard) speeds in benchmark tests.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1891,21 +1891,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Support for 25/20ppm Print Speed</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Product must support print speeds of 25ppm (pages per minute) for PDL and 20ppm for standard mode.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Competitive print speeds are required to meet market demands.</t>
+          <t>Meets environmental and regulatory standards, enabling market access.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1915,17 +1915,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>End Users, Marketing</t>
+          <t>Regulatory, Marketing, QA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Print engine design, firmware.</t>
+          <t>Product design, documentation.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Printers demonstrate 25ppm (PDL) and 20ppm (standard) speeds in benchmark tests.</t>
+          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1940,21 +1940,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Input and Output Tray Adjustments for Tank Protrusion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for the product.</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Provides protection during shipping and handling.</t>
+          <t>Ensures usability and compactness despite larger tank size.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics, QA</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Packaging design, supplier availability.</t>
+          <t>Tank design finalization.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Packaging passes drop and vibration tests as per HP standards.</t>
+          <t>Trays fit seamlessly with tank and pass usability tests.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1989,41 +1989,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for the PDL SKU.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Meets environmental and regulatory standards, enabling market access.</t>
+          <t>Improves user interface and accessibility.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Regulatory, Marketing, QA</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Product design, documentation.</t>
+          <t>UI design, hardware integration.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications.</t>
+          <t>Display is functional and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2038,45 +2038,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Input and Output Tray Adjustments for Tank Protrusion</t>
+          <t>4-Tube Ink Delivery Platform</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for a 4-tube platform.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures usability and compactness despite larger tank size.</t>
+          <t>Supports reliable ink delivery and accommodates new tank configuration.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Industrial Design, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tank design finalization.</t>
+          <t>Tube sourcing, design integration.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Trays fit seamlessly with tank and pass usability tests.</t>
+          <t>Ink delivery system passes flow and reliability tests under all operating conditions.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2087,21 +2087,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Improves user interface and accessibility.</t>
+          <t>Ensures mechanical reliability and print quality.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2111,21 +2111,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UI design, hardware integration.</t>
+          <t>Tube and tank design finalization.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Display is functional and passes usability and reliability tests.</t>
+          <t>Carriage system passes stress and dynamic motion tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4-Tube Ink Delivery Platform</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for a 4-tube platform.</t>
+          <t>Redesign paper path to support increased page life up to 80K pages.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Supports reliable ink delivery and accommodates new tank configuration.</t>
+          <t>Ensures consistent operation and reliability over extended use.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2160,17 +2160,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tube sourcing, design integration.</t>
+          <t>Paper path component design.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ink delivery system passes flow and reliability tests under all operating conditions.</t>
+          <t>Paper path passes durability tests for 80K page cycles.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2185,21 +2185,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Ink Maintenance as Serviceable Part</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Modify the service station for improved aerosol management due to tank changes.</t>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Prevents ink mist and maintains print quality and internal cleanliness.</t>
+          <t>Reduces TCO and supports extended product lifecycle.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, QA, Manufacturing</t>
+          <t>Service Centers, End Users</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service station redesign.</t>
+          <t>Component design, service documentation.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Aerosol levels remain within safe limits in all operating conditions.</t>
+          <t>Maintenance part replacement process is validated at service centers.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -2234,45 +2234,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>New Make-Break and FI Connection in IDS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Implement new make-break and FI (Fluidic Interface) connection in the Ink Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality.</t>
+          <t>Improves reliability and security of ink delivery.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>R&amp;D, QA, Manufacturing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tube and tank design finalization.</t>
+          <t>IDS redesign, tank and bottle compatibility.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carriage system passes stress and dynamic motion tests.</t>
+          <t>IDS passes connection reliability and security tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2283,21 +2283,21 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life up to 80K pages.</t>
+          <t>Develop new startup algorithm and air management for IDS to ensure optimal operation.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures consistent operation and reliability over extended use.</t>
+          <t>Prevents air entrapment and startup failures, enhancing reliability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2312,16 +2312,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Paper path component design.</t>
+          <t>Firmware, IDS hardware.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paper path passes durability tests for 80K page cycles.</t>
+          <t>Startup algorithm passes reliability tests with zero startup failures in 99% of cases.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part</t>
+          <t>New Print Quality Goals and Depletion Definitions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
+          <t>Set new print quality (PQ) goals and ink depletion definitions to align with increased page yield targets.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reduces TCO and supports extended product lifecycle.</t>
+          <t>Ensures customer satisfaction and accurate yield claims.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2356,21 +2356,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service Centers, End Users</t>
+          <t>R&amp;D, Marketing, QA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Component design, service documentation.</t>
+          <t>Yield testing, PQ benchmarking.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maintenance part replacement process is validated at service centers.</t>
+          <t>PQ and depletion metrics are defined and documented; product passes PQ tests at yield endpoints.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2381,45 +2381,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Develop new startup algorithm and air management for IDS to ensure optimal operation.</t>
+          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Prevents air entrapment and startup failures, enhancing reliability.</t>
+          <t>Reduces development costs and leverages proven electronics.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Firmware, IDS hardware.</t>
+          <t>Component compatibility.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Startup algorithm passes reliability tests with zero startup failures in 99% of cases.</t>
+          <t>Product passes functional and reliability tests with reused components.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definitions</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and ink depletion definitions to align with increased page yield targets.</t>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures customer satisfaction and accurate yield claims.</t>
+          <t>Provides modern wireless networking capabilities.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2454,21 +2454,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Marketing, QA</t>
+          <t>End Users, IT, QA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yield testing, PQ benchmarking.</t>
+          <t>Firmware, hardware integration.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PQ and depletion metrics are defined and documented; product passes PQ tests at yield endpoints.</t>
+          <t>Wi-Fi passes connectivity and throughput benchmarks.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Firmware Dune Integration</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
+          <t>Use Dune firmware in the product.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Reduces development costs and leverages proven electronics.</t>
+          <t>Standardizes software stack and leverages existing capabilities.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2503,21 +2503,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Component compatibility.</t>
+          <t>Firmware compatibility.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Product passes functional and reliability tests with reused components.</t>
+          <t>Product passes all functional and regression firmware tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2528,41 +2528,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Gauss4.xx Security for HW &amp; FW</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Implement Gauss4.xx security in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Provides modern wireless networking capabilities.</t>
+          <t>Enhances product security and protects against unauthorized access.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>End Users, IT, QA</t>
+          <t>Security, R&amp;D, QA, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Firmware, hardware integration.</t>
+          <t>HW and FW integration.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Wi-Fi passes connectivity and throughput benchmarks.</t>
+          <t>Security features pass penetration and vulnerability tests.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2577,21 +2577,21 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Firmware Dune Integration</t>
+          <t>SMB and Enterprise Solution Integration</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Use Dune firmware in the product.</t>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Standardizes software stack and leverages existing capabilities.</t>
+          <t>Expands product applicability to business and enterprise segments.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>SMB and Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Firmware compatibility.</t>
+          <t>Software and hardware integration.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Product passes all functional and regression firmware tests.</t>
+          <t>All solutions are functional and pass customer acceptance tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2626,41 +2626,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security for HW &amp; FW</t>
+          <t>Clients &amp; Drivers Support</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security in both hardware and firmware.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and clients.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Enhances product security and protects against unauthorized access.</t>
+          <t>Maximizes customer compatibility and ease of onboarding.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, QA, End Users</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HW and FW integration.</t>
+          <t>Firmware, driver development.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Security features pass penetration and vulnerability tests.</t>
+          <t>All listed drivers and clients are tested and certified for compatibility.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2675,21 +2675,21 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Solution Integration</t>
+          <t>Business Model Flexibility (Consumer, SMB, Enterprise)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
+          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Expands product applicability to business and enterprise segments.</t>
+          <t>Increases market reach and adapts to evolving customer needs.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2699,17 +2699,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Customers, IT, Product Management</t>
+          <t>Business Development, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Software and hardware integration.</t>
+          <t>Solution and service integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>All solutions are functional and pass customer acceptance tests.</t>
+          <t>Product and services are available and functional for all targeted business models.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2724,21 +2724,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Clients &amp; Drivers Support</t>
+          <t>Onboarding and S&amp;O Path Support</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and clients.</t>
+          <t>Support onboarding through Consumer/HPX path, HP One path, SMB Portal path, and ECP path.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maximizes customer compatibility and ease of onboarding.</t>
+          <t>Streamlines customer onboarding and setup.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2753,16 +2753,16 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Firmware, driver development.</t>
+          <t>Software integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>All listed drivers and clients are tested and certified for compatibility.</t>
+          <t>All onboarding paths are tested and documented for smooth user experience.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2773,143 +2773,143 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Business Model Flexibility (Consumer, SMB, Enterprise)</t>
+          <t>SuperAmp PHA Life at 65K</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS and WorkFromHome/Flexworker services.</t>
+          <t>SuperAmp PHA must achieve a life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Increases market reach and adapts to evolving customer needs.</t>
+          <t>Ensures key component reliability and aligns with warranty/service intervals.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Business Development, Product Management</t>
+          <t>R&amp;D, QA, Service</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Solution and service integration.</t>
+          <t>Component durability testing.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Product and services are available and functional for all targeted business models.</t>
+          <t>SuperAmp PHA passes life testing to 65K pages without failure.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Onboarding and S&amp;O Path Support</t>
+          <t>Warranty Life of 2 Years</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Support onboarding through Consumer/HPX path, HP One path, SMB Portal path, and ECP path.</t>
+          <t>Product must support a warranty life of 2 years.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Streamlines customer onboarding and setup.</t>
+          <t>Meets standard industry warranty expectations.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>End Users, IT, Support</t>
+          <t>Marketing, End Users, Service</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Software integration.</t>
+          <t>Component reliability, service support.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>All onboarding paths are tested and documented for smooth user experience.</t>
+          <t>Product warranty is validated for 2 years under normal use conditions.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K</t>
+          <t>Serviceability (Maintenance Box)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must achieve a life of 65,000 pages.</t>
+          <t>Design the maintenance box for easy serviceability.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ensures key component reliability and aligns with warranty/service intervals.</t>
+          <t>Reduces service time and cost.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, QA, Service</t>
+          <t>Service Centers, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Component durability testing.</t>
+          <t>Maintenance box design.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing to 65K pages without failure.</t>
+          <t>Maintenance box can be replaced or serviced in under 5 minutes by a trained technician.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2920,166 +2920,166 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years</t>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Product must support a warranty life of 2 years.</t>
+          <t>Host support for 12K-CMYK and trade page 6K as flexible requirements.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Meets standard industry warranty expectations.</t>
+          <t>Allows future scalability and market adaptation.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Platform capability.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Product can be configured to support 12K-CMYK and trade page 6K if required.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-based productivity and manageability solutions, including Perfect Print and Perfect Scan, to streamline workflows and device management for SMBs.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SMBs need efficient, easy-to-manage solutions without dedicated IT teams. AI features differentiate Magellan from competitors and address key customer needs for ROI and efficiency.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Marketing, End Users, Service</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Component reliability, service support.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Product warranty is validated for 2 years under normal use conditions.</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Requires AI software integration, compatible hardware, and SMB portal development.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AI-based Perfect Print and Perfect Scan functionalities are available and improve workflow efficiency by at least 20% over standard solutions. Usability validated with non-IT users in SMBs.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.95</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>35</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Serviceability (Maintenance Box)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Design the maintenance box for easy serviceability.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Reduces service time and cost.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Service Centers, End Users</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Maintenance box design.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Maintenance box can be replaced or serviced in under 5 minutes by a trained technician.</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.85</v>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>36</v>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K (Flexible)</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Host support for 12K-CMYK and trade page 6K as flexible requirements.</t>
+          <t>Design Magellan as HP’s most cost-efficient color printing solution for SMBs, ensuring lowest TCO through high-yield tanks, minimal intervention, and reduced maintenance.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Allows future scalability and market adaptation.</t>
+          <t>Cost efficiency is a top priority for SMBs. Lowest TCO is a key differentiator and core value proposition for Magellan.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platform capability.</t>
+          <t>Requires high-yield ink tank system, optimized consumables, and robust hardware.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Product can be configured to support 12K-CMYK and trade page 6K if required.</t>
+          <t>TCO for Magellan is demonstrably lower than comparable SMB printers (by at least 10%) in independent testing.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Serviceability – Customer Replaceable Parts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-based productivity and manageability solutions, including Perfect Print and Perfect Scan, to streamline workflows and device management for SMBs.</t>
+          <t>Enable customer replaceable parts (e.g., maintenance box) and ensure ease of service with PHA (customer replaceable) and MINK (service center, if out of warranty) thresholds.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SMBs need efficient, easy-to-manage solutions without dedicated IT teams. AI features differentiate Magellan from competitors and address key customer needs for ROI and efficiency.</t>
+          <t>SMBs lack dedicated IT support and require simple, low-cost servicing options to minimize downtime.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3089,95 +3089,95 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Quality', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires AI software integration, compatible hardware, and SMB portal development.</t>
+          <t>Design for serviceability, documentation, and part supply chain.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AI-based Perfect Print and Perfect Scan functionalities are available and improve workflow efficiency by at least 20% over standard solutions. Usability validated with non-IT users in SMBs.</t>
+          <t>80%+ of common service events can be handled by customers without professional intervention. User documentation provided.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Design Magellan as HP’s most cost-efficient color printing solution for SMBs, ensuring lowest TCO through high-yield tanks, minimal intervention, and reduced maintenance.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top priority for SMBs. Lowest TCO is a key differentiator and core value proposition for Magellan.</t>
+          <t>Reduces user error and service calls, improving user experience and reducing support costs.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires high-yield ink tank system, optimized consumables, and robust hardware.</t>
+          <t>Requires unique bottle design and printer detection mechanism.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TCO for Magellan is demonstrably lower than comparable SMB printers (by at least 10%) in independent testing.</t>
+          <t>Keyed bottles are physically incompatible with incorrect tanks; 100% prevention rate in usability tests.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Serviceability – Customer Replaceable Parts</t>
+          <t>Non-PDL SKU – SMB Portal and PaaS Support</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Enable customer replaceable parts (e.g., maintenance box) and ensure ease of service with PHA (customer replaceable) and MINK (service center, if out of warranty) thresholds.</t>
+          <t>For Non-PDL SKUs, integrate SMB2.0 Solutions and Advanced View SMB portal, and ensure support for Printing-as-a-Service (PaaS) models.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT support and require simple, low-cost servicing options to minimize downtime.</t>
+          <t>SMB customers require centralized, simple management and flexible service models.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Quality', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Design for serviceability, documentation, and part supply chain.</t>
+          <t>Portal development, PaaS infrastructure, and integration with printer firmware.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>80%+ of common service events can be handled by customers without professional intervention. User documentation provided.</t>
+          <t>Non-PDL SKUs support SMB portal and PaaS; validated in controlled SMB pilot.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3205,52 +3205,52 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>PDL SKU – Enhanced Speed and PDL/PS Support</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
+          <t>For PDL SKUs, provide improved print speed (25/20 ppm target) and support for PDL/PS (Page Description Language/PostScript).</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Reduces user error and service calls, improving user experience and reducing support costs.</t>
+          <t>Higher speed and PDL/PS support are critical for advanced SMB workflows and compatibility.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Requires unique bottle design and printer detection mechanism.</t>
+          <t>Hardware and firmware capable of target speeds and PDL/PS support.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Keyed bottles are physically incompatible with incorrect tanks; 100% prevention rate in usability tests.</t>
+          <t>PDL SKUs achieve 25/20 ppm and pass compatibility tests with PDL/PS applications.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3258,73 +3258,73 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Non-PDL SKU – SMB Portal and PaaS Support</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>For Non-PDL SKUs, integrate SMB2.0 Solutions and Advanced View SMB portal, and ensure support for Printing-as-a-Service (PaaS) models.</t>
+          <t>Ensure Magellan meets Blue Angel environmental certification requirements for relevant SKUs.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SMB customers require centralized, simple management and flexible service models.</t>
+          <t>Sustainability is a key differentiator and increasingly required in many markets.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Portal development, PaaS infrastructure, and integration with printer firmware.</t>
+          <t>Design, materials, and manufacturing processes must comply with Blue Angel standards.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs support SMB portal and PaaS; validated in controlled SMB pilot.</t>
+          <t>Blue Angel certification is obtained for designated SKUs before launch.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PDL SKU – Enhanced Speed and PDL/PS Support</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>For PDL SKUs, provide improved print speed (25/20 ppm target) and support for PDL/PS (Page Description Language/PostScript).</t>
+          <t>Introduce a replaceable maintenance box as a new feature for Magellan, enabling users to easily maintain printer health.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Higher speed and PDL/PS support are critical for advanced SMB workflows and compatibility.</t>
+          <t>Addresses new use-cases and pain points for SMBs, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3334,17 +3334,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Tech Reg', 'BA']</t>
+          <t>['Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hardware and firmware capable of target speeds and PDL/PS support.</t>
+          <t>Design for user replacement, supply chain for maintenance boxes.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PDL SKUs achieve 25/20 ppm and pass compatibility tests with PDL/PS applications.</t>
+          <t>Maintenance box can be replaced by users in under 5 minutes with provided instructions; success rate &gt;95% in testing.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3356,73 +3356,73 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>Consolidated Device Management Portal (SMB Portal)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ensure Magellan meets Blue Angel environmental certification requirements for relevant SKUs.</t>
+          <t>Develop a consolidated portal for device management, targeting unmanaged and lightly managed SMBs for easy printer monitoring, configuration, and support.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and increasingly required in many markets.</t>
+          <t>Office managers/generalist IT need simple, centralized management tools to handle multiple printers efficiently.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Design, materials, and manufacturing processes must comply with Blue Angel standards.</t>
+          <t>Portal software development, printer integration, security compliance.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Blue Angel certification is obtained for designated SKUs before launch.</t>
+          <t>Portal allows management of at least 15 printers, with positive usability feedback from SMB pilot users.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box as a new feature for Magellan, enabling users to easily maintain printer health.</t>
+          <t>Enable seamless mobile printing and integration with the HP App for Magellan printers.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Addresses new use-cases and pain points for SMBs, reducing downtime and service costs.</t>
+          <t>Mobile printing is a core SMB use case and a top customer priority.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['Quality', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Design for user replacement, supply chain for maintenance boxes.</t>
+          <t>HP App compatibility and printer firmware support.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by users in under 5 minutes with provided instructions; success rate &gt;95% in testing.</t>
+          <t>Users can print from mobile devices via HP App with &gt;98% success rate in user testing.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3450,77 +3450,77 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Consolidated Device Management Portal (SMB Portal)</t>
+          <t>High Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal for device management, targeting unmanaged and lightly managed SMBs for easy printer monitoring, configuration, and support.</t>
+          <t>Use at least 60% recycled content plastic (RCP) in Magellan’s construction to exceed competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Office managers/generalist IT need simple, centralized management tools to handle multiple printers efficiently.</t>
+          <t>Sustainability is a key differentiator and aligns with HP’s environmental goals.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Portal software development, printer integration, security compliance.</t>
+          <t>Supply chain sourcing, manufacturing process adaptation.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Portal allows management of at least 15 printers, with positive usability feedback from SMB pilot users.</t>
+          <t>Material composition verified by third-party audit; 60%+ RCP in all applicable parts.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Warranty – 80,000 Pages or 2 Years</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing and integration with the HP App for Magellan printers.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mobile printing is a core SMB use case and a top customer priority.</t>
+          <t>Provides assurance to SMBs about durability and reliability, supporting purchase decision.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3530,17 +3530,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HP App compatibility and printer firmware support.</t>
+          <t>Hardware reliability and warranty support infrastructure.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Users can print from mobile devices via HP App with &gt;98% success rate in user testing.</t>
+          <t>Warranty terms are clearly documented and implemented in all regions at launch.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3548,28 +3548,28 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>High Recycled Content Plastic (RCP)</t>
+          <t>Telemetry and Advanced Analytics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Use at least 60% recycled content plastic (RCP) in Magellan’s construction to exceed competitor benchmarks (Epson 30%, Canon TBC).</t>
+          <t>Implement robust telemetry features to collect device usage, health, and performance data for proactive support and insights.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and aligns with HP’s environmental goals.</t>
+          <t>Enables advanced support, predictive maintenance, and continuous improvement for SMB customers.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Supply chain sourcing, manufacturing process adaptation.</t>
+          <t>Telemetry module integration, data privacy compliance.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Material composition verified by third-party audit; 60%+ RCP in all applicable parts.</t>
+          <t>Telemetry data is collected, anonymized, and accessible in the SMB portal; compliance with privacy regulations demonstrated.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3597,108 +3597,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Warranty – 80,000 Pages or 2 Years</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years (whichever comes first) for Magellan printers.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Provides assurance to SMBs about durability and reliability, supporting purchase decision.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>['Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Hardware reliability and warranty support infrastructure.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Warranty terms are clearly documented and implemented in all regions at launch.</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Telemetry and Advanced Analytics</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Implement robust telemetry features to collect device usage, health, and performance data for proactive support and insights.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Enables advanced support, predictive maintenance, and continuous improvement for SMB customers.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Telemetry module integration, data privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Telemetry data is collected, anonymized, and accessible in the SMB portal; compliance with privacy regulations demonstrated.</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
         <v>13</v>
       </c>
     </row>
